--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E5D0E2-451E-443B-A72A-84EEEA54D54A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C561227-F5A7-4980-82C8-7F98D68571FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="74">
   <si>
     <t>Booking</t>
   </si>
@@ -103,12 +103,6 @@
     <t>Salman Butt</t>
   </si>
   <si>
-    <t>Mobeen Butt</t>
-  </si>
-  <si>
-    <t>Furqan Ali</t>
-  </si>
-  <si>
     <t xml:space="preserve">Umair Rehman </t>
   </si>
   <si>
@@ -250,19 +244,10 @@
     <t>Hamid</t>
   </si>
   <si>
-    <t>Resignd</t>
-  </si>
-  <si>
-    <t>Not Available</t>
-  </si>
-  <si>
-    <t>Resigned</t>
-  </si>
-  <si>
-    <t>Waqar</t>
-  </si>
-  <si>
-    <t>Jabar</t>
+    <t>Jabbar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Umair </t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1542,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46231</v>
+        <v>46235</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1631,16 +1616,16 @@
         <v>11</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>12</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="T3" s="5" t="s">
         <v>12</v>
@@ -1677,32 +1662,38 @@
       <c r="G4" s="30">
         <v>50</v>
       </c>
-      <c r="H4" s="8"/>
+      <c r="H4" s="8">
+        <v>17</v>
+      </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0</v>
+        <v>0.34</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
-      <c r="K4" s="31"/>
+      <c r="K4" s="31">
+        <v>17</v>
+      </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="30" t="e">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N4" s="33" t="e">
+        <v>1</v>
+      </c>
+      <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O4" s="30"/>
+        <v>1.2499999999999998</v>
+      </c>
+      <c r="O4" s="30">
+        <v>17</v>
+      </c>
       <c r="P4" s="96"/>
-      <c r="Q4" s="32" t="e">
+      <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="R4" s="30"/>
       <c r="S4" s="96"/>
@@ -1742,32 +1733,38 @@
       <c r="G5" s="30">
         <v>50</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>7</v>
+      </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
-      <c r="K5" s="12"/>
+      <c r="K5" s="12">
+        <v>13</v>
+      </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="e">
+        <v>0.43333333333333335</v>
+      </c>
+      <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" s="14" t="e">
+        <v>1.8571428571428572</v>
+      </c>
+      <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O5" s="30"/>
+        <v>3.0952380952380949</v>
+      </c>
+      <c r="O5" s="30">
+        <v>7</v>
+      </c>
       <c r="P5" s="97"/>
-      <c r="Q5" s="13" t="e">
+      <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="R5" s="30"/>
       <c r="S5" s="97"/>
@@ -1802,7 +1799,7 @@
         <v>22</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G6" s="30">
         <v>50</v>
@@ -1828,7 +1825,9 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O6" s="30"/>
+      <c r="O6" s="30">
+        <v>0</v>
+      </c>
       <c r="P6" s="97"/>
       <c r="Q6" s="13" t="e">
         <f t="shared" si="3"/>
@@ -1848,9 +1847,7 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W6" s="34" t="s">
-        <v>74</v>
-      </c>
+      <c r="W6" s="34"/>
     </row>
     <row r="7" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -1869,7 +1866,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G7" s="30">
         <v>50</v>
@@ -1895,7 +1892,9 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O7" s="30"/>
+      <c r="O7" s="30">
+        <v>0</v>
+      </c>
       <c r="P7" s="97"/>
       <c r="Q7" s="13" t="e">
         <f t="shared" si="3"/>
@@ -1915,9 +1914,7 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W7" s="34" t="s">
-        <v>74</v>
-      </c>
+      <c r="W7" s="34"/>
     </row>
     <row r="8" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -1936,7 +1933,7 @@
         <v>22</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>78</v>
+        <v>26</v>
       </c>
       <c r="G8" s="30">
         <v>50</v>
@@ -2001,7 +1998,7 @@
         <v>22</v>
       </c>
       <c r="F9" s="95" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9" s="30">
         <v>0</v>
@@ -2047,9 +2044,7 @@
         <f t="shared" si="5"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="W9" s="34" t="s">
-        <v>75</v>
-      </c>
+      <c r="W9" s="34"/>
     </row>
     <row r="10" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="35" t="s">
@@ -2068,7 +2063,7 @@
         <v>22</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G10" s="30">
         <v>25</v>
@@ -2094,7 +2089,9 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O10" s="30"/>
+      <c r="O10" s="30">
+        <v>0</v>
+      </c>
       <c r="P10" s="97"/>
       <c r="Q10" s="13" t="e">
         <f t="shared" si="3"/>
@@ -2136,7 +2133,7 @@
         <v>22</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G11" s="30">
         <v>50</v>
@@ -2204,7 +2201,7 @@
         <v>22</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G12" s="30">
         <v>50</v>
@@ -2272,7 +2269,7 @@
         <v>22</v>
       </c>
       <c r="F13" s="49" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G13" s="11"/>
       <c r="H13" s="12"/>
@@ -2312,7 +2309,7 @@
         <v>22</v>
       </c>
       <c r="F14" s="49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="12"/>
@@ -2352,7 +2349,7 @@
         <v>22</v>
       </c>
       <c r="F15" s="49" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="12"/>
@@ -2430,7 +2427,7 @@
         <v>22</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="12"/>
@@ -2470,7 +2467,7 @@
         <v>22</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G18" s="36"/>
       <c r="H18" s="37"/>
@@ -2514,11 +2511,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>6.4000000000000001E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2526,15 +2523,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="40" t="e">
+        <v>7.792207792207792E-2</v>
+      </c>
+      <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>#DIV/0!</v>
+        <v>1.25</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2542,15 +2539,15 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
         <v>0</v>
       </c>
-      <c r="Q19" s="42" t="e">
+      <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>#DIV/0!</v>
+        <v>0</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
@@ -2588,13 +2585,13 @@
         <v>21</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
@@ -2666,13 +2663,13 @@
         <v>21</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E21" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F21" s="18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G21" s="11">
         <v>50</v>
@@ -2744,13 +2741,13 @@
         <v>21</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G22" s="11">
         <v>50</v>
@@ -2822,13 +2819,13 @@
         <v>21</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G23" s="11">
         <v>50</v>
@@ -2900,13 +2897,13 @@
         <v>21</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="G24" s="36">
         <v>50</v>
@@ -3056,13 +3053,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F26" s="52" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G26" s="7">
         <v>600</v>
@@ -3131,13 +3128,13 @@
         <v>21</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="G27" s="11">
         <v>600</v>
@@ -3206,13 +3203,13 @@
         <v>21</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G28" s="11">
         <v>600</v>
@@ -3281,13 +3278,13 @@
         <v>21</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F29" s="53" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="G29" s="36">
         <v>600</v>
@@ -3431,7 +3428,7 @@
         <v>20</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" s="57"/>
       <c r="D31" s="57"/>
@@ -3443,11 +3440,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>138</v>
+        <v>162</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>4.5619834710743802E-2</v>
+        <v>5.3553719008264465E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3455,15 +3452,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>167</v>
+        <v>197</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>6.4603481624758222E-2</v>
+        <v>7.6208897485493227E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.2101449275362319</v>
+        <v>1.2160493827160495</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3471,7 +3468,7 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
@@ -3479,7 +3476,7 @@
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.75838926174496646</v>
+        <v>0.65317919075144504</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
@@ -3545,16 +3542,16 @@
   <sheetData>
     <row r="1" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="61" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="D1" s="61" t="s">
         <v>58</v>
-      </c>
-      <c r="C1" s="61" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="61" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -3562,33 +3559,33 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>3.8461538461538464E-2</v>
+        <v>0.11538461538461539</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F2" s="94">
-        <v>46235</v>
+        <v>46237</v>
       </c>
       <c r="G2" s="107" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H2" s="108"/>
       <c r="I2" s="108"/>
       <c r="J2" s="104" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K2" s="105"/>
       <c r="L2" s="105"/>
       <c r="M2" s="105"/>
       <c r="N2" s="106"/>
       <c r="O2" s="110" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="P2" s="111"/>
     </row>
@@ -3615,25 +3612,25 @@
         <v>10</v>
       </c>
       <c r="H3" s="59" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="I3" s="27" t="s">
         <v>12</v>
       </c>
       <c r="J3" s="64" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="K3" s="65" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="L3" s="65" t="s">
         <v>12</v>
       </c>
       <c r="M3" s="65" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="N3" s="66" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="O3" s="67" t="s">
         <v>15</v>
@@ -3667,30 +3664,34 @@
       <c r="G4" s="30">
         <v>600</v>
       </c>
-      <c r="H4" s="31"/>
+      <c r="H4" s="31">
+        <v>14</v>
+      </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0</v>
+        <v>2.3333333333333334E-2</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
-      <c r="K4" s="8"/>
+      <c r="K4" s="8">
+        <v>21</v>
+      </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0</v>
+        <v>3.6521739130434785E-2</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>575</v>
+        <v>554</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>23</v>
-      </c>
-      <c r="O4" s="69" t="e">
+        <v>24.086956521739129</v>
+      </c>
+      <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>#DIV/0!</v>
+        <v>1.5</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3719,34 +3720,38 @@
       <c r="G5" s="30">
         <v>600</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>11</v>
+      </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.8333333333333333E-2</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
-      <c r="K5" s="12"/>
+      <c r="K5" s="12">
+        <v>20</v>
+      </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>3.6363636363636362E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="O5" s="72" t="e">
+        <v>23.043478260869566</v>
+      </c>
+      <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P5" s="14" t="e">
+        <v>1.8181818181818181</v>
+      </c>
+      <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>1.9834710743801651</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3767,43 +3772,45 @@
         <v>22</v>
       </c>
       <c r="F6" s="17" t="s">
-        <v>25</v>
+        <v>73</v>
       </c>
       <c r="G6" s="30">
         <v>600</v>
       </c>
-      <c r="H6" s="12"/>
+      <c r="H6" s="12">
+        <v>10</v>
+      </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
-      <c r="K6" s="12"/>
+      <c r="K6" s="12">
+        <v>12</v>
+      </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.181818181818182E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>22</v>
-      </c>
-      <c r="O6" s="72" t="e">
+        <v>23.391304347826086</v>
+      </c>
+      <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P6" s="14" t="e">
+        <v>1.2</v>
+      </c>
+      <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q6" s="34" t="s">
-        <v>76</v>
-      </c>
+        <v>1.3090909090909093</v>
+      </c>
+      <c r="Q6" s="34"/>
     </row>
     <row r="7" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -3822,7 +3829,7 @@
         <v>22</v>
       </c>
       <c r="F7" s="17" t="s">
-        <v>26</v>
+        <v>72</v>
       </c>
       <c r="G7" s="30">
         <v>600</v>
@@ -3846,7 +3853,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>22</v>
+        <v>23.913043478260871</v>
       </c>
       <c r="O7" s="72" t="e">
         <f t="shared" si="4"/>
@@ -3856,9 +3863,7 @@
         <f t="shared" si="4"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q7" s="34" t="s">
-        <v>76</v>
-      </c>
+      <c r="Q7" s="34"/>
     </row>
     <row r="8" spans="1:17" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -3877,7 +3882,7 @@
         <v>22</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="30">
         <v>600</v>
@@ -3901,7 +3906,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="O8" s="72" t="e">
         <f t="shared" si="4"/>
@@ -3930,7 +3935,7 @@
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9" s="30">
         <v>600</v>
@@ -3954,7 +3959,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23.913043478260871</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -3983,12 +3988,14 @@
         <v>22</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G10" s="11">
         <v>200</v>
       </c>
-      <c r="H10" s="12"/>
+      <c r="H10" s="12">
+        <v>0</v>
+      </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -4007,7 +4014,7 @@
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>184.8</v>
+        <v>200.86956521739131</v>
       </c>
       <c r="O10" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4036,7 +4043,7 @@
         <v>22</v>
       </c>
       <c r="F11" s="17" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G11" s="11">
         <v>600</v>
@@ -4060,7 +4067,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>26</v>
+        <v>28.260869565217391</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4089,7 +4096,7 @@
         <v>22</v>
       </c>
       <c r="F12" s="17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G12" s="11">
         <v>600</v>
@@ -4113,7 +4120,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23.913043478260871</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4189,7 +4196,7 @@
         <v>22</v>
       </c>
       <c r="F14" s="49" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G14" s="11"/>
       <c r="H14" s="12"/>
@@ -4238,7 +4245,7 @@
         <v>22</v>
       </c>
       <c r="F15" s="49" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="12"/>
@@ -4287,7 +4294,7 @@
         <v>22</v>
       </c>
       <c r="F16" s="49" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="G16" s="11"/>
       <c r="H16" s="12"/>
@@ -4309,7 +4316,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>60</v>
+        <v>65.217391304347828</v>
       </c>
       <c r="O16" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4338,7 +4345,7 @@
         <v>22</v>
       </c>
       <c r="F17" s="49" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="G17" s="11"/>
       <c r="H17" s="12"/>
@@ -4375,7 +4382,7 @@
         <v>22</v>
       </c>
       <c r="F18" s="50" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G18" s="36"/>
       <c r="H18" s="37"/>
@@ -4416,11 +4423,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4428,23 +4435,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>0</v>
+        <v>53</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0</v>
+        <v>4.9671977507029057E-3</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>10670</v>
+        <v>10617</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>426.8</v>
-      </c>
-      <c r="O19" s="84" t="e">
+        <v>461.60869565217394</v>
+      </c>
+      <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>#DIV/0!</v>
+        <v>1.5142857142857142</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4463,13 +4470,13 @@
         <v>21</v>
       </c>
       <c r="D20" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E20" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="52" t="s">
         <v>31</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F20" s="52" t="s">
-        <v>33</v>
       </c>
       <c r="G20" s="7">
         <v>50</v>
@@ -4497,7 +4504,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>18.600000000000001</v>
+        <v>20.217391304347824</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4519,13 +4526,13 @@
         <v>21</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E21" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="18" t="s">
         <v>32</v>
-      </c>
-      <c r="F21" s="18" t="s">
-        <v>34</v>
       </c>
       <c r="G21" s="7">
         <v>50</v>
@@ -4553,7 +4560,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>18.68</v>
+        <v>20.304347826086957</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4575,13 +4582,13 @@
         <v>21</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E22" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F22" s="18" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G22" s="7">
         <v>50</v>
@@ -4609,7 +4616,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>18.559999999999999</v>
+        <v>20.173913043478262</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4631,13 +4638,13 @@
         <v>21</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E23" s="16" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F23" s="18" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G23" s="7">
         <v>50</v>
@@ -4665,7 +4672,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>18.920000000000002</v>
+        <v>20.565217391304348</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4687,13 +4694,13 @@
         <v>21</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F24" s="53" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G24" s="7">
         <v>50</v>
@@ -4721,7 +4728,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>19.36</v>
+        <v>21.043478260869566</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4777,7 +4784,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>94.12</v>
+        <v>102.30434782608695</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4800,13 +4807,13 @@
         <v>21</v>
       </c>
       <c r="D26" s="15" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F26" s="52" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="G26" s="7">
         <v>50</v>
@@ -4834,7 +4841,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>24.64</v>
+        <v>26.782608695652176</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4856,13 +4863,13 @@
         <v>21</v>
       </c>
       <c r="D27" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E27" s="16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F27" s="18" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="G27" s="11">
         <v>50</v>
@@ -4890,7 +4897,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>22.64</v>
+        <v>24.608695652173914</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4912,13 +4919,13 @@
         <v>21</v>
       </c>
       <c r="D28" s="16" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E28" s="16" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F28" s="18" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G28" s="11">
         <v>50</v>
@@ -4946,7 +4953,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>22.96</v>
+        <v>24.956521739130434</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -4968,13 +4975,13 @@
         <v>21</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F29" s="53" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G29" s="36">
         <v>50</v>
@@ -5002,7 +5009,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>24.48</v>
+        <v>26.608695652173914</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5058,7 +5065,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>94.72</v>
+        <v>102.95652173913044</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5075,7 +5082,7 @@
         <v>20</v>
       </c>
       <c r="B31" s="56" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C31" s="57"/>
       <c r="D31" s="57"/>
@@ -5087,11 +5094,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>3.6880733944954128E-2</v>
+        <v>4.3302752293577981E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5099,23 +5106,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>1.7804722399489471E-2</v>
+        <v>2.1186981493299298E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>15391</v>
+        <v>15338</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>615.64</v>
+        <v>666.86956521739125</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>1.3880597014925373</v>
+        <v>1.4067796610169492</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C561227-F5A7-4980-82C8-7F98D68571FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93F160D-7E6D-4D07-8F37-01888AFD4ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46235</v>
+        <v>46238</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1663,51 +1663,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>17</v>
+        <v>32.5</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.42499999999999999</v>
+        <v>0.8125</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1</v>
+        <v>1.4130434782608696</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.2499999999999998</v>
+        <v>1.7663043478260869</v>
       </c>
       <c r="O4" s="30">
-        <v>17</v>
-      </c>
-      <c r="P4" s="96"/>
+        <v>21</v>
+      </c>
+      <c r="P4" s="96">
+        <v>19</v>
+      </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0</v>
-      </c>
-      <c r="R4" s="30"/>
-      <c r="S4" s="96"/>
-      <c r="T4" s="32" t="e">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="R4" s="30">
+        <v>24</v>
+      </c>
+      <c r="S4" s="96">
+        <v>23</v>
+      </c>
+      <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" s="30" t="e">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" s="33" t="e">
+        <v>1.2105263157894737</v>
+      </c>
+      <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1.0592105263157896</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1734,37 +1740,35 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.43333333333333335</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.8571428571428572</v>
+        <v>1.8181818181818181</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>3.0952380952380949</v>
-      </c>
-      <c r="O5" s="30">
-        <v>7</v>
-      </c>
+        <v>3.0303030303030303</v>
+      </c>
+      <c r="O5" s="30"/>
       <c r="P5" s="97"/>
-      <c r="Q5" s="13">
+      <c r="Q5" s="13" t="e">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R5" s="30"/>
       <c r="S5" s="97"/>
@@ -1804,48 +1808,58 @@
       <c r="G6" s="30">
         <v>50</v>
       </c>
-      <c r="H6" s="12"/>
+      <c r="H6" s="12">
+        <v>8</v>
+      </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
-      <c r="K6" s="12"/>
+      <c r="K6" s="12">
+        <v>16</v>
+      </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="11" t="e">
+        <v>0.64</v>
+      </c>
+      <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N6" s="14" t="e">
+        <v>2</v>
+      </c>
+      <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>4</v>
       </c>
       <c r="O6" s="30">
-        <v>0</v>
-      </c>
-      <c r="P6" s="97"/>
-      <c r="Q6" s="13" t="e">
+        <v>5</v>
+      </c>
+      <c r="P6" s="97">
+        <v>9</v>
+      </c>
+      <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R6" s="30"/>
-      <c r="S6" s="97"/>
-      <c r="T6" s="13" t="e">
+        <v>1.8</v>
+      </c>
+      <c r="R6" s="30">
+        <v>3</v>
+      </c>
+      <c r="S6" s="97">
+        <v>5</v>
+      </c>
+      <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" s="11" t="e">
+        <v>1.6666666666666667</v>
+      </c>
+      <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V6" s="14" t="e">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.92592592592592593</v>
       </c>
       <c r="W6" s="34"/>
     </row>
@@ -2068,22 +2082,26 @@
       <c r="G10" s="30">
         <v>25</v>
       </c>
-      <c r="H10" s="12"/>
+      <c r="H10" s="12">
+        <v>2</v>
+      </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
-      <c r="K10" s="12"/>
+      <c r="K10" s="12">
+        <v>20</v>
+      </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M10" s="11" t="e">
+      <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>10</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2511,11 +2529,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>6.4000000000000001E-2</v>
+        <v>0.11733333333333333</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2523,15 +2541,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>30</v>
+        <v>88.5</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>7.792207792207792E-2</v>
+        <v>0.22987012987012986</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>1.25</v>
+        <v>2.0113636363636362</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2539,31 +2557,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0</v>
+        <v>1.0769230769230769</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>0</v>
-      </c>
-      <c r="T19" s="42" t="e">
+        <v>28</v>
+      </c>
+      <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U19" s="40" t="e">
+        <v>1.037037037037037</v>
+      </c>
+      <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3440,11 +3458,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>162</v>
+        <v>182</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.3553719008264465E-2</v>
+        <v>6.0165289256198344E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3452,15 +3470,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>197</v>
+        <v>255.5</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>7.6208897485493227E-2</v>
+        <v>9.8839458413926495E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.2160493827160495</v>
+        <v>1.4038461538461537</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3468,31 +3486,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.65317919075144504</v>
+        <v>0.80571428571428572</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.54393305439330542</v>
+        <v>0.59398496240601506</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.1504424778761062</v>
+        <v>1.1205673758865249</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3559,18 +3577,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.11538461538461539</v>
+        <v>0.15384615384615385</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F2" s="94">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3665,33 +3683,35 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <v>14</v>
+        <f>14+19</f>
+        <v>33</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>2.3333333333333334E-2</v>
+        <v>5.5E-2</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <v>21</v>
+        <f>21+22.7</f>
+        <v>43.7</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>3.6521739130434785E-2</v>
+        <v>7.5999999999999998E-2</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>554</v>
+        <v>531.29999999999995</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>24.086956521739129</v>
+        <v>24.15</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.5</v>
+        <v>1.3242424242424242</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3721,37 +3741,39 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <v>11</v>
+        <f>11+3</f>
+        <v>14</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>1.8333333333333333E-2</v>
+        <v>2.3333333333333334E-2</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <v>20</v>
+        <f>20+5</f>
+        <v>25</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>3.6363636363636362E-2</v>
+        <v>4.5454545454545456E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>23.043478260869566</v>
+        <v>23.863636363636363</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.8181818181818181</v>
+        <v>1.7857142857142858</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.9834710743801651</v>
+        <v>1.948051948051948</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3800,7 +3822,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>23.391304347826086</v>
+        <v>24.454545454545453</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3853,7 +3875,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>23.913043478260871</v>
+        <v>25</v>
       </c>
       <c r="O7" s="72" t="e">
         <f t="shared" si="4"/>
@@ -3906,7 +3928,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26.136363636363637</v>
       </c>
       <c r="O8" s="72" t="e">
         <f t="shared" si="4"/>
@@ -3959,7 +3981,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>23.913043478260871</v>
+        <v>25</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4014,7 +4036,7 @@
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>200.86956521739131</v>
+        <v>210</v>
       </c>
       <c r="O10" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4067,7 +4089,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>28.260869565217391</v>
+        <v>29.545454545454547</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4120,7 +4142,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>23.913043478260871</v>
+        <v>25</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4316,7 +4338,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>65.217391304347828</v>
+        <v>68.181818181818187</v>
       </c>
       <c r="O16" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4423,11 +4445,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>7.0000000000000001E-3</v>
+        <v>1.14E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4435,23 +4457,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>53</v>
+        <v>80.7</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>4.9671977507029057E-3</v>
+        <v>7.5632614807872546E-3</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>10617</v>
+        <v>10589.3</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>461.60869565217394</v>
+        <v>481.33181818181816</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>1.5142857142857142</v>
+        <v>1.4157894736842105</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4504,7 +4526,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>20.217391304347824</v>
+        <v>21.136363636363637</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4560,7 +4582,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>20.304347826086957</v>
+        <v>21.227272727272727</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4616,7 +4638,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>20.173913043478262</v>
+        <v>21.09090909090909</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4672,7 +4694,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>20.565217391304348</v>
+        <v>21.5</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4728,7 +4750,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>21.043478260869566</v>
+        <v>22</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4784,7 +4806,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>102.30434782608695</v>
+        <v>106.95454545454545</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4841,7 +4863,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>26.782608695652176</v>
+        <v>28</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4897,7 +4919,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>24.608695652173914</v>
+        <v>25.727272727272727</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4953,7 +4975,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>24.956521739130434</v>
+        <v>26.09090909090909</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5009,7 +5031,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>26.608695652173914</v>
+        <v>27.818181818181817</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5065,7 +5087,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>102.95652173913044</v>
+        <v>107.63636363636364</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5094,11 +5116,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>236</v>
+        <v>258</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>4.3302752293577981E-2</v>
+        <v>4.7339449541284405E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5106,23 +5128,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>332</v>
+        <v>359.7</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>2.1186981493299298E-2</v>
+        <v>2.2954690491384811E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>15338</v>
+        <v>15310.3</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>666.86956521739125</v>
+        <v>695.92272727272723</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>1.4067796610169492</v>
+        <v>1.3941860465116278</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93F160D-7E6D-4D07-8F37-01888AFD4ACA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67271442-2984-4565-9FF2-61E0EBF89012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1501,7 +1501,7 @@
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.453125" customWidth="1"/>
+    <col min="6" max="6" width="24.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.453125" style="24" customWidth="1"/>
     <col min="8" max="8" width="7.7265625" customWidth="1"/>
     <col min="9" max="9" width="5.54296875" customWidth="1"/>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1663,57 +1663,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.46</v>
+        <v>0.32</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>32.5</v>
+        <v>12</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.8125</v>
+        <v>0.3</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.4130434782608696</v>
+        <v>0.75</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.7663043478260869</v>
+        <v>0.9375</v>
       </c>
       <c r="O4" s="30">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P4" s="96">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.90476190476190477</v>
+        <v>0.91304347826086951</v>
       </c>
       <c r="R4" s="30">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="S4" s="96">
         <v>23</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.95833333333333337</v>
+        <v>0.69696969696969702</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.2105263157894737</v>
+        <v>1.0952380952380953</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>1.0592105263157896</v>
+        <v>0.76334776334776344</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1740,49 +1740,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.66666666666666663</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.8181818181818181</v>
+        <v>2</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>3.0303030303030303</v>
-      </c>
-      <c r="O5" s="30"/>
-      <c r="P5" s="97"/>
-      <c r="Q5" s="13" t="e">
+        <v>3.333333333333333</v>
+      </c>
+      <c r="O5" s="30">
+        <v>11</v>
+      </c>
+      <c r="P5" s="97">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R5" s="30"/>
-      <c r="S5" s="97"/>
-      <c r="T5" s="13" t="e">
+        <v>1</v>
+      </c>
+      <c r="R5" s="30">
+        <v>20</v>
+      </c>
+      <c r="S5" s="97">
+        <v>20</v>
+      </c>
+      <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U5" s="11" t="e">
+        <v>1</v>
+      </c>
+      <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V5" s="14" t="e">
+        <v>1.8181818181818181</v>
+      </c>
+      <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1809,57 +1817,57 @@
         <v>50</v>
       </c>
       <c r="H6" s="12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.16</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
       <c r="K6" s="12">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.64</v>
+        <v>0.32</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>4</v>
+        <v>2.2857142857142856</v>
       </c>
       <c r="O6" s="30">
+        <v>8</v>
+      </c>
+      <c r="P6" s="97">
         <v>5</v>
-      </c>
-      <c r="P6" s="97">
-        <v>9</v>
       </c>
       <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>1.8</v>
+        <v>0.625</v>
       </c>
       <c r="R6" s="30">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="S6" s="97">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>1.6666666666666667</v>
+        <v>0.8</v>
       </c>
       <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>0.55555555555555558</v>
+        <v>2.4</v>
       </c>
       <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>0.92592592592592593</v>
+        <v>1.28</v>
       </c>
       <c r="W6" s="34"/>
     </row>
@@ -1885,26 +1893,30 @@
       <c r="G7" s="30">
         <v>50</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="12">
+        <v>5</v>
+      </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
-      <c r="K7" s="12"/>
+      <c r="K7" s="12">
+        <v>4</v>
+      </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="e">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="14" t="e">
+        <v>0.8</v>
+      </c>
+      <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="O7" s="30">
         <v>0</v>
@@ -2083,17 +2095,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2101,33 +2113,39 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>10</v>
+        <v>16.666666666666668</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>0</v>
-      </c>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="13" t="e">
+        <v>2</v>
+      </c>
+      <c r="P10" s="97">
+        <v>2</v>
+      </c>
+      <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R10" s="30"/>
-      <c r="S10" s="97"/>
-      <c r="T10" s="13" t="e">
+        <v>1</v>
+      </c>
+      <c r="R10" s="30">
+        <v>29</v>
+      </c>
+      <c r="S10" s="97">
+        <v>29</v>
+      </c>
+      <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U10" s="11" t="e">
+        <v>1</v>
+      </c>
+      <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V10" s="14" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="W10" s="34"/>
       <c r="AB10">
@@ -2529,11 +2547,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.11733333333333333</v>
+        <v>0.10133333333333333</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2541,15 +2559,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>88.5</v>
+        <v>88</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.22987012987012986</v>
+        <v>0.22857142857142856</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>2.0113636363636362</v>
+        <v>2.3157894736842106</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2557,31 +2575,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>1.0769230769230769</v>
+        <v>0.88636363636363635</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>1.037037037037037</v>
+        <v>0.865979381443299</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>1</v>
+        <v>2.1538461538461537</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3458,11 +3476,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>6.0165289256198344E-2</v>
+        <v>5.8181818181818182E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3470,15 +3488,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>255.5</v>
+        <v>255</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>9.8839458413926495E-2</v>
+        <v>9.8646034816247577E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.4038461538461537</v>
+        <v>1.4488636363636365</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3486,31 +3504,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.80571428571428572</v>
+        <v>0.78756476683937826</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>158</v>
+        <v>214</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.59398496240601506</v>
+        <v>0.63690476190476186</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.1205673758865249</v>
+        <v>1.4078947368421053</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3544,7 +3562,7 @@
     <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.1796875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="24" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.1796875" bestFit="1" customWidth="1"/>
@@ -3577,18 +3595,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.15384615384615385</v>
+        <v>0.19230769230769232</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F2" s="94">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3683,35 +3701,35 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>14+19</f>
-        <v>33</v>
+        <f>14+19+21</f>
+        <v>54</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>5.5E-2</v>
+        <v>0.09</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <f>21+22.7</f>
-        <v>43.7</v>
+        <f>21+22.7+22.5</f>
+        <v>66.2</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>7.5999999999999998E-2</v>
+        <v>0.1151304347826087</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>531.29999999999995</v>
+        <v>508.8</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>24.15</v>
+        <v>24.228571428571428</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.3242424242424242</v>
+        <v>1.2259259259259261</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3741,39 +3759,39 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>11+3</f>
-        <v>14</v>
+        <f>11+3+11</f>
+        <v>25</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>2.3333333333333334E-2</v>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <f>20+5</f>
-        <v>25</v>
+        <f>20+5+19.9</f>
+        <v>44.9</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>4.5454545454545456E-2</v>
+        <v>8.1636363636363632E-2</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>525</v>
+        <v>505.1</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>23.863636363636363</v>
+        <v>24.052380952380954</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.7857142857142858</v>
+        <v>1.796</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.948051948051948</v>
+        <v>1.9592727272727273</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3800,37 +3818,39 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <v>10</v>
+        <f>10+5</f>
+        <v>15</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>1.6666666666666666E-2</v>
+        <v>2.5000000000000001E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>12</v>
+        <f>12+12.1</f>
+        <v>24.1</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>2.181818181818182E-2</v>
+        <v>4.3818181818181819E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>538</v>
+        <v>525.9</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>24.454545454545453</v>
+        <v>25.042857142857141</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.2</v>
+        <v>1.6066666666666667</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.3090909090909093</v>
+        <v>1.7527272727272727</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3875,7 +3895,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>25</v>
+        <v>26.19047619047619</v>
       </c>
       <c r="O7" s="72" t="e">
         <f t="shared" si="4"/>
@@ -3928,7 +3948,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>26.136363636363637</v>
+        <v>27.38095238095238</v>
       </c>
       <c r="O8" s="72" t="e">
         <f t="shared" si="4"/>
@@ -3981,7 +4001,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26.19047619047619</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4016,35 +4036,37 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
-      <c r="K10" s="12"/>
+      <c r="K10" s="12">
+        <v>29</v>
+      </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>6.2770562770562768E-3</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>4620</v>
+        <v>4591</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>210</v>
-      </c>
-      <c r="O10" s="72" t="e">
+        <v>218.61904761904762</v>
+      </c>
+      <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P10" s="14" t="e">
+        <v>14.5</v>
+      </c>
+      <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0.62770562770562766</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4089,7 +4111,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>29.545454545454547</v>
+        <v>30.952380952380953</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4142,7 +4164,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>25</v>
+        <v>26.19047619047619</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4338,7 +4360,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>68.181818181818187</v>
+        <v>71.428571428571431</v>
       </c>
       <c r="O16" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4445,11 +4467,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>57</v>
+        <v>96</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>1.14E-2</v>
+        <v>1.9199999999999998E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4457,23 +4479,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>80.7</v>
+        <v>164.2</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>7.5632614807872546E-3</v>
+        <v>1.5388940955951265E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>10589.3</v>
+        <v>10505.8</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>481.33181818181816</v>
+        <v>500.27619047619044</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>1.4157894736842105</v>
+        <v>1.7104166666666665</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4526,7 +4548,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>21.136363636363637</v>
+        <v>22.142857142857142</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4582,7 +4604,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>21.227272727272727</v>
+        <v>22.238095238095237</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4638,7 +4660,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>21.09090909090909</v>
+        <v>22.095238095238095</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4694,7 +4716,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>21.5</v>
+        <v>22.523809523809526</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4750,7 +4772,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>22</v>
+        <v>23.047619047619047</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4806,7 +4828,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>106.95454545454545</v>
+        <v>112.04761904761905</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4863,7 +4885,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>28</v>
+        <v>29.333333333333332</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4919,7 +4941,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>25.727272727272727</v>
+        <v>26.952380952380953</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4975,7 +4997,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>26.09090909090909</v>
+        <v>27.333333333333332</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5031,7 +5053,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>27.818181818181817</v>
+        <v>29.142857142857142</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5087,7 +5109,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>107.63636363636364</v>
+        <v>112.76190476190476</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5116,11 +5138,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>258</v>
+        <v>297</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>4.7339449541284405E-2</v>
+        <v>5.4495412844036695E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5128,23 +5150,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>359.7</v>
+        <v>443.2</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>2.2954690491384811E-2</v>
+        <v>2.828334396936822E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>15310.3</v>
+        <v>15226.8</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>695.92272727272723</v>
+        <v>725.08571428571429</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>1.3941860465116278</v>
+        <v>1.4922558922558922</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67271442-2984-4565-9FF2-61E0EBF89012}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADDF78DA-196F-443F-9ABF-2D4B76272341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1663,57 +1663,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.32</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.3</v>
+        <v>0.47499999999999998</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>0.75</v>
+        <v>1.3571428571428572</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>0.9375</v>
+        <v>1.6964285714285712</v>
       </c>
       <c r="O4" s="30">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="P4" s="96">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.91304347826086951</v>
+        <v>0.8125</v>
       </c>
       <c r="R4" s="30">
-        <v>33</v>
+        <v>12</v>
       </c>
       <c r="S4" s="96">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.69696969696969702</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.0952380952380953</v>
+        <v>0.53846153846153844</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>0.76334776334776344</v>
+        <v>0.71794871794871795</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1740,57 +1740,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.22</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.46666666666666667</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>3.333333333333333</v>
+        <v>1.6666666666666665</v>
       </c>
       <c r="O5" s="30">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="P5" s="97">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="R5" s="30">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="S5" s="97">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>1.8181818181818181</v>
+        <v>2.1666666666666665</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.0833333333333335</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1817,57 +1817,57 @@
         <v>50</v>
       </c>
       <c r="H6" s="12">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.14000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
       <c r="K6" s="12">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.32</v>
+        <v>0.2</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>1.1428571428571428</v>
+        <v>1</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>2.2857142857142856</v>
+        <v>2</v>
       </c>
       <c r="O6" s="30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="P6" s="97">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>0.625</v>
+        <v>1</v>
       </c>
       <c r="R6" s="30">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="S6" s="97">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>2.4</v>
+        <v>1.1428571428571428</v>
       </c>
       <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>1.28</v>
+        <v>1</v>
       </c>
       <c r="W6" s="34"/>
     </row>
@@ -1894,51 +1894,57 @@
         <v>50</v>
       </c>
       <c r="H7" s="12">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.12</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.13333333333333333</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>0.8</v>
+        <v>1.1666666666666667</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>1.3333333333333333</v>
+        <v>1.9444444444444446</v>
       </c>
       <c r="O7" s="30">
-        <v>0</v>
-      </c>
-      <c r="P7" s="97"/>
-      <c r="Q7" s="13" t="e">
+        <v>5</v>
+      </c>
+      <c r="P7" s="97">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R7" s="30"/>
-      <c r="S7" s="97"/>
-      <c r="T7" s="13" t="e">
+        <v>0.2</v>
+      </c>
+      <c r="R7" s="30">
+        <v>3</v>
+      </c>
+      <c r="S7" s="97">
+        <v>0.3</v>
+      </c>
+      <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U7" s="11" t="e">
+        <v>9.9999999999999992E-2</v>
+      </c>
+      <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V7" s="14" t="e">
+        <v>0.3</v>
+      </c>
+      <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>0.49999999999999994</v>
       </c>
       <c r="W7" s="34"/>
     </row>
@@ -2105,7 +2111,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>50</v>
+        <v>81</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2113,39 +2119,39 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>16.666666666666668</v>
+        <v>27</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P10" s="97">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R10" s="30">
-        <v>29</v>
+        <v>115</v>
       </c>
       <c r="S10" s="97">
-        <v>29</v>
+        <v>114</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.99130434782608701</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>14.5</v>
+        <v>22.8</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.99130434782608701</v>
       </c>
       <c r="W10" s="34"/>
       <c r="AB10">
@@ -2547,11 +2553,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.10133333333333333</v>
+        <v>0.104</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2559,15 +2565,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>88</v>
+        <v>123</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.22857142857142856</v>
+        <v>0.31948051948051948</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>2.3157894736842106</v>
+        <v>3.1538461538461537</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2575,31 +2581,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.88636363636363635</v>
+        <v>0.8</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>97</v>
+        <v>152</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>84</v>
+        <v>142.30000000000001</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.865979381443299</v>
+        <v>0.93618421052631584</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>2.1538461538461537</v>
+        <v>4.4468750000000004</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3476,11 +3482,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.8181818181818182E-2</v>
+        <v>5.8512396694214874E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3488,15 +3494,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>255</v>
+        <v>290</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>9.8646034816247577E-2</v>
+        <v>0.11218568665377177</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.4488636363636365</v>
+        <v>1.6384180790960452</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3504,31 +3510,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.78756476683937826</v>
+        <v>0.76719576719576721</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>336</v>
+        <v>391</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>214</v>
+        <v>272.3</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.63690476190476186</v>
+        <v>0.69641943734015344</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.4078947368421053</v>
+        <v>1.8779310344827587</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3595,18 +3601,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.19230769230769232</v>
+        <v>0.23076923076923078</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F2" s="94">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3701,35 +3707,35 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>14+19+21</f>
-        <v>54</v>
+        <f>14+19+21+13</f>
+        <v>67</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.09</v>
+        <v>0.11166666666666666</v>
       </c>
       <c r="J4" s="30">
         <v>575</v>
       </c>
       <c r="K4" s="8">
-        <f>21+22.7+22.5</f>
-        <v>66.2</v>
+        <f>21+22.7+22.5+7.4</f>
+        <v>73.600000000000009</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.1151304347826087</v>
+        <v>0.128</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>508.8</v>
+        <v>501.4</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>24.228571428571428</v>
+        <v>25.07</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.2259259259259261</v>
+        <v>1.0985074626865672</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3759,39 +3765,39 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>11+3+11</f>
-        <v>25</v>
+        <f>11+3+11+6</f>
+        <v>31</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>4.1666666666666664E-2</v>
+        <v>5.1666666666666666E-2</v>
       </c>
       <c r="J5" s="11">
         <v>550</v>
       </c>
       <c r="K5" s="12">
-        <f>20+5+19.9</f>
-        <v>44.9</v>
+        <f>20+5+19.9+13.1</f>
+        <v>58</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>8.1636363636363632E-2</v>
+        <v>0.10545454545454545</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>505.1</v>
+        <v>492</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>24.052380952380954</v>
+        <v>24.6</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.796</v>
+        <v>1.8709677419354838</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.9592727272727273</v>
+        <v>2.0410557184750733</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3818,39 +3824,39 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>10+5</f>
-        <v>15</v>
+        <f>10+5+7</f>
+        <v>22</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>2.5000000000000001E-2</v>
+        <v>3.6666666666666667E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <f>12+12.1</f>
-        <v>24.1</v>
+        <f>12+12.1+8.4</f>
+        <v>32.5</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>4.3818181818181819E-2</v>
+        <v>5.909090909090909E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>525.9</v>
+        <v>517.5</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>25.042857142857141</v>
+        <v>25.875</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.6066666666666667</v>
+        <v>1.4772727272727273</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.7527272727272727</v>
+        <v>1.6115702479338843</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3895,7 +3901,7 @@
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>26.19047619047619</v>
+        <v>27.5</v>
       </c>
       <c r="O7" s="72" t="e">
         <f t="shared" si="4"/>
@@ -3948,7 +3954,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>27.38095238095238</v>
+        <v>28.75</v>
       </c>
       <c r="O8" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4001,7 +4007,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>26.19047619047619</v>
+        <v>27.5</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4036,37 +4042,39 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <v>2</v>
+        <f>2+5</f>
+        <v>7</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.01</v>
+        <v>3.5000000000000003E-2</v>
       </c>
       <c r="J10" s="11">
         <v>4620</v>
       </c>
       <c r="K10" s="12">
-        <v>29</v>
+        <f>29+113.8</f>
+        <v>142.80000000000001</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>6.2770562770562768E-3</v>
+        <v>3.090909090909091E-2</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>4591</v>
+        <v>4477.2</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>218.61904761904762</v>
+        <v>223.85999999999999</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>14.5</v>
+        <v>20.400000000000002</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.62770562770562766</v>
+        <v>0.88311688311688308</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4111,7 +4119,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>30.952380952380953</v>
+        <v>32.5</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4164,7 +4172,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>26.19047619047619</v>
+        <v>27.5</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4243,16 +4251,22 @@
         <v>44</v>
       </c>
       <c r="G14" s="11"/>
-      <c r="H14" s="12"/>
+      <c r="H14" s="12">
+        <v>1</v>
+      </c>
       <c r="I14" s="70" t="e">
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J14" s="11"/>
-      <c r="K14" s="12"/>
-      <c r="L14" s="71" t="e">
+      <c r="J14" s="11">
+        <v>100</v>
+      </c>
+      <c r="K14" s="12">
+        <v>100</v>
+      </c>
+      <c r="L14" s="71">
         <f t="shared" si="8"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="M14" s="12">
         <f t="shared" si="5"/>
@@ -4262,9 +4276,9 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="O14" s="72" t="e">
+      <c r="O14" s="72">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>100</v>
       </c>
       <c r="P14" s="14" t="e">
         <f t="shared" si="11"/>
@@ -4360,7 +4374,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>71.428571428571431</v>
+        <v>75</v>
       </c>
       <c r="O16" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4467,35 +4481,35 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>1.9199999999999998E-2</v>
+        <v>2.5600000000000001E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
-        <v>10670</v>
+        <v>10770</v>
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>164.2</v>
+        <v>406.90000000000003</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>1.5388940955951265E-2</v>
+        <v>3.7780872794800371E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>10505.8</v>
+        <v>10363.1</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>500.27619047619044</v>
+        <v>518.15499999999997</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>1.7104166666666665</v>
+        <v>3.1789062500000003</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4548,7 +4562,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>22.142857142857142</v>
+        <v>23.25</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4604,7 +4618,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>22.238095238095237</v>
+        <v>23.35</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4660,7 +4674,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>22.095238095238095</v>
+        <v>23.2</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4716,7 +4730,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>22.523809523809526</v>
+        <v>23.65</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4772,7 +4786,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>23.047619047619047</v>
+        <v>24.2</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4828,7 +4842,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>112.04761904761905</v>
+        <v>117.65</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4885,7 +4899,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>29.333333333333332</v>
+        <v>30.8</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4941,7 +4955,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>26.952380952380953</v>
+        <v>28.3</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4997,7 +5011,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>27.333333333333332</v>
+        <v>28.7</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5053,7 +5067,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>29.142857142857142</v>
+        <v>30.6</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5109,7 +5123,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>112.76190476190476</v>
+        <v>118.4</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5138,35 +5152,35 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>5.4495412844036695E-2</v>
+        <v>6.0366972477064219E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
-        <v>15670</v>
+        <v>15770</v>
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>443.2</v>
+        <v>685.90000000000009</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>2.828334396936822E-2</v>
+        <v>4.3493975903614465E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>15226.8</v>
+        <v>15084.1</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>725.08571428571429</v>
+        <v>754.20500000000004</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>1.4922558922558922</v>
+        <v>2.0848024316109424</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADDF78DA-196F-443F-9ABF-2D4B76272341}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490C4719-6B6F-41DB-AC6C-919D8F0986C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1542,7 +1542,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1663,57 +1663,49 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.28000000000000003</v>
+        <v>0.18</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.47499999999999998</v>
+        <v>0.6</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.3571428571428572</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.6964285714285712</v>
-      </c>
-      <c r="O4" s="30">
-        <v>16</v>
-      </c>
-      <c r="P4" s="96">
-        <v>13</v>
-      </c>
-      <c r="Q4" s="32">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="O4" s="30"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="32" t="e">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.8125</v>
-      </c>
-      <c r="R4" s="30">
-        <v>12</v>
-      </c>
-      <c r="S4" s="96">
-        <v>7</v>
-      </c>
-      <c r="T4" s="32">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R4" s="30"/>
+      <c r="S4" s="96"/>
+      <c r="T4" s="32" t="e">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.58333333333333337</v>
-      </c>
-      <c r="U4" s="30">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U4" s="30" t="e">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>0.53846153846153844</v>
-      </c>
-      <c r="V4" s="33">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V4" s="33" t="e">
         <f t="shared" si="5"/>
-        <v>0.71794871794871795</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1740,57 +1732,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.22</v>
+        <v>0.06</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.36666666666666664</v>
+        <v>0.3</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>1.6666666666666665</v>
+        <v>5</v>
       </c>
       <c r="O5" s="30">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="P5" s="97">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0.8571428571428571</v>
+        <v>1</v>
       </c>
       <c r="R5" s="30">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="S5" s="97">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.9285714285714286</v>
+        <v>0.8</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>2.1666666666666665</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>1.0833333333333335</v>
+        <v>0.8</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1817,57 +1809,49 @@
         <v>50</v>
       </c>
       <c r="H6" s="12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
       <c r="K6" s="12">
-        <v>5</v>
+        <v>46</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.2</v>
+        <v>1.84</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>1</v>
+        <v>4.5999999999999996</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>2</v>
-      </c>
-      <c r="O6" s="30">
-        <v>7</v>
-      </c>
-      <c r="P6" s="97">
-        <v>7</v>
-      </c>
-      <c r="Q6" s="13">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="O6" s="30"/>
+      <c r="P6" s="97"/>
+      <c r="Q6" s="13" t="e">
         <f t="shared" si="3"/>
-        <v>1</v>
-      </c>
-      <c r="R6" s="30">
-        <v>8</v>
-      </c>
-      <c r="S6" s="97">
-        <v>8</v>
-      </c>
-      <c r="T6" s="13">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R6" s="30"/>
+      <c r="S6" s="97"/>
+      <c r="T6" s="13" t="e">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="U6" s="11">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U6" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>1.1428571428571428</v>
-      </c>
-      <c r="V6" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V6" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="W6" s="34"/>
     </row>
@@ -1893,58 +1877,54 @@
       <c r="G7" s="30">
         <v>50</v>
       </c>
-      <c r="H7" s="12">
-        <v>6</v>
-      </c>
+      <c r="H7" s="12"/>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
-      <c r="K7" s="12">
-        <v>7</v>
-      </c>
+      <c r="K7" s="12"/>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.23333333333333334</v>
-      </c>
-      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1.1666666666666667</v>
-      </c>
-      <c r="N7" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>1.9444444444444446</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O7" s="30">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="P7" s="97">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="R7" s="30">
+        <v>8</v>
+      </c>
+      <c r="S7" s="97">
         <v>3</v>
-      </c>
-      <c r="S7" s="97">
-        <v>0.3</v>
       </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>9.9999999999999992E-2</v>
+        <v>0.375</v>
       </c>
       <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>0.3</v>
+        <v>0.75</v>
       </c>
       <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>0.49999999999999994</v>
+        <v>0.75</v>
       </c>
       <c r="W7" s="34"/>
     </row>
@@ -2101,17 +2081,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2119,39 +2099,39 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>27</v>
+        <v>13.333333333333334</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P10" s="97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R10" s="30">
-        <v>115</v>
+        <v>280</v>
       </c>
       <c r="S10" s="97">
-        <v>114</v>
+        <v>268</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.99130434782608701</v>
+        <v>0.95714285714285718</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>22.8</v>
+        <v>44.666666666666664</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>0.99130434782608701</v>
+        <v>0.95714285714285718</v>
       </c>
       <c r="W10" s="34"/>
       <c r="AB10">
@@ -2553,11 +2533,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.104</v>
+        <v>8.2666666666666666E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2565,15 +2545,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>123</v>
+        <v>199</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.31948051948051948</v>
+        <v>0.51688311688311683</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>3.1538461538461537</v>
+        <v>6.419354838709677</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2581,31 +2561,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.8</v>
+        <v>0.76470588235294112</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>152</v>
+        <v>293</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>142.30000000000001</v>
+        <v>275</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.93618421052631584</v>
+        <v>0.93856655290102387</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>4.4468750000000004</v>
+        <v>21.153846153846153</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3482,11 +3462,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.8512396694214874E-2</v>
+        <v>5.586776859504132E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3494,15 +3474,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>290</v>
+        <v>366</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>0.11218568665377177</v>
+        <v>0.14158607350096711</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.6384180790960452</v>
+        <v>2.165680473372781</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3510,31 +3490,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>189</v>
+        <v>166</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>145</v>
+        <v>126</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.76719576719576721</v>
+        <v>0.75903614457831325</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>391</v>
+        <v>532</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>272.3</v>
+        <v>405</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.69641943734015344</v>
+        <v>0.76127819548872178</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.8779310344827587</v>
+        <v>3.2142857142857144</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3601,18 +3581,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.23076923076923078</v>
+        <v>0.30769230769230771</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F2" s="94">
-        <v>46240</v>
+        <v>46242</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3707,35 +3687,33 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>14+19+21+13</f>
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.11166666666666666</v>
+        <v>0.13500000000000001</v>
       </c>
       <c r="J4" s="30">
-        <v>575</v>
+        <v>550</v>
       </c>
       <c r="K4" s="8">
-        <f>21+22.7+22.5+7.4</f>
-        <v>73.600000000000009</v>
+        <v>92.42</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.128</v>
+        <v>0.16803636363636365</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>501.4</v>
+        <v>457.58</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>25.07</v>
+        <v>25.421111111111109</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.0985074626865672</v>
+        <v>1.1409876543209876</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3765,39 +3743,37 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>11+3+11+6</f>
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>5.1666666666666666E-2</v>
+        <v>5.8333333333333334E-2</v>
       </c>
       <c r="J5" s="11">
-        <v>550</v>
+        <v>450</v>
       </c>
       <c r="K5" s="12">
-        <f>20+5+19.9+13.1</f>
         <v>58</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.10545454545454545</v>
+        <v>0.12888888888888889</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>492</v>
+        <v>392</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>24.6</v>
+        <v>21.777777777777779</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.8709677419354838</v>
+        <v>1.6571428571428573</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>2.0410557184750733</v>
+        <v>2.2095238095238092</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3824,39 +3800,37 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>10+5+7</f>
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>3.6666666666666667E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <f>12+12.1+8.4</f>
-        <v>32.5</v>
+        <v>41.52</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>5.909090909090909E-2</v>
+        <v>7.5490909090909095E-2</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>517.5</v>
+        <v>508.48</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>25.875</v>
+        <v>28.248888888888889</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.4772727272727273</v>
+        <v>1.5377777777777779</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.6115702479338843</v>
+        <v>1.6775757575757577</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3882,34 +3856,38 @@
       <c r="G7" s="30">
         <v>600</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="12">
+        <v>5</v>
+      </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8.3333333333333332E-3</v>
       </c>
       <c r="J7" s="11">
-        <v>550</v>
-      </c>
-      <c r="K7" s="12"/>
+        <v>400</v>
+      </c>
+      <c r="K7" s="12">
+        <v>8.5500000000000007</v>
+      </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.1375000000000002E-2</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>550</v>
+        <v>391.45</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>27.5</v>
-      </c>
-      <c r="O7" s="72" t="e">
+        <v>21.74722222222222</v>
+      </c>
+      <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P7" s="14" t="e">
+        <v>1.7100000000000002</v>
+      </c>
+      <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>2.5650000000000004</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3954,7 +3932,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>28.75</v>
+        <v>31.944444444444443</v>
       </c>
       <c r="O8" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4007,7 +3985,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>27.5</v>
+        <v>30.555555555555557</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4042,39 +4020,37 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>2+5</f>
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>3.5000000000000003E-2</v>
+        <v>0.08</v>
       </c>
       <c r="J10" s="11">
-        <v>4620</v>
+        <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <f>29+113.8</f>
-        <v>142.80000000000001</v>
+        <v>462</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>3.090909090909091E-2</v>
+        <v>0.154</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>4477.2</v>
+        <v>2538</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>223.85999999999999</v>
+        <v>141</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>20.400000000000002</v>
+        <v>28.875</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>0.88311688311688308</v>
+        <v>1.925</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4119,7 +4095,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>32.5</v>
+        <v>36.111111111111114</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4172,7 +4148,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>27.5</v>
+        <v>30.555555555555557</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4374,7 +4350,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>75</v>
+        <v>83.333333333333329</v>
       </c>
       <c r="O16" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4481,35 +4457,35 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>2.5600000000000001E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
-        <v>10770</v>
+        <v>8875</v>
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>406.90000000000003</v>
+        <v>762.49</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>3.7780872794800371E-2</v>
+        <v>8.5914366197183095E-2</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>10363.1</v>
+        <v>8112.51</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>518.15499999999997</v>
+        <v>450.69499999999999</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.1789062500000003</v>
+        <v>4.6211515151515155</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4562,7 +4538,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>23.25</v>
+        <v>25.833333333333332</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4618,7 +4594,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>23.35</v>
+        <v>25.944444444444443</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4674,7 +4650,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>23.2</v>
+        <v>25.777777777777779</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4730,7 +4706,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>23.65</v>
+        <v>26.277777777777779</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4786,7 +4762,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>24.2</v>
+        <v>26.888888888888889</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4842,7 +4818,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>117.65</v>
+        <v>130.72222222222223</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4899,7 +4875,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>30.8</v>
+        <v>34.222222222222221</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4955,7 +4931,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>28.3</v>
+        <v>31.444444444444443</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5011,7 +4987,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>28.7</v>
+        <v>31.888888888888889</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5067,7 +5043,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>30.6</v>
+        <v>34</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5123,7 +5099,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>118.4</v>
+        <v>131.55555555555554</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5152,35 +5128,35 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>329</v>
+        <v>366</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>6.0366972477064219E-2</v>
+        <v>6.7155963302752295E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
-        <v>15770</v>
+        <v>13875</v>
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>685.90000000000009</v>
+        <v>1041.49</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>4.3493975903614465E-2</v>
+        <v>7.5062342342342339E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>15084.1</v>
+        <v>12833.51</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>754.20500000000004</v>
+        <v>712.97277777777776</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.0848024316109424</v>
+        <v>2.845601092896175</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{490C4719-6B6F-41DB-AC6C-919D8F0986C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FBCFDD-AE00-4932-88A7-E30DBAC1DF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="75">
   <si>
     <t>Booking</t>
   </si>
@@ -248,6 +248,9 @@
   </si>
   <si>
     <t xml:space="preserve">Umair </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jabran Iqbal </t>
   </si>
 </sst>
 </file>
@@ -1542,7 +1545,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1663,49 +1666,57 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.6</v>
+        <v>0.27500000000000002</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>2.6666666666666665</v>
+        <v>1</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="O4" s="30"/>
-      <c r="P4" s="96"/>
-      <c r="Q4" s="32" t="e">
+        <v>1.25</v>
+      </c>
+      <c r="O4" s="30">
+        <v>9</v>
+      </c>
+      <c r="P4" s="96">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R4" s="30"/>
-      <c r="S4" s="96"/>
-      <c r="T4" s="32" t="e">
+        <v>1</v>
+      </c>
+      <c r="R4" s="30">
+        <v>12</v>
+      </c>
+      <c r="S4" s="96">
+        <v>12</v>
+      </c>
+      <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" s="30" t="e">
+        <v>1</v>
+      </c>
+      <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" s="33" t="e">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1732,57 +1743,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.06</v>
+        <v>0.18</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>3</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>5</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="O5" s="30">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="P5" s="97">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R5" s="30">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="S5" s="97">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>1.3333333333333333</v>
+        <v>1.5</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1819,39 +1830,47 @@
         <v>25</v>
       </c>
       <c r="K6" s="12">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>1.84</v>
+        <v>0.48</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>4.5999999999999996</v>
+        <v>1.2</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="O6" s="30"/>
-      <c r="P6" s="97"/>
-      <c r="Q6" s="13" t="e">
+        <v>2.4</v>
+      </c>
+      <c r="O6" s="30">
+        <v>7</v>
+      </c>
+      <c r="P6" s="97">
+        <v>7</v>
+      </c>
+      <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R6" s="30"/>
-      <c r="S6" s="97"/>
-      <c r="T6" s="13" t="e">
+        <v>1</v>
+      </c>
+      <c r="R6" s="30">
+        <v>18</v>
+      </c>
+      <c r="S6" s="97">
+        <v>18</v>
+      </c>
+      <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" s="11" t="e">
+        <v>1</v>
+      </c>
+      <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V6" s="14" t="e">
+        <v>2.5714285714285716</v>
+      </c>
+      <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="W6" s="34"/>
     </row>
@@ -1877,54 +1896,58 @@
       <c r="G7" s="30">
         <v>50</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="12">
+        <v>1</v>
+      </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
-      <c r="K7" s="12"/>
+      <c r="K7" s="12">
+        <v>1</v>
+      </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="e">
+        <v>3.3333333333333333E-2</v>
+      </c>
+      <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="14" t="e">
+        <v>1</v>
+      </c>
+      <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>1.6666666666666665</v>
       </c>
       <c r="O7" s="30">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="P7" s="97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R7" s="30">
-        <v>8</v>
+        <v>7.95</v>
       </c>
       <c r="S7" s="97">
-        <v>3</v>
+        <v>7.65</v>
       </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>0.375</v>
+        <v>0.96226415094339623</v>
       </c>
       <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>0.75</v>
+        <v>1.53</v>
       </c>
       <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>0.75</v>
+        <v>0.96226415094339623</v>
       </c>
       <c r="W7" s="34"/>
     </row>
@@ -1945,51 +1968,63 @@
         <v>22</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G8" s="30">
         <v>50</v>
       </c>
-      <c r="H8" s="12"/>
+      <c r="H8" s="12">
+        <v>2</v>
+      </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
-      <c r="K8" s="12"/>
+      <c r="K8" s="12">
+        <v>2</v>
+      </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="e">
+        <v>0.1</v>
+      </c>
+      <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="14" t="e">
+        <v>1</v>
+      </c>
+      <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O8" s="30"/>
-      <c r="P8" s="97"/>
-      <c r="Q8" s="13" t="e">
+        <v>2.5</v>
+      </c>
+      <c r="O8" s="30">
+        <v>2</v>
+      </c>
+      <c r="P8" s="97">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R8" s="30"/>
-      <c r="S8" s="97"/>
-      <c r="T8" s="13" t="e">
+        <v>0.5</v>
+      </c>
+      <c r="R8" s="30">
+        <v>2</v>
+      </c>
+      <c r="S8" s="97">
+        <v>1.5</v>
+      </c>
+      <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U8" s="11" t="e">
+        <v>0.75</v>
+      </c>
+      <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V8" s="14" t="e">
+        <v>1.5</v>
+      </c>
+      <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1.5</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2081,17 +2116,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>120</v>
+        <v>98</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2099,39 +2134,39 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>13.333333333333334</v>
+        <v>9.8000000000000007</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="P10" s="97">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="R10" s="30">
-        <v>280</v>
+        <v>32</v>
       </c>
       <c r="S10" s="97">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.95714285714285718</v>
+        <v>0.65625</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>44.666666666666664</v>
+        <v>10.5</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>0.95714285714285718</v>
+        <v>0.65625</v>
       </c>
       <c r="W10" s="34"/>
       <c r="AB10">
@@ -2533,11 +2568,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>8.2666666666666666E-2</v>
+        <v>0.11466666666666667</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2545,15 +2580,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>199</v>
+        <v>130</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.51688311688311683</v>
+        <v>0.33766233766233766</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>6.419354838709677</v>
+        <v>3.0232558139534884</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2561,31 +2596,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.76470588235294112</v>
+        <v>0.96969696969696972</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>293</v>
+        <v>83.95</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>275</v>
+        <v>72.150000000000006</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.93856655290102387</v>
+        <v>0.85944014294222759</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>21.153846153846153</v>
+        <v>2.2546875000000002</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3462,11 +3497,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>169</v>
+        <v>181</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.586776859504132E-2</v>
+        <v>5.9834710743801652E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3474,15 +3509,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>366</v>
+        <v>297</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>0.14158607350096711</v>
+        <v>0.1148936170212766</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>2.165680473372781</v>
+        <v>1.6408839779005524</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3490,31 +3525,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.75903614457831325</v>
+        <v>0.79670329670329665</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>532</v>
+        <v>322.95</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>405</v>
+        <v>202.15</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.76127819548872178</v>
+        <v>0.62594828920885592</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>3.2142857142857144</v>
+        <v>1.3941379310344828</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3581,18 +3616,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.30769230769230771</v>
+        <v>0.42307692307692307</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F2" s="94">
-        <v>46242</v>
+        <v>46245</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3687,33 +3722,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <v>81</v>
+        <f>92+9</f>
+        <v>101</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.13500000000000001</v>
+        <v>0.16833333333333333</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>92.42</v>
+        <v>128</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.16803636363636365</v>
+        <v>0.23272727272727273</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>457.58</v>
+        <v>422</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>25.421111111111109</v>
+        <v>28.133333333333333</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1409876543209876</v>
+        <v>1.2673267326732673</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3743,37 +3779,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <v>35</v>
+        <f>38+8</f>
+        <v>46</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>5.8333333333333334E-2</v>
+        <v>7.6666666666666661E-2</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>58</v>
+        <v>86</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.12888888888888889</v>
+        <v>0.19111111111111112</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>392</v>
+        <v>364</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>21.777777777777779</v>
+        <v>24.266666666666666</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.6571428571428573</v>
+        <v>1.8695652173913044</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>2.2095238095238092</v>
+        <v>2.4927536231884062</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3800,37 +3837,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <v>27</v>
+        <f>32+7</f>
+        <v>39</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>4.4999999999999998E-2</v>
+        <v>6.5000000000000002E-2</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>41.52</v>
+        <v>106</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>7.5490909090909095E-2</v>
+        <v>0.19272727272727272</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>508.48</v>
+        <v>444</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>28.248888888888889</v>
+        <v>29.6</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.5377777777777779</v>
+        <v>2.7179487179487181</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>1.6775757575757577</v>
+        <v>2.965034965034965</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3857,37 +3895,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <v>5</v>
+        <f>5+5</f>
+        <v>10</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>8.3333333333333332E-3</v>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>8.5500000000000007</v>
+        <v>16</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>2.1375000000000002E-2</v>
+        <v>0.04</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>391.45</v>
+        <v>384</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>21.74722222222222</v>
+        <v>25.6</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.7100000000000002</v>
+        <v>1.6</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>2.5650000000000004</v>
+        <v>2.4</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3908,39 +3947,43 @@
         <v>22</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>26</v>
+        <v>74</v>
       </c>
       <c r="G8" s="30">
         <v>600</v>
       </c>
-      <c r="H8" s="12"/>
+      <c r="H8" s="12">
+        <v>2</v>
+      </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.3333333333333335E-3</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
-      <c r="K8" s="12"/>
+      <c r="K8" s="12">
+        <v>1.5</v>
+      </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>2.6086956521739132E-3</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>575</v>
+        <v>573.5</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>31.944444444444443</v>
-      </c>
-      <c r="O8" s="72" t="e">
+        <v>38.233333333333334</v>
+      </c>
+      <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P8" s="14" t="e">
+        <v>0.75</v>
+      </c>
+      <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0.78260869565217395</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -3985,7 +4028,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>30.555555555555557</v>
+        <v>36.666666666666664</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4020,37 +4063,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <v>16</v>
+        <f>22+2</f>
+        <v>24</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>462</v>
+        <v>567</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.154</v>
+        <v>0.189</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2538</v>
+        <v>2433</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>141</v>
+        <v>162.19999999999999</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>28.875</v>
+        <v>23.625</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.925</v>
+        <v>1.5750000000000002</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4095,7 +4139,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>36.111111111111114</v>
+        <v>43.333333333333336</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4148,7 +4192,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>30.555555555555557</v>
+        <v>36.666666666666664</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4350,7 +4394,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>83.333333333333329</v>
+        <v>100</v>
       </c>
       <c r="O16" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4457,11 +4501,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>3.3000000000000002E-2</v>
+        <v>4.4600000000000001E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4469,23 +4513,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>762.49</v>
+        <v>1004.5</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>8.5914366197183095E-2</v>
+        <v>0.11318309859154929</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>8112.51</v>
+        <v>7870.5</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>450.69499999999999</v>
+        <v>524.70000000000005</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>4.6211515151515155</v>
+        <v>4.5044843049327357</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4538,7 +4582,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>25.833333333333332</v>
+        <v>31</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4594,7 +4638,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>25.944444444444443</v>
+        <v>31.133333333333333</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4650,7 +4694,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>25.777777777777779</v>
+        <v>30.933333333333334</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4706,7 +4750,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>26.277777777777779</v>
+        <v>31.533333333333335</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4762,7 +4806,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>26.888888888888889</v>
+        <v>32.266666666666666</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4818,7 +4862,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>130.72222222222223</v>
+        <v>156.86666666666667</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4875,7 +4919,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>34.222222222222221</v>
+        <v>41.06666666666667</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4931,7 +4975,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>31.444444444444443</v>
+        <v>37.733333333333334</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -4987,7 +5031,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>31.888888888888889</v>
+        <v>38.266666666666666</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5043,7 +5087,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>34</v>
+        <v>40.799999999999997</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5099,7 +5143,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>131.55555555555554</v>
+        <v>157.86666666666667</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5128,11 +5172,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>366</v>
+        <v>424</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>6.7155963302752295E-2</v>
+        <v>7.7798165137614672E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5140,23 +5184,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1041.49</v>
+        <v>1283.5</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>7.5062342342342339E-2</v>
+        <v>9.2504504504504509E-2</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>12833.51</v>
+        <v>12591.5</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>712.97277777777776</v>
+        <v>839.43333333333328</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.845601092896175</v>
+        <v>3.0271226415094339</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{89FBCFDD-AE00-4932-88A7-E30DBAC1DF1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A70A6E-6F1A-4C07-91BB-BDE54463EAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1499,12 +1499,12 @@
   <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" customWidth="1"/>
+    <col min="5" max="5" width="17.453125" customWidth="1"/>
+    <col min="6" max="6" width="25.26953125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5.453125" style="24" customWidth="1"/>
     <col min="8" max="8" width="7.7265625" customWidth="1"/>
     <col min="9" max="9" width="5.54296875" customWidth="1"/>
@@ -1545,7 +1545,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1665,58 +1665,54 @@
       <c r="G4" s="30">
         <v>50</v>
       </c>
-      <c r="H4" s="8">
-        <v>11</v>
-      </c>
+      <c r="H4" s="8"/>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.22</v>
+        <v>0</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
-      <c r="K4" s="31">
-        <v>11</v>
-      </c>
+      <c r="K4" s="31"/>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.27500000000000002</v>
-      </c>
-      <c r="M4" s="30">
+        <v>0</v>
+      </c>
+      <c r="M4" s="30" t="e">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1</v>
-      </c>
-      <c r="N4" s="33">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N4" s="33" t="e">
         <f t="shared" si="2"/>
-        <v>1.25</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O4" s="30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="P4" s="96">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
         <v>1</v>
       </c>
       <c r="R4" s="30">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="S4" s="96">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.3333333333333333</v>
+        <v>0.4</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="W4" s="34"/>
     </row>
@@ -1742,30 +1738,26 @@
       <c r="G5" s="30">
         <v>50</v>
       </c>
-      <c r="H5" s="12">
-        <v>9</v>
-      </c>
+      <c r="H5" s="12"/>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
-      <c r="K5" s="12">
-        <v>6</v>
-      </c>
+      <c r="K5" s="12"/>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.2</v>
-      </c>
-      <c r="M5" s="11">
+        <v>0</v>
+      </c>
+      <c r="M5" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="N5" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N5" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>1.1111111111111112</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O5" s="30">
         <v>8</v>
@@ -1778,22 +1770,22 @@
         <v>1</v>
       </c>
       <c r="R5" s="30">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="S5" s="97">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>0.75</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1819,58 +1811,54 @@
       <c r="G6" s="30">
         <v>50</v>
       </c>
-      <c r="H6" s="12">
-        <v>10</v>
-      </c>
+      <c r="H6" s="12"/>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
-      <c r="K6" s="12">
-        <v>12</v>
-      </c>
+      <c r="K6" s="12"/>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.48</v>
-      </c>
-      <c r="M6" s="11">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1.2</v>
-      </c>
-      <c r="N6" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N6" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>2.4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O6" s="30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="P6" s="97">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R6" s="30">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="S6" s="97">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>2.5714285714285716</v>
+        <v>1.3333333333333333</v>
       </c>
       <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.0666666666666667</v>
       </c>
       <c r="W6" s="34"/>
     </row>
@@ -1896,58 +1884,54 @@
       <c r="G7" s="30">
         <v>50</v>
       </c>
-      <c r="H7" s="12">
-        <v>1</v>
-      </c>
+      <c r="H7" s="12"/>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
-      <c r="K7" s="12">
-        <v>1</v>
-      </c>
+      <c r="K7" s="12"/>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>3.3333333333333333E-2</v>
-      </c>
-      <c r="M7" s="11">
+        <v>0</v>
+      </c>
+      <c r="M7" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N7" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N7" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>1.6666666666666665</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O7" s="30">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="P7" s="97">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R7" s="30">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="S7" s="97">
-        <v>7.65</v>
+        <v>6</v>
       </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>0.96226415094339623</v>
+        <v>0.75</v>
       </c>
       <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>1.53</v>
+        <v>1</v>
       </c>
       <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>0.96226415094339623</v>
+        <v>1.125</v>
       </c>
       <c r="W7" s="34"/>
     </row>
@@ -1973,58 +1957,54 @@
       <c r="G8" s="30">
         <v>50</v>
       </c>
-      <c r="H8" s="12">
-        <v>2</v>
-      </c>
+      <c r="H8" s="12"/>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
-      <c r="K8" s="12">
-        <v>2</v>
-      </c>
+      <c r="K8" s="12"/>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="M8" s="11">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N8" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="14" t="e">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O8" s="30">
+        <v>3</v>
+      </c>
+      <c r="P8" s="97">
         <v>2</v>
-      </c>
-      <c r="P8" s="97">
-        <v>1</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="R8" s="30">
+        <v>3</v>
+      </c>
+      <c r="S8" s="97">
         <v>2</v>
-      </c>
-      <c r="S8" s="97">
-        <v>1.5</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.75</v>
+        <v>0.66666666666666663</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2115,58 +2095,54 @@
       <c r="G10" s="30">
         <v>25</v>
       </c>
-      <c r="H10" s="12">
-        <v>10</v>
-      </c>
+      <c r="H10" s="12"/>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
-      <c r="K10" s="12">
-        <v>98</v>
-      </c>
+      <c r="K10" s="12"/>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M10" s="11">
+      <c r="M10" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>9.8000000000000007</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P10" s="97">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="R10" s="30">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="S10" s="97">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>0.65625</v>
+        <v>0.76666666666666672</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>10.5</v>
+        <v>7.666666666666667</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>0.65625</v>
+        <v>1.0222222222222224</v>
       </c>
       <c r="W10" s="34"/>
       <c r="AB10">
@@ -2568,11 +2544,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.11466666666666667</v>
+        <v>0</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2580,15 +2556,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.33766233766233766</v>
-      </c>
-      <c r="M19" s="40">
+        <v>0</v>
+      </c>
+      <c r="M19" s="40" t="e">
         <f>K19/H19</f>
-        <v>3.0232558139534884</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2596,31 +2572,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>33</v>
+        <v>42</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.96969696969696972</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>83.95</v>
+        <v>66</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>72.150000000000006</v>
+        <v>49</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.85944014294222759</v>
+        <v>0.74242424242424243</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>2.2546875000000002</v>
+        <v>1.4</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3497,11 +3473,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>181</v>
+        <v>138</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.9834710743801652E-2</v>
+        <v>4.5619834710743802E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3509,15 +3485,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>297</v>
+        <v>167</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>0.1148936170212766</v>
+        <v>6.4603481624758222E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.6408839779005524</v>
+        <v>1.2101449275362319</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3525,31 +3501,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.79670329670329665</v>
+        <v>0.77486910994764402</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>322.95</v>
+        <v>305</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>202.15</v>
+        <v>179</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.62594828920885592</v>
+        <v>0.58688524590163937</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.3941379310344828</v>
+        <v>1.2094594594594594</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3583,7 +3559,7 @@
     <col min="3" max="3" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.26953125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="26" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="5" style="24" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="7.1796875" bestFit="1" customWidth="1"/>
@@ -3616,18 +3592,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.42307692307692307</v>
+        <v>0.5</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F2" s="94">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3722,34 +3698,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9</f>
-        <v>101</v>
+        <f>92+9+11+10</f>
+        <v>122</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.16833333333333333</v>
+        <v>0.20333333333333334</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.23272727272727273</v>
+        <v>0.25636363636363635</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>28.133333333333333</v>
+        <v>31.46153846153846</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.2673267326732673</v>
+        <v>1.1557377049180328</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3779,38 +3755,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8</f>
-        <v>46</v>
+        <f>38+8+5+8</f>
+        <v>59</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>7.6666666666666661E-2</v>
+        <v>9.8333333333333328E-2</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.19111111111111112</v>
+        <v>0.21555555555555556</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>24.266666666666666</v>
+        <v>27.153846153846153</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.8695652173913044</v>
+        <v>1.6440677966101696</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>2.4927536231884062</v>
+        <v>2.1920903954802262</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3837,38 +3813,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7</f>
-        <v>39</v>
+        <f>32+7+9+6</f>
+        <v>54</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>6.5000000000000002E-2</v>
+        <v>0.09</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.19272727272727272</v>
+        <v>0.22545454545454546</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>444</v>
+        <v>426</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>29.6</v>
+        <v>32.769230769230766</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>2.7179487179487181</v>
+        <v>2.2962962962962963</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.965034965034965</v>
+        <v>2.5050505050505052</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3895,38 +3871,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5</f>
-        <v>10</v>
+        <f>5+5+1+6</f>
+        <v>17</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>1.6666666666666666E-2</v>
+        <v>2.8333333333333332E-2</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>25.6</v>
+        <v>28.923076923076923</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.6</v>
+        <v>1.411764705882353</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>2.4</v>
+        <v>2.1176470588235294</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3953,37 +3929,37 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
+        <v>6.6666666666666671E-3</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>2.6086956521739132E-3</v>
+        <v>8.6956521739130436E-3</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>573.5</v>
+        <v>570</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>38.233333333333334</v>
+        <v>43.846153846153847</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>0.75</v>
+        <v>1.25</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>0.78260869565217395</v>
+        <v>1.3043478260869565</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4028,7 +4004,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>36.666666666666664</v>
+        <v>42.307692307692307</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4063,38 +4039,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2</f>
-        <v>24</v>
+        <f>22+2+7+3</f>
+        <v>34</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>567</v>
+        <v>664</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.189</v>
+        <v>0.22133333333333333</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2433</v>
+        <v>2336</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>162.19999999999999</v>
+        <v>179.69230769230768</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>23.625</v>
+        <v>19.529411764705884</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.5750000000000002</v>
+        <v>1.3019607843137253</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4139,7 +4115,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>43.333333333333336</v>
+        <v>50</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4192,7 +4168,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>36.666666666666664</v>
+        <v>42.307692307692307</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4278,23 +4254,21 @@
         <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="J14" s="11">
-        <v>100</v>
-      </c>
+      <c r="J14" s="11"/>
       <c r="K14" s="12">
         <v>100</v>
       </c>
-      <c r="L14" s="71">
+      <c r="L14" s="71" t="e">
         <f t="shared" si="8"/>
-        <v>1</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="M14" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>-7.6923076923076925</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4375,30 +4349,32 @@
         <v>64</v>
       </c>
       <c r="G16" s="11"/>
-      <c r="H16" s="12"/>
+      <c r="H16" s="12">
+        <v>1</v>
+      </c>
       <c r="I16" s="70" t="e">
         <f t="shared" ref="I16" si="12">H16/G16</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="J16" s="11">
-        <v>1500</v>
-      </c>
-      <c r="K16" s="12"/>
-      <c r="L16" s="71">
+      <c r="J16" s="11"/>
+      <c r="K16" s="12">
+        <v>450</v>
+      </c>
+      <c r="L16" s="71" t="e">
         <f t="shared" si="8"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="M16" s="12">
         <f t="shared" si="5"/>
-        <v>1500</v>
+        <v>-450</v>
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
-      <c r="O16" s="72" t="e">
+        <v>-34.615384615384613</v>
+      </c>
+      <c r="O16" s="72">
         <f t="shared" si="10"/>
-        <v>#DIV/0!</v>
+        <v>450</v>
       </c>
       <c r="P16" s="14" t="e">
         <f t="shared" si="11"/>
@@ -4501,35 +4477,35 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>223</v>
+        <v>292</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>4.4600000000000001E-2</v>
+        <v>5.8400000000000001E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
-        <v>8875</v>
+        <v>7275</v>
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>1004.5</v>
+        <v>1605</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.11318309859154929</v>
+        <v>0.22061855670103092</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>7870.5</v>
+        <v>5670</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>524.70000000000005</v>
+        <v>436.15384615384613</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>4.5044843049327357</v>
+        <v>5.4965753424657535</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4582,7 +4558,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>31</v>
+        <v>35.769230769230766</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4638,7 +4614,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>31.133333333333333</v>
+        <v>35.92307692307692</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4694,7 +4670,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>30.933333333333334</v>
+        <v>35.692307692307693</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4750,7 +4726,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>31.533333333333335</v>
+        <v>36.384615384615387</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4806,7 +4782,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>32.266666666666666</v>
+        <v>37.230769230769234</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4862,7 +4838,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>156.86666666666667</v>
+        <v>181</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4919,7 +4895,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>41.06666666666667</v>
+        <v>47.384615384615387</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4975,7 +4951,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>37.733333333333334</v>
+        <v>43.53846153846154</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5031,7 +5007,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>38.266666666666666</v>
+        <v>44.153846153846153</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5087,7 +5063,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>40.799999999999997</v>
+        <v>47.07692307692308</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5143,7 +5119,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>157.86666666666667</v>
+        <v>182.15384615384616</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5172,35 +5148,35 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>424</v>
+        <v>493</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>7.7798165137614672E-2</v>
+        <v>9.0458715596330272E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
-        <v>13875</v>
+        <v>12275</v>
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1283.5</v>
+        <v>1884</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>9.2504504504504509E-2</v>
+        <v>0.15348268839103871</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>12591.5</v>
+        <v>10391</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>839.43333333333328</v>
+        <v>799.30769230769226</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.0271226415094339</v>
+        <v>3.8215010141987831</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58A70A6E-6F1A-4C07-91BB-BDE54463EAF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412B7D61-086A-47E6-A0FE-FF4BB8C4C721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1665,26 +1665,30 @@
       <c r="G4" s="30">
         <v>50</v>
       </c>
-      <c r="H4" s="8"/>
+      <c r="H4" s="8">
+        <v>10</v>
+      </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
-      <c r="K4" s="31"/>
+      <c r="K4" s="31">
+        <v>12</v>
+      </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0</v>
-      </c>
-      <c r="M4" s="30" t="e">
+        <v>0.3</v>
+      </c>
+      <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N4" s="33" t="e">
+        <v>1.2</v>
+      </c>
+      <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>1.4999999999999998</v>
       </c>
       <c r="O4" s="30">
         <v>10</v>
@@ -1738,26 +1742,30 @@
       <c r="G5" s="30">
         <v>50</v>
       </c>
-      <c r="H5" s="12"/>
+      <c r="H5" s="12">
+        <v>13</v>
+      </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
-      <c r="K5" s="12"/>
+      <c r="K5" s="12">
+        <v>14</v>
+      </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M5" s="11" t="e">
+        <v>0.46666666666666667</v>
+      </c>
+      <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N5" s="14" t="e">
+        <v>1.0769230769230769</v>
+      </c>
+      <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>1.7948717948717949</v>
       </c>
       <c r="O5" s="30">
         <v>8</v>
@@ -1811,26 +1819,30 @@
       <c r="G6" s="30">
         <v>50</v>
       </c>
-      <c r="H6" s="12"/>
+      <c r="H6" s="12">
+        <v>10</v>
+      </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
-      <c r="K6" s="12"/>
+      <c r="K6" s="12">
+        <v>13</v>
+      </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M6" s="11" t="e">
+        <v>0.52</v>
+      </c>
+      <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N6" s="14" t="e">
+        <v>1.3</v>
+      </c>
+      <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>2.6</v>
       </c>
       <c r="O6" s="30">
         <v>8</v>
@@ -1884,26 +1896,30 @@
       <c r="G7" s="30">
         <v>50</v>
       </c>
-      <c r="H7" s="12"/>
+      <c r="H7" s="12">
+        <v>3</v>
+      </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
-      <c r="K7" s="12"/>
+      <c r="K7" s="12">
+        <v>4</v>
+      </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M7" s="11" t="e">
+        <v>0.13333333333333333</v>
+      </c>
+      <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N7" s="14" t="e">
+        <v>1.3333333333333333</v>
+      </c>
+      <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>2.2222222222222223</v>
       </c>
       <c r="O7" s="30">
         <v>9</v>
@@ -1957,26 +1973,30 @@
       <c r="G8" s="30">
         <v>50</v>
       </c>
-      <c r="H8" s="12"/>
+      <c r="H8" s="12">
+        <v>8</v>
+      </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.16</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
-      <c r="K8" s="12"/>
+      <c r="K8" s="12">
+        <v>8</v>
+      </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="e">
+        <v>0.4</v>
+      </c>
+      <c r="M8" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="14" t="e">
+        <v>1</v>
+      </c>
+      <c r="N8" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>2.5</v>
       </c>
       <c r="O8" s="30">
         <v>3</v>
@@ -2030,7 +2050,9 @@
       <c r="G9" s="30">
         <v>0</v>
       </c>
-      <c r="H9" s="12"/>
+      <c r="H9" s="12">
+        <v>3</v>
+      </c>
       <c r="I9" s="13" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2038,14 +2060,16 @@
       <c r="J9" s="30">
         <v>20</v>
       </c>
-      <c r="K9" s="12"/>
+      <c r="K9" s="12">
+        <v>49</v>
+      </c>
       <c r="L9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="11" t="e">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="M9" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>16.333333333333332</v>
       </c>
       <c r="N9" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2544,11 +2568,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.12533333333333332</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2556,15 +2580,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0</v>
-      </c>
-      <c r="M19" s="40" t="e">
+        <v>0.25974025974025972</v>
+      </c>
+      <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>#DIV/0!</v>
+        <v>2.1276595744680851</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -3473,11 +3497,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>4.5619834710743802E-2</v>
+        <v>6.1157024793388429E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3485,15 +3509,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>167</v>
+        <v>267</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>6.4603481624758222E-2</v>
+        <v>0.10328820116054159</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.2101449275362319</v>
+        <v>1.4432432432432432</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412B7D61-086A-47E6-A0FE-FF4BB8C4C721}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBA9ECE-3109-4737-BA85-B11228776845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="367" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="77">
   <si>
     <t>Booking</t>
   </si>
@@ -251,6 +251,12 @@
   </si>
   <si>
     <t xml:space="preserve">Jabran Iqbal </t>
+  </si>
+  <si>
+    <t>Pending Supply</t>
+  </si>
+  <si>
+    <t>Furqan</t>
   </si>
 </sst>
 </file>
@@ -1545,7 +1551,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1666,59 +1672,53 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>1.2</v>
+        <v>2.6666666666666665</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>1.4999999999999998</v>
-      </c>
-      <c r="O4" s="30">
-        <v>10</v>
-      </c>
-      <c r="P4" s="96">
-        <v>10</v>
-      </c>
-      <c r="Q4" s="32">
+        <v>3.3333333333333335</v>
+      </c>
+      <c r="O4" s="30"/>
+      <c r="P4" s="96"/>
+      <c r="Q4" s="32" t="e">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>1</v>
-      </c>
-      <c r="R4" s="30">
-        <v>8</v>
-      </c>
-      <c r="S4" s="96">
-        <v>4</v>
-      </c>
-      <c r="T4" s="32">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R4" s="30"/>
+      <c r="S4" s="96"/>
+      <c r="T4" s="32" t="e">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>0.5</v>
-      </c>
-      <c r="U4" s="30">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U4" s="30" t="e">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>0.4</v>
-      </c>
-      <c r="V4" s="33">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V4" s="33" t="e">
         <f t="shared" si="5"/>
-        <v>0.5</v>
-      </c>
-      <c r="W4" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W4" s="34" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="5" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
@@ -1743,57 +1743,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.18</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.46666666666666667</v>
+        <v>0.26666666666666666</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.0769230769230769</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>1.7948717948717949</v>
+        <v>1.4814814814814816</v>
       </c>
       <c r="O5" s="30">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="P5" s="97">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.38461538461538464</v>
       </c>
       <c r="R5" s="30">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="S5" s="97">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.8571428571428571</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>0.75</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>0.8571428571428571</v>
+        <v>2.0428571428571427</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1820,211 +1820,201 @@
         <v>50</v>
       </c>
       <c r="H6" s="12">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
       <c r="K6" s="12">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.52</v>
+        <v>0.44</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>1.3</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>2.6</v>
-      </c>
-      <c r="O6" s="30">
-        <v>8</v>
-      </c>
-      <c r="P6" s="97">
-        <v>6</v>
-      </c>
-      <c r="Q6" s="13">
+        <v>4.3999999999999995</v>
+      </c>
+      <c r="O6" s="30"/>
+      <c r="P6" s="97"/>
+      <c r="Q6" s="13" t="e">
         <f t="shared" si="3"/>
-        <v>0.75</v>
-      </c>
-      <c r="R6" s="30">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R6" s="30"/>
+      <c r="S6" s="97"/>
+      <c r="T6" s="13" t="e">
+        <f t="shared" si="4"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U6" s="11" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V6" s="14" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W6" s="34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A7" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="G7" s="30">
+        <v>50</v>
+      </c>
+      <c r="H7" s="12">
+        <v>4</v>
+      </c>
+      <c r="I7" s="13">
+        <f t="shared" si="0"/>
+        <v>0.08</v>
+      </c>
+      <c r="J7" s="30">
+        <v>30</v>
+      </c>
+      <c r="K7" s="12">
         <v>10</v>
       </c>
-      <c r="S6" s="97">
-        <v>8</v>
-      </c>
-      <c r="T6" s="13">
+      <c r="L7" s="13">
+        <f t="shared" si="1"/>
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="M7" s="11">
+        <f t="shared" si="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="N7" s="14">
+        <f t="shared" si="2"/>
+        <v>4.1666666666666661</v>
+      </c>
+      <c r="O7" s="30">
+        <v>3</v>
+      </c>
+      <c r="P7" s="97">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="13">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
+      <c r="R7" s="30">
+        <v>4</v>
+      </c>
+      <c r="S7" s="97">
+        <v>4</v>
+      </c>
+      <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>0.8</v>
-      </c>
-      <c r="U6" s="11">
+        <v>1</v>
+      </c>
+      <c r="U7" s="11">
         <f t="shared" si="5"/>
         <v>1.3333333333333333</v>
       </c>
-      <c r="V6" s="14">
+      <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>1.0666666666666667</v>
-      </c>
-      <c r="W6" s="34"/>
-    </row>
-    <row r="7" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A7" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="34"/>
+    </row>
+    <row r="8" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A8" s="35" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="E7" s="16" t="s">
+      <c r="E8" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="G7" s="30">
+      <c r="F8" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="G8" s="30">
         <v>50</v>
       </c>
-      <c r="H7" s="12">
-        <v>3</v>
-      </c>
-      <c r="I7" s="13">
+      <c r="H8" s="12"/>
+      <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0.06</v>
-      </c>
-      <c r="J7" s="30">
-        <v>30</v>
-      </c>
-      <c r="K7" s="12">
+        <v>0</v>
+      </c>
+      <c r="J8" s="30">
+        <v>20</v>
+      </c>
+      <c r="K8" s="12"/>
+      <c r="L8" s="13">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N8" s="14" t="e">
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O8" s="30">
+        <v>8</v>
+      </c>
+      <c r="P8" s="97">
         <v>4</v>
       </c>
-      <c r="L7" s="13">
-        <f t="shared" si="1"/>
-        <v>0.13333333333333333</v>
-      </c>
-      <c r="M7" s="11">
-        <f t="shared" si="2"/>
-        <v>1.3333333333333333</v>
-      </c>
-      <c r="N7" s="14">
-        <f t="shared" si="2"/>
-        <v>2.2222222222222223</v>
-      </c>
-      <c r="O7" s="30">
-        <v>9</v>
-      </c>
-      <c r="P7" s="97">
+      <c r="Q8" s="13">
+        <f t="shared" si="3"/>
+        <v>0.5</v>
+      </c>
+      <c r="R8" s="30">
+        <v>8</v>
+      </c>
+      <c r="S8" s="97">
         <v>6</v>
       </c>
-      <c r="Q7" s="13">
-        <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="R7" s="30">
-        <v>8</v>
-      </c>
-      <c r="S7" s="97">
-        <v>6</v>
-      </c>
-      <c r="T7" s="13">
+      <c r="T8" s="13">
         <f t="shared" si="4"/>
         <v>0.75</v>
       </c>
-      <c r="U7" s="11">
-        <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="V7" s="14">
-        <f t="shared" si="5"/>
-        <v>1.125</v>
-      </c>
-      <c r="W7" s="34"/>
-    </row>
-    <row r="8" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A8" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="C8" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="D8" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="17" t="s">
-        <v>74</v>
-      </c>
-      <c r="G8" s="30">
-        <v>50</v>
-      </c>
-      <c r="H8" s="12">
-        <v>8</v>
-      </c>
-      <c r="I8" s="13">
-        <f t="shared" si="0"/>
-        <v>0.16</v>
-      </c>
-      <c r="J8" s="30">
-        <v>20</v>
-      </c>
-      <c r="K8" s="12">
-        <v>8</v>
-      </c>
-      <c r="L8" s="13">
-        <f t="shared" si="1"/>
-        <v>0.4</v>
-      </c>
-      <c r="M8" s="11">
-        <f t="shared" si="2"/>
-        <v>1</v>
-      </c>
-      <c r="N8" s="14">
-        <f t="shared" si="2"/>
-        <v>2.5</v>
-      </c>
-      <c r="O8" s="30">
-        <v>3</v>
-      </c>
-      <c r="P8" s="97">
-        <v>2</v>
-      </c>
-      <c r="Q8" s="13">
-        <f t="shared" si="3"/>
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="R8" s="30">
-        <v>3</v>
-      </c>
-      <c r="S8" s="97">
-        <v>2</v>
-      </c>
-      <c r="T8" s="13">
-        <f t="shared" si="4"/>
-        <v>0.66666666666666663</v>
-      </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="W8" s="34"/>
     </row>
@@ -2045,13 +2035,13 @@
         <v>22</v>
       </c>
       <c r="F9" s="95" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="G9" s="30">
         <v>0</v>
       </c>
       <c r="H9" s="12">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I9" s="13" t="e">
         <f t="shared" si="0"/>
@@ -2061,15 +2051,15 @@
         <v>20</v>
       </c>
       <c r="K9" s="12">
-        <v>49</v>
+        <v>2</v>
       </c>
       <c r="L9" s="13">
         <f t="shared" si="1"/>
-        <v>2.4500000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="M9" s="11">
         <f t="shared" si="2"/>
-        <v>16.333333333333332</v>
+        <v>0.4</v>
       </c>
       <c r="N9" s="14" t="e">
         <f t="shared" si="2"/>
@@ -2140,35 +2130,29 @@
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O10" s="30">
-        <v>4</v>
-      </c>
-      <c r="P10" s="97">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="13">
+      <c r="O10" s="30"/>
+      <c r="P10" s="97"/>
+      <c r="Q10" s="13" t="e">
         <f t="shared" si="3"/>
-        <v>0.75</v>
-      </c>
-      <c r="R10" s="30">
-        <v>30</v>
-      </c>
-      <c r="S10" s="97">
-        <v>23</v>
-      </c>
-      <c r="T10" s="13">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R10" s="30"/>
+      <c r="S10" s="97"/>
+      <c r="T10" s="13" t="e">
         <f t="shared" si="4"/>
-        <v>0.76666666666666672</v>
-      </c>
-      <c r="U10" s="11">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="U10" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>7.666666666666667</v>
-      </c>
-      <c r="V10" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V10" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>1.0222222222222224</v>
-      </c>
-      <c r="W10" s="34"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W10" s="34" t="s">
+        <v>75</v>
+      </c>
       <c r="AB10">
         <v>33</v>
       </c>
@@ -2568,11 +2552,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.12533333333333332</v>
+        <v>8.533333333333333E-2</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2580,15 +2564,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.25974025974025972</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>2.1276595744680851</v>
+        <v>1.71875</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2596,31 +2580,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.83333333333333337</v>
+        <v>0.5</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>66</v>
+        <v>26</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.74242424242424243</v>
+        <v>0.80769230769230771</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3497,11 +3481,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>6.1157024793388429E-2</v>
+        <v>5.6198347107438019E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3509,15 +3493,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>267</v>
+        <v>222</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>0.10328820116054159</v>
+        <v>8.5880077369439076E-2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.4432432432432432</v>
+        <v>1.3058823529411765</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3525,31 +3509,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>191</v>
+        <v>173</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.77486910994764402</v>
+        <v>0.7225433526011561</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>305</v>
+        <v>265</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.58688524590163937</v>
+        <v>0.56981132075471697</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.2094594594594594</v>
+        <v>1.208</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3616,18 +3600,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.5</v>
+        <v>0.57692307692307687</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F2" s="94">
-        <v>46247</v>
+        <v>46249</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3722,12 +3706,12 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10</f>
-        <v>122</v>
+        <f>92+9+11+10+6</f>
+        <v>128</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.20333333333333334</v>
+        <v>0.21333333333333335</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
@@ -3745,11 +3729,11 @@
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>31.46153846153846</v>
+        <v>37.18181818181818</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1557377049180328</v>
+        <v>1.1015625</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3779,38 +3763,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8</f>
-        <v>59</v>
+        <f>38+8+5+8+8</f>
+        <v>67</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>9.8333333333333328E-2</v>
+        <v>0.11166666666666666</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.21555555555555556</v>
+        <v>0.24</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>27.153846153846153</v>
+        <v>31.09090909090909</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.6440677966101696</v>
+        <v>1.6119402985074627</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>2.1920903954802262</v>
+        <v>2.1492537313432836</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3860,7 +3844,7 @@
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>32.769230769230766</v>
+        <v>38.727272727272727</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
@@ -3895,38 +3879,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6</f>
-        <v>17</v>
+        <f>5+5+1+6+5</f>
+        <v>22</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>2.8333333333333332E-2</v>
+        <v>3.6666666666666667E-2</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.06</v>
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>28.923076923076923</v>
+        <v>33.81818181818182</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.411764705882353</v>
+        <v>1.2727272727272727</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>2.1176470588235294</v>
+        <v>1.9090909090909092</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3963,27 +3947,27 @@
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>8.6956521739130436E-3</v>
+        <v>1.9130434782608695E-2</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>43.846153846153847</v>
+        <v>51.272727272727273</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.25</v>
+        <v>2.75</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.3043478260869565</v>
+        <v>2.8695652173913042</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4028,7 +4012,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>42.307692307692307</v>
+        <v>50</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4063,38 +4047,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3</f>
-        <v>34</v>
+        <f>22+2+7+3+7</f>
+        <v>41</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.17</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>664</v>
+        <v>724</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.22133333333333333</v>
+        <v>0.24133333333333334</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2336</v>
+        <v>2276</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>179.69230769230768</v>
+        <v>206.90909090909091</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>19.529411764705884</v>
+        <v>17.658536585365855</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.3019607843137253</v>
+        <v>1.1772357723577238</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4139,7 +4123,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>50</v>
+        <v>59.090909090909093</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4192,7 +4176,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>42.307692307692307</v>
+        <v>50</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4292,7 +4276,7 @@
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>-7.6923076923076925</v>
+        <v>-9.0909090909090917</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4382,7 +4366,7 @@
       </c>
       <c r="J16" s="11"/>
       <c r="K16" s="12">
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="L16" s="71" t="e">
         <f t="shared" si="8"/>
@@ -4390,15 +4374,15 @@
       </c>
       <c r="M16" s="12">
         <f t="shared" si="5"/>
-        <v>-450</v>
+        <v>-500</v>
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>-34.615384615384613</v>
+        <v>-45.454545454545453</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
-        <v>450</v>
+        <v>500</v>
       </c>
       <c r="P16" s="14" t="e">
         <f t="shared" si="11"/>
@@ -4501,11 +4485,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>292</v>
+        <v>318</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>5.8400000000000001E-2</v>
+        <v>6.3600000000000004E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4513,23 +4497,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>1605</v>
+        <v>1736</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.22061855670103092</v>
+        <v>0.2386254295532646</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>5670</v>
+        <v>5539</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>436.15384615384613</v>
+        <v>503.54545454545456</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>5.4965753424657535</v>
+        <v>5.4591194968553456</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4582,7 +4566,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>35.769230769230766</v>
+        <v>42.272727272727273</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4638,7 +4622,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>35.92307692307692</v>
+        <v>42.454545454545453</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4694,7 +4678,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>35.692307692307693</v>
+        <v>42.18181818181818</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4750,7 +4734,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>36.384615384615387</v>
+        <v>43</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4806,7 +4790,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>37.230769230769234</v>
+        <v>44</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4862,7 +4846,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>181</v>
+        <v>213.90909090909091</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4919,7 +4903,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>47.384615384615387</v>
+        <v>56</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4975,7 +4959,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>43.53846153846154</v>
+        <v>51.454545454545453</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5031,7 +5015,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>44.153846153846153</v>
+        <v>52.18181818181818</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5087,7 +5071,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>47.07692307692308</v>
+        <v>55.636363636363633</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5143,7 +5127,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>182.15384615384616</v>
+        <v>215.27272727272728</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5172,11 +5156,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>493</v>
+        <v>519</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>9.0458715596330272E-2</v>
+        <v>9.5229357798165132E-2</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5184,23 +5168,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>1884</v>
+        <v>2015</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.15348268839103871</v>
+        <v>0.16415478615071283</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>10391</v>
+        <v>10260</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>799.30769230769226</v>
+        <v>932.72727272727275</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.8215010141987831</v>
+        <v>3.882466281310212</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEBA9ECE-3109-4737-BA85-B11228776845}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332E3393-C39A-4147-A935-E77158C1EDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="79">
   <si>
     <t>Booking</t>
   </si>
@@ -257,6 +257,12 @@
   </si>
   <si>
     <t>Furqan</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Both delivered </t>
+  </si>
+  <si>
+    <t>Pending Delivered</t>
   </si>
 </sst>
 </file>
@@ -1551,7 +1557,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1672,52 +1678,60 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.18</v>
+        <v>0.32</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>2.6666666666666665</v>
+        <v>0.75</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>3.3333333333333335</v>
-      </c>
-      <c r="O4" s="30"/>
-      <c r="P4" s="96"/>
-      <c r="Q4" s="32" t="e">
+        <v>0.9375</v>
+      </c>
+      <c r="O4" s="30">
+        <v>15</v>
+      </c>
+      <c r="P4" s="96">
+        <v>9</v>
+      </c>
+      <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R4" s="30"/>
-      <c r="S4" s="96"/>
-      <c r="T4" s="32" t="e">
+        <v>0.6</v>
+      </c>
+      <c r="R4" s="30">
+        <v>16</v>
+      </c>
+      <c r="S4" s="96">
+        <v>13</v>
+      </c>
+      <c r="T4" s="32">
         <f t="shared" ref="T4:T12" si="4">S4/R4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U4" s="30" t="e">
+        <v>0.8125</v>
+      </c>
+      <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V4" s="33" t="e">
+        <v>1.4444444444444444</v>
+      </c>
+      <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1.3541666666666667</v>
       </c>
       <c r="W4" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -1743,57 +1757,57 @@
         <v>50</v>
       </c>
       <c r="H5" s="12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.2</v>
       </c>
       <c r="J5" s="30">
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.26666666666666666</v>
+        <v>0.36666666666666664</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>0.88888888888888884</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>1.4814814814814816</v>
+        <v>1.833333333333333</v>
       </c>
       <c r="O5" s="30">
         <v>13</v>
       </c>
       <c r="P5" s="97">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0.38461538461538464</v>
+        <v>0.69230769230769229</v>
       </c>
       <c r="R5" s="30">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="S5" s="97">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="T5" s="13">
         <f t="shared" si="4"/>
-        <v>0.7857142857142857</v>
+        <v>0.5</v>
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>2.2000000000000002</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>2.0428571428571427</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1820,52 +1834,60 @@
         <v>50</v>
       </c>
       <c r="H6" s="12">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
       <c r="K6" s="12">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.44</v>
+        <v>0.68</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>2.2000000000000002</v>
+        <v>1.7</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>4.3999999999999995</v>
-      </c>
-      <c r="O6" s="30"/>
-      <c r="P6" s="97"/>
-      <c r="Q6" s="13" t="e">
+        <v>3.4</v>
+      </c>
+      <c r="O6" s="30">
+        <v>5</v>
+      </c>
+      <c r="P6" s="97">
+        <v>3</v>
+      </c>
+      <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R6" s="30"/>
-      <c r="S6" s="97"/>
-      <c r="T6" s="13" t="e">
+        <v>0.6</v>
+      </c>
+      <c r="R6" s="30">
+        <v>11</v>
+      </c>
+      <c r="S6" s="97">
+        <v>7</v>
+      </c>
+      <c r="T6" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U6" s="11" t="e">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V6" s="14" t="e">
+        <v>2.3333333333333335</v>
+      </c>
+      <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1.0606060606060606</v>
       </c>
       <c r="W6" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
@@ -1891,59 +1913,61 @@
         <v>50</v>
       </c>
       <c r="H7" s="12">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I7" s="13">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="J7" s="30">
         <v>30</v>
       </c>
       <c r="K7" s="12">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L7" s="13">
         <f t="shared" si="1"/>
-        <v>0.33333333333333331</v>
+        <v>3.3333333333333333E-2</v>
       </c>
       <c r="M7" s="11">
         <f t="shared" si="2"/>
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" si="2"/>
-        <v>4.1666666666666661</v>
+        <v>0.83333333333333326</v>
       </c>
       <c r="O7" s="30">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="P7" s="97">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="R7" s="30">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="S7" s="97">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T7" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>1.3333333333333333</v>
+        <v>1</v>
       </c>
       <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="W7" s="34"/>
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="W7" s="34" t="s">
+        <v>77</v>
+      </c>
     </row>
     <row r="8" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -1989,24 +2013,24 @@
         <v>#DIV/0!</v>
       </c>
       <c r="O8" s="30">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P8" s="97">
         <v>4</v>
       </c>
       <c r="Q8" s="13">
         <f t="shared" si="3"/>
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="R8" s="30">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="S8" s="97">
         <v>6</v>
       </c>
       <c r="T8" s="13">
         <f t="shared" si="4"/>
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="U8" s="11">
         <f t="shared" si="5"/>
@@ -2014,9 +2038,11 @@
       </c>
       <c r="V8" s="14">
         <f t="shared" si="5"/>
-        <v>1.5</v>
-      </c>
-      <c r="W8" s="34"/>
+        <v>1</v>
+      </c>
+      <c r="W8" s="34" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="9" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
@@ -2040,9 +2066,7 @@
       <c r="G9" s="30">
         <v>0</v>
       </c>
-      <c r="H9" s="12">
-        <v>5</v>
-      </c>
+      <c r="H9" s="12"/>
       <c r="I9" s="13" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2050,42 +2074,50 @@
       <c r="J9" s="30">
         <v>20</v>
       </c>
-      <c r="K9" s="12">
-        <v>2</v>
-      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="13">
         <f t="shared" si="1"/>
-        <v>0.1</v>
-      </c>
-      <c r="M9" s="11">
+        <v>0</v>
+      </c>
+      <c r="M9" s="11" t="e">
         <f t="shared" si="2"/>
-        <v>0.4</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="N9" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O9" s="30"/>
-      <c r="P9" s="97"/>
-      <c r="Q9" s="13" t="e">
+      <c r="O9" s="30">
+        <v>5</v>
+      </c>
+      <c r="P9" s="97">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R9" s="30"/>
-      <c r="S9" s="97"/>
-      <c r="T9" s="13" t="e">
+        <v>0.6</v>
+      </c>
+      <c r="R9" s="30">
+        <v>2</v>
+      </c>
+      <c r="S9" s="97">
+        <v>1</v>
+      </c>
+      <c r="T9" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U9" s="11" t="e">
+        <v>0.5</v>
+      </c>
+      <c r="U9" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V9" s="14" t="e">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V9" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W9" s="34"/>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="W9" s="34" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="10" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="35" t="s">
@@ -2109,46 +2141,58 @@
       <c r="G10" s="30">
         <v>25</v>
       </c>
-      <c r="H10" s="12"/>
+      <c r="H10" s="12">
+        <v>12</v>
+      </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.48</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
-      <c r="K10" s="12"/>
+      <c r="K10" s="12">
+        <v>309</v>
+      </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="M10" s="11" t="e">
+      <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>25.75</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="O10" s="30"/>
-      <c r="P10" s="97"/>
-      <c r="Q10" s="13" t="e">
+      <c r="O10" s="30">
+        <v>4</v>
+      </c>
+      <c r="P10" s="97">
+        <v>4</v>
+      </c>
+      <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="R10" s="30"/>
-      <c r="S10" s="97"/>
-      <c r="T10" s="13" t="e">
+        <v>1</v>
+      </c>
+      <c r="R10" s="30">
+        <v>47</v>
+      </c>
+      <c r="S10" s="97">
+        <v>47</v>
+      </c>
+      <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="U10" s="11" t="e">
+        <v>1</v>
+      </c>
+      <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="V10" s="14" t="e">
+        <v>11.75</v>
+      </c>
+      <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>#DIV/0!</v>
+        <v>1</v>
       </c>
       <c r="W10" s="34" t="s">
         <v>75</v>
@@ -2552,11 +2596,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>8.533333333333333E-2</v>
+        <v>0.13333333333333333</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2564,15 +2608,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>55</v>
+        <v>350</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.14285714285714285</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>1.71875</v>
+        <v>7</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2580,31 +2624,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.5</v>
+        <v>0.72413793103448276</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>26</v>
+        <v>111</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>21</v>
+        <v>92</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.80769230769230771</v>
+        <v>0.8288288288288288</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>1.75</v>
+        <v>2.1904761904761907</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3481,11 +3525,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>5.6198347107438019E-2</v>
+        <v>6.2148760330578513E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3493,15 +3537,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>222</v>
+        <v>517</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>8.5880077369439076E-2</v>
+        <v>0.2</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>1.3058823529411765</v>
+        <v>2.75</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3509,31 +3553,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>173</v>
+        <v>207</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>125</v>
+        <v>155</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.7225433526011561</v>
+        <v>0.74879227053140096</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>265</v>
+        <v>350</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>151</v>
+        <v>222</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.56981132075471697</v>
+        <v>0.63428571428571423</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.208</v>
+        <v>1.4322580645161291</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3600,18 +3644,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.57692307692307687</v>
+        <v>0.61538461538461542</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F2" s="94">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3706,34 +3750,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6</f>
-        <v>128</v>
+        <f>92+9+11+10+6+12</f>
+        <v>140</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.21333333333333335</v>
+        <v>0.23333333333333334</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>141</v>
+        <v>164</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.25636363636363635</v>
+        <v>0.29818181818181816</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>409</v>
+        <v>386</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>37.18181818181818</v>
+        <v>38.6</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1015625</v>
+        <v>1.1714285714285715</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3763,38 +3807,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8+8</f>
-        <v>67</v>
+        <f>38+8+5+8+8+8</f>
+        <v>75</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.11166666666666666</v>
+        <v>0.125</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.24</v>
+        <v>0.25111111111111112</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>342</v>
+        <v>337</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>31.09090909090909</v>
+        <v>33.700000000000003</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.6119402985074627</v>
+        <v>1.5066666666666666</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>2.1492537313432836</v>
+        <v>2.0088888888888889</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3821,38 +3865,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6</f>
-        <v>54</v>
+        <f>32+7+9+6+8</f>
+        <v>62</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.09</v>
+        <v>0.10333333333333333</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.22545454545454546</v>
+        <v>0.26363636363636361</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>426</v>
+        <v>405</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>38.727272727272727</v>
+        <v>40.5</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>2.2962962962962963</v>
+        <v>2.338709677419355</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.5050505050505052</v>
+        <v>2.5513196480938416</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3879,38 +3923,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6+5</f>
-        <v>22</v>
+        <f>5+5+1+6+5+23</f>
+        <v>45</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>3.6666666666666667E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>7.0000000000000007E-2</v>
+        <v>9.2499999999999999E-2</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>33.81818181818182</v>
+        <v>36.299999999999997</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.2727272727272727</v>
+        <v>0.82222222222222219</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.9090909090909092</v>
+        <v>1.2333333333333334</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3959,7 +4003,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>51.272727272727273</v>
+        <v>56.4</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
@@ -3988,39 +4032,43 @@
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>26</v>
+        <v>76</v>
       </c>
       <c r="G9" s="30">
         <v>600</v>
       </c>
-      <c r="H9" s="12"/>
+      <c r="H9" s="12">
+        <v>2</v>
+      </c>
       <c r="I9" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>3.3333333333333335E-3</v>
       </c>
       <c r="J9" s="11">
         <v>550</v>
       </c>
-      <c r="K9" s="12"/>
+      <c r="K9" s="12">
+        <v>1</v>
+      </c>
       <c r="L9" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>1.8181818181818182E-3</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="5"/>
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>50</v>
-      </c>
-      <c r="O9" s="72" t="e">
+        <v>54.9</v>
+      </c>
+      <c r="O9" s="72">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P9" s="14" t="e">
+        <v>0.5</v>
+      </c>
+      <c r="P9" s="14">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="Q9" s="34"/>
     </row>
@@ -4047,38 +4095,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3+7</f>
-        <v>41</v>
+        <f>22+2+7+3+7+5</f>
+        <v>46</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.20499999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>724</v>
+        <v>771</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.24133333333333334</v>
+        <v>0.25700000000000001</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2276</v>
+        <v>2229</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>206.90909090909091</v>
+        <v>222.9</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>17.658536585365855</v>
+        <v>16.760869565217391</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.1772357723577238</v>
+        <v>1.1173913043478261</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4123,7 +4171,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>59.090909090909093</v>
+        <v>65</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4176,7 +4224,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4276,7 +4324,7 @@
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>-9.0909090909090917</v>
+        <v>-10</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4378,7 +4426,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>-45.454545454545453</v>
+        <v>-50</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4485,11 +4533,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>6.3600000000000004E-2</v>
+        <v>7.5200000000000003E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4497,23 +4545,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>1736</v>
+        <v>1842</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.2386254295532646</v>
+        <v>0.2531958762886598</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>5539</v>
+        <v>5433</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>503.54545454545456</v>
+        <v>543.29999999999995</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>5.4591194968553456</v>
+        <v>4.8989361702127656</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4566,7 +4614,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>42.272727272727273</v>
+        <v>46.5</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4622,7 +4670,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>42.454545454545453</v>
+        <v>46.7</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4678,7 +4726,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>42.18181818181818</v>
+        <v>46.4</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4734,7 +4782,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>43</v>
+        <v>47.3</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4790,7 +4838,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>44</v>
+        <v>48.4</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4846,7 +4894,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>213.90909090909091</v>
+        <v>235.3</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4903,7 +4951,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>56</v>
+        <v>61.6</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -4959,7 +5007,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>51.454545454545453</v>
+        <v>56.6</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5015,7 +5063,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>52.18181818181818</v>
+        <v>57.4</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5071,7 +5119,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>55.636363636363633</v>
+        <v>61.2</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5127,7 +5175,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>215.27272727272728</v>
+        <v>236.8</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5156,11 +5204,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>519</v>
+        <v>577</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>9.5229357798165132E-2</v>
+        <v>0.10587155963302752</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5168,23 +5216,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>2015</v>
+        <v>2121</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.16415478615071283</v>
+        <v>0.17279022403258656</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>10260</v>
+        <v>10154</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>932.72727272727275</v>
+        <v>1015.4</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.882466281310212</v>
+        <v>3.6759098786828424</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{332E3393-C39A-4147-A935-E77158C1EDA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBDBBCB-AE16-47C4-9855-943B61017B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -3644,18 +3644,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.61538461538461542</v>
+        <v>0.65384615384615385</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" s="94">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3750,34 +3750,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6+12</f>
-        <v>140</v>
+        <f>92+9+11+10+6+12+6+6</f>
+        <v>152</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.23333333333333334</v>
+        <v>0.25333333333333335</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.29818181818181816</v>
+        <v>0.31636363636363635</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>38.6</v>
+        <v>41.777777777777779</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1714285714285715</v>
+        <v>1.1447368421052631</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3807,38 +3807,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8+8+8</f>
-        <v>75</v>
+        <f>38+8+5+8+8+8+8</f>
+        <v>83</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.125</v>
+        <v>0.13833333333333334</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.25111111111111112</v>
+        <v>0.27555555555555555</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>337</v>
+        <v>326</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>33.700000000000003</v>
+        <v>36.222222222222221</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.5066666666666666</v>
+        <v>1.4939759036144578</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>2.0088888888888889</v>
+        <v>1.9919678714859437</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3865,38 +3865,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6+8</f>
-        <v>62</v>
+        <f>32+7+9+6+8+5</f>
+        <v>67</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.10333333333333333</v>
+        <v>0.11166666666666666</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>145</v>
+        <v>157</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.26363636363636361</v>
+        <v>0.28545454545454546</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>405</v>
+        <v>393</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>40.5</v>
+        <v>43.666666666666664</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>2.338709677419355</v>
+        <v>2.3432835820895521</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.5513196480938416</v>
+        <v>2.5563093622795114</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3934,27 +3934,27 @@
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>9.2499999999999999E-2</v>
+        <v>9.5000000000000001E-2</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>36.299999999999997</v>
+        <v>40.222222222222221</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>0.82222222222222219</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.2333333333333334</v>
+        <v>1.2666666666666668</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -4003,7 +4003,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>56.4</v>
+        <v>62.666666666666664</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
@@ -4060,7 +4060,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>54.9</v>
+        <v>61</v>
       </c>
       <c r="O9" s="72">
         <f t="shared" si="4"/>
@@ -4106,27 +4106,27 @@
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.25700000000000001</v>
+        <v>0.25733333333333336</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>222.9</v>
+        <v>247.55555555555554</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>16.760869565217391</v>
+        <v>16.782608695652176</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.1173913043478261</v>
+        <v>1.1188405797101451</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>65</v>
+        <v>72.222222222222229</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>55</v>
+        <v>61.111111111111114</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>-10</v>
+        <v>-11.111111111111111</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>-50</v>
+        <v>-55.555555555555557</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4533,11 +4533,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>376</v>
+        <v>401</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>7.5200000000000003E-2</v>
+        <v>8.0199999999999994E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4545,23 +4545,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>1842</v>
+        <v>1877</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.2531958762886598</v>
+        <v>0.25800687285223367</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>5433</v>
+        <v>5398</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>543.29999999999995</v>
+        <v>599.77777777777783</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>4.8989361702127656</v>
+        <v>4.6807980049875315</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>46.5</v>
+        <v>51.666666666666664</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>46.7</v>
+        <v>51.888888888888886</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>46.4</v>
+        <v>51.555555555555557</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>47.3</v>
+        <v>52.555555555555557</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>48.4</v>
+        <v>53.777777777777779</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>235.3</v>
+        <v>261.44444444444446</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>61.6</v>
+        <v>68.444444444444443</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>56.6</v>
+        <v>62.888888888888886</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>57.4</v>
+        <v>63.777777777777779</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>61.2</v>
+        <v>68</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>236.8</v>
+        <v>263.11111111111109</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5204,11 +5204,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.10587155963302752</v>
+        <v>0.11045871559633028</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5216,23 +5216,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>2121</v>
+        <v>2156</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.17279022403258656</v>
+        <v>0.17564154786150712</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>10154</v>
+        <v>10119</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1015.4</v>
+        <v>1124.3333333333333</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.6759098786828424</v>
+        <v>3.5813953488372094</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CBDBBCB-AE16-47C4-9855-943B61017B71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728BF3AA-4CC2-4D14-A3CD-EE9180728105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="373" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="78">
   <si>
     <t>Booking</t>
   </si>
@@ -253,16 +253,13 @@
     <t xml:space="preserve">Jabran Iqbal </t>
   </si>
   <si>
-    <t>Pending Supply</t>
-  </si>
-  <si>
     <t>Furqan</t>
   </si>
   <si>
-    <t xml:space="preserve">Both delivered </t>
-  </si>
-  <si>
-    <t>Pending Delivered</t>
+    <t xml:space="preserve">Hasan </t>
+  </si>
+  <si>
+    <t>Pendings</t>
   </si>
 </sst>
 </file>
@@ -1557,7 +1554,7 @@
     </row>
     <row r="2" spans="1:28" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="F2" s="94">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>2</v>
@@ -1678,39 +1675,39 @@
         <v>50</v>
       </c>
       <c r="H4" s="8">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="I4" s="32">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.32</v>
+        <v>0.18</v>
       </c>
       <c r="J4" s="30">
         <v>40</v>
       </c>
       <c r="K4" s="31">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L4" s="32">
         <f t="shared" ref="L4:L12" si="1">K4/J4</f>
-        <v>0.3</v>
+        <v>0.32500000000000001</v>
       </c>
       <c r="M4" s="30">
         <f t="shared" ref="M4:N12" si="2">K4/H4</f>
-        <v>0.75</v>
+        <v>1.4444444444444444</v>
       </c>
       <c r="N4" s="33">
         <f t="shared" si="2"/>
-        <v>0.9375</v>
+        <v>1.8055555555555556</v>
       </c>
       <c r="O4" s="30">
         <v>15</v>
       </c>
       <c r="P4" s="96">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Q4" s="32">
         <f t="shared" ref="Q4:Q12" si="3">P4/O4</f>
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="R4" s="30">
         <v>16</v>
@@ -1724,15 +1721,13 @@
       </c>
       <c r="U4" s="30">
         <f t="shared" ref="U4:V12" si="5">S4/P4</f>
-        <v>1.4444444444444444</v>
+        <v>1.0833333333333333</v>
       </c>
       <c r="V4" s="33">
         <f t="shared" si="5"/>
-        <v>1.3541666666666667</v>
-      </c>
-      <c r="W4" s="34" t="s">
-        <v>77</v>
-      </c>
+        <v>1.015625</v>
+      </c>
+      <c r="W4" s="34"/>
     </row>
     <row r="5" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A5" s="35" t="s">
@@ -1767,29 +1762,29 @@
         <v>30</v>
       </c>
       <c r="K5" s="12">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L5" s="13">
         <f t="shared" si="1"/>
-        <v>0.36666666666666664</v>
+        <v>0.4</v>
       </c>
       <c r="M5" s="11">
         <f t="shared" si="2"/>
-        <v>1.1000000000000001</v>
+        <v>1.2</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="2"/>
-        <v>1.833333333333333</v>
+        <v>2</v>
       </c>
       <c r="O5" s="30">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="P5" s="97">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="Q5" s="13">
         <f t="shared" si="3"/>
-        <v>0.69230769230769229</v>
+        <v>1</v>
       </c>
       <c r="R5" s="30">
         <v>16</v>
@@ -1803,11 +1798,11 @@
       </c>
       <c r="U5" s="11">
         <f t="shared" si="5"/>
-        <v>0.88888888888888884</v>
+        <v>0.72727272727272729</v>
       </c>
       <c r="V5" s="14">
         <f t="shared" si="5"/>
-        <v>0.72222222222222221</v>
+        <v>0.5</v>
       </c>
       <c r="W5" s="34"/>
     </row>
@@ -1834,39 +1829,39 @@
         <v>50</v>
       </c>
       <c r="H6" s="12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>0.2</v>
+        <v>0.14000000000000001</v>
       </c>
       <c r="J6" s="30">
         <v>25</v>
       </c>
       <c r="K6" s="12">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="L6" s="13">
         <f t="shared" si="1"/>
-        <v>0.68</v>
+        <v>0.36</v>
       </c>
       <c r="M6" s="11">
         <f t="shared" si="2"/>
-        <v>1.7</v>
+        <v>1.2857142857142858</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="2"/>
-        <v>3.4</v>
+        <v>2.5714285714285712</v>
       </c>
       <c r="O6" s="30">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="P6" s="97">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q6" s="13">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>0.63636363636363635</v>
       </c>
       <c r="R6" s="30">
         <v>11</v>
@@ -1880,15 +1875,13 @@
       </c>
       <c r="U6" s="11">
         <f t="shared" si="5"/>
-        <v>2.3333333333333335</v>
+        <v>1</v>
       </c>
       <c r="V6" s="14">
         <f t="shared" si="5"/>
-        <v>1.0606060606060606</v>
-      </c>
-      <c r="W6" s="34" t="s">
-        <v>77</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="W6" s="34"/>
     </row>
     <row r="7" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A7" s="35" t="s">
@@ -1938,14 +1931,14 @@
         <v>0.83333333333333326</v>
       </c>
       <c r="O7" s="30">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="P7" s="97">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q7" s="13">
         <f t="shared" si="3"/>
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="R7" s="30">
         <v>13</v>
@@ -1959,15 +1952,13 @@
       </c>
       <c r="U7" s="11">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.1111111111111112</v>
       </c>
       <c r="V7" s="14">
         <f t="shared" si="5"/>
-        <v>0.92307692307692313</v>
-      </c>
-      <c r="W7" s="34" t="s">
-        <v>77</v>
-      </c>
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="W7" s="34"/>
     </row>
     <row r="8" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A8" s="35" t="s">
@@ -1986,41 +1977,41 @@
         <v>22</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G8" s="30">
         <v>50</v>
       </c>
-      <c r="H8" s="12"/>
+      <c r="H8" s="12">
+        <v>3</v>
+      </c>
       <c r="I8" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="J8" s="30">
         <v>20</v>
       </c>
-      <c r="K8" s="12"/>
+      <c r="K8" s="12">
+        <v>3</v>
+      </c>
       <c r="L8" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M8" s="11" t="e">
+        <v>0.15</v>
+      </c>
+      <c r="M8" s="11">
         <f t="shared" si="2"/>
+        <v>1</v>
+      </c>
+      <c r="N8" s="14">
+        <f t="shared" si="2"/>
+        <v>2.5</v>
+      </c>
+      <c r="O8" s="30"/>
+      <c r="P8" s="97"/>
+      <c r="Q8" s="13" t="e">
+        <f t="shared" si="3"/>
         <v>#DIV/0!</v>
-      </c>
-      <c r="N8" s="14" t="e">
-        <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="O8" s="30">
-        <v>4</v>
-      </c>
-      <c r="P8" s="97">
-        <v>4</v>
-      </c>
-      <c r="Q8" s="13">
-        <f t="shared" si="3"/>
-        <v>1</v>
       </c>
       <c r="R8" s="30">
         <v>6</v>
@@ -2032,17 +2023,15 @@
         <f t="shared" si="4"/>
         <v>1</v>
       </c>
-      <c r="U8" s="11">
+      <c r="U8" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>1.5</v>
-      </c>
-      <c r="V8" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V8" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="W8" s="34" t="s">
-        <v>78</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W8" s="34"/>
     </row>
     <row r="9" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A9" s="35" t="s">
@@ -2061,12 +2050,14 @@
         <v>22</v>
       </c>
       <c r="F9" s="95" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G9" s="30">
         <v>0</v>
       </c>
-      <c r="H9" s="12"/>
+      <c r="H9" s="12">
+        <v>10</v>
+      </c>
       <c r="I9" s="13" t="e">
         <f t="shared" si="0"/>
         <v>#DIV/0!</v>
@@ -2074,28 +2065,30 @@
       <c r="J9" s="30">
         <v>20</v>
       </c>
-      <c r="K9" s="12"/>
+      <c r="K9" s="12">
+        <v>7</v>
+      </c>
       <c r="L9" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="11" t="e">
+        <v>0.35</v>
+      </c>
+      <c r="M9" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0.7</v>
       </c>
       <c r="N9" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O9" s="30">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="P9" s="97">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13" t="e">
         <f t="shared" si="3"/>
-        <v>0.6</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="R9" s="30">
         <v>2</v>
@@ -2107,17 +2100,15 @@
         <f t="shared" si="4"/>
         <v>0.5</v>
       </c>
-      <c r="U9" s="11">
+      <c r="U9" s="11" t="e">
         <f t="shared" si="5"/>
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="V9" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="V9" s="14" t="e">
         <f t="shared" si="5"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="W9" s="34" t="s">
-        <v>78</v>
-      </c>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W9" s="34"/>
     </row>
     <row r="10" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="A10" s="35" t="s">
@@ -2142,17 +2133,17 @@
         <v>25</v>
       </c>
       <c r="H10" s="12">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="I10" s="13">
         <f t="shared" si="0"/>
-        <v>0.48</v>
+        <v>0.24</v>
       </c>
       <c r="J10" s="30">
         <v>0</v>
       </c>
       <c r="K10" s="12">
-        <v>309</v>
+        <v>61</v>
       </c>
       <c r="L10" s="13" t="e">
         <f t="shared" si="1"/>
@@ -2160,42 +2151,42 @@
       </c>
       <c r="M10" s="11">
         <f t="shared" si="2"/>
-        <v>25.75</v>
+        <v>10.166666666666666</v>
       </c>
       <c r="N10" s="14" t="e">
         <f t="shared" si="2"/>
         <v>#DIV/0!</v>
       </c>
       <c r="O10" s="30">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P10" s="97">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q10" s="13">
         <f t="shared" si="3"/>
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="R10" s="30">
-        <v>47</v>
+        <v>180</v>
       </c>
       <c r="S10" s="97">
-        <v>47</v>
+        <v>155</v>
       </c>
       <c r="T10" s="13">
         <f t="shared" si="4"/>
-        <v>1</v>
+        <v>0.86111111111111116</v>
       </c>
       <c r="U10" s="11">
         <f t="shared" si="5"/>
-        <v>11.75</v>
+        <v>31</v>
       </c>
       <c r="V10" s="14">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>1.0333333333333334</v>
       </c>
       <c r="W10" s="34" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AB10">
         <v>33</v>
@@ -2223,26 +2214,30 @@
       <c r="G11" s="30">
         <v>50</v>
       </c>
-      <c r="H11" s="12"/>
+      <c r="H11" s="12">
+        <v>14</v>
+      </c>
       <c r="I11" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J11" s="30">
         <v>200</v>
       </c>
-      <c r="K11" s="12"/>
+      <c r="K11" s="12">
+        <v>23</v>
+      </c>
       <c r="L11" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M11" s="11" t="e">
+        <v>0.115</v>
+      </c>
+      <c r="M11" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N11" s="14" t="e">
+        <v>1.6428571428571428</v>
+      </c>
+      <c r="N11" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>0.4107142857142857</v>
       </c>
       <c r="O11" s="30"/>
       <c r="P11" s="12"/>
@@ -2291,26 +2286,30 @@
       <c r="G12" s="30">
         <v>50</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="12">
+        <v>13</v>
+      </c>
       <c r="I12" s="13">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.26</v>
       </c>
       <c r="J12" s="30">
         <v>20</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="12">
+        <v>14</v>
+      </c>
       <c r="L12" s="13">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M12" s="11" t="e">
+        <v>0.7</v>
+      </c>
+      <c r="M12" s="11">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N12" s="14" t="e">
+        <v>1.0769230769230769</v>
+      </c>
+      <c r="N12" s="14">
         <f t="shared" si="2"/>
-        <v>#DIV/0!</v>
+        <v>2.6923076923076921</v>
       </c>
       <c r="O12" s="30"/>
       <c r="P12" s="12"/>
@@ -2596,11 +2595,11 @@
       </c>
       <c r="H19" s="41">
         <f>SUM(H4:H18)</f>
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="I19" s="42">
         <f t="shared" si="0"/>
-        <v>0.13333333333333333</v>
+        <v>0.19733333333333333</v>
       </c>
       <c r="J19" s="40">
         <f>SUM(J4:J18)</f>
@@ -2608,15 +2607,15 @@
       </c>
       <c r="K19" s="41">
         <f>SUM(K4:K18)</f>
-        <v>350</v>
+        <v>143</v>
       </c>
       <c r="L19" s="42">
         <f t="shared" ref="L19" si="6">K19/J19</f>
-        <v>0.90909090909090906</v>
+        <v>0.37142857142857144</v>
       </c>
       <c r="M19" s="40">
         <f>K19/H19</f>
-        <v>7</v>
+        <v>1.9324324324324325</v>
       </c>
       <c r="N19" s="43" t="e">
         <f>AVERAGE(N4:N18)</f>
@@ -2624,31 +2623,31 @@
       </c>
       <c r="O19" s="40">
         <f>SUM(O4:O18)</f>
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="P19" s="41">
         <f>SUM(P4:P18)</f>
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Q19" s="42">
         <f t="shared" ref="Q19" si="7">P19/O19</f>
-        <v>0.72413793103448276</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="R19" s="40">
         <f>SUM(R4:R18)</f>
-        <v>111</v>
+        <v>244</v>
       </c>
       <c r="S19" s="41">
         <f>SUM(S4:S18)</f>
-        <v>92</v>
+        <v>200</v>
       </c>
       <c r="T19" s="42">
         <f t="shared" ref="T19" si="8">S19/R19</f>
-        <v>0.8288288288288288</v>
+        <v>0.81967213114754101</v>
       </c>
       <c r="U19" s="40">
         <f>S19/P19</f>
-        <v>2.1904761904761907</v>
+        <v>4.5454545454545459</v>
       </c>
       <c r="V19" s="43" t="e">
         <f>AVERAGE(V4:V18)</f>
@@ -3525,11 +3524,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31" si="24">+H30+H25+H19</f>
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="I31" s="22">
         <f t="shared" si="0"/>
-        <v>6.2148760330578513E-2</v>
+        <v>7.0082644628099169E-2</v>
       </c>
       <c r="J31" s="20">
         <f>+J30+J25+J19</f>
@@ -3537,15 +3536,15 @@
       </c>
       <c r="K31" s="21">
         <f t="shared" ref="K31" si="25">+K30+K25+K19</f>
-        <v>517</v>
+        <v>310</v>
       </c>
       <c r="L31" s="22">
         <f t="shared" si="9"/>
-        <v>0.2</v>
+        <v>0.11992263056092843</v>
       </c>
       <c r="M31" s="20">
         <f>K31/H31</f>
-        <v>2.75</v>
+        <v>1.4622641509433962</v>
       </c>
       <c r="N31" s="23" t="e">
         <f>AVERAGE(N30,N19,N25)</f>
@@ -3553,31 +3552,31 @@
       </c>
       <c r="O31" s="20">
         <f>+O30+O25+O19</f>
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="P31" s="21">
         <f t="shared" ref="P31" si="26">+P30+P25+P19</f>
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q31" s="22">
         <f t="shared" si="11"/>
-        <v>0.74879227053140096</v>
+        <v>0.78109452736318408</v>
       </c>
       <c r="R31" s="20">
         <f>+R30+R25+R19</f>
-        <v>350</v>
+        <v>483</v>
       </c>
       <c r="S31" s="21">
         <f t="shared" ref="S31" si="27">+S30+S25+S19</f>
-        <v>222</v>
+        <v>330</v>
       </c>
       <c r="T31" s="22">
         <f t="shared" si="12"/>
-        <v>0.63428571428571423</v>
+        <v>0.68322981366459623</v>
       </c>
       <c r="U31" s="20">
         <f>S31/P31</f>
-        <v>1.4322580645161291</v>
+        <v>2.1019108280254777</v>
       </c>
       <c r="V31" s="23" t="e">
         <f>AVERAGE(V30,V19,V25)</f>
@@ -3644,18 +3643,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.65384615384615385</v>
+        <v>0.69230769230769229</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="94">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3750,34 +3749,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6+12+6+6</f>
-        <v>152</v>
+        <f>92+9+11+10+6+12+6+6+12</f>
+        <v>164</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.25333333333333335</v>
+        <v>0.27333333333333332</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.31636363636363635</v>
+        <v>0.33636363636363636</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>376</v>
+        <v>365</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>41.777777777777779</v>
+        <v>45.625</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1447368421052631</v>
+        <v>1.1280487804878048</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3807,38 +3806,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8+8+8+8</f>
-        <v>83</v>
+        <f>38+8+5+8+8+8+8+8</f>
+        <v>91</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.13833333333333334</v>
+        <v>0.15166666666666667</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>124</v>
+        <v>138</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.27555555555555555</v>
+        <v>0.30666666666666664</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>326</v>
+        <v>312</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>36.222222222222221</v>
+        <v>39</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.4939759036144578</v>
+        <v>1.5164835164835164</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.9919678714859437</v>
+        <v>2.0219780219780219</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3865,38 +3864,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6+8+5</f>
-        <v>67</v>
+        <f>32+7+9+6+8+5+9</f>
+        <v>76</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.11166666666666666</v>
+        <v>0.12666666666666668</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.28545454545454546</v>
+        <v>0.30545454545454548</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>393</v>
+        <v>382</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>43.666666666666664</v>
+        <v>47.75</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>2.3432835820895521</v>
+        <v>2.2105263157894739</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.5563093622795114</v>
+        <v>2.4114832535885169</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3923,38 +3922,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6+5+23</f>
-        <v>45</v>
+        <f>5+5+1+6+5+23+3</f>
+        <v>48</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>7.4999999999999997E-2</v>
+        <v>0.08</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>9.5000000000000001E-2</v>
+        <v>0.1125</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>40.222222222222221</v>
+        <v>44.375</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>0.84444444444444444</v>
+        <v>0.9375</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.2666666666666668</v>
+        <v>1.40625</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -4003,7 +4002,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>62.666666666666664</v>
+        <v>70.5</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
@@ -4032,17 +4031,18 @@
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G9" s="30">
         <v>600</v>
       </c>
       <c r="H9" s="12">
-        <v>2</v>
+        <f>2+4</f>
+        <v>6</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" si="0"/>
-        <v>3.3333333333333335E-3</v>
+        <v>0.01</v>
       </c>
       <c r="J9" s="11">
         <v>550</v>
@@ -4060,15 +4060,15 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>61</v>
+        <v>68.625</v>
       </c>
       <c r="O9" s="72">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="P9" s="14">
         <f t="shared" si="4"/>
-        <v>0.54545454545454541</v>
+        <v>0.18181818181818182</v>
       </c>
       <c r="Q9" s="34"/>
     </row>
@@ -4095,38 +4095,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3+7+5</f>
-        <v>46</v>
+        <f>22+2+7+3+7+5+6</f>
+        <v>52</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.23</v>
+        <v>0.26</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>772</v>
+        <v>1058</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.25733333333333336</v>
+        <v>0.35266666666666668</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>2228</v>
+        <v>1942</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>247.55555555555554</v>
+        <v>242.75</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>16.782608695652176</v>
+        <v>20.346153846153847</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.1188405797101451</v>
+        <v>1.3564102564102565</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>72.222222222222229</v>
+        <v>81.25</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>61.111111111111114</v>
+        <v>68.75</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>-11.111111111111111</v>
+        <v>-12.5</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>-55.555555555555557</v>
+        <v>-62.5</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4533,11 +4533,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>8.0199999999999994E-2</v>
+        <v>8.8599999999999998E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4545,23 +4545,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>1877</v>
+        <v>2206</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.25800687285223367</v>
+        <v>0.30323024054982817</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>5398</v>
+        <v>5069</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>599.77777777777783</v>
+        <v>633.625</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>4.6807980049875315</v>
+        <v>4.979683972911964</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>51.666666666666664</v>
+        <v>58.125</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>51.888888888888886</v>
+        <v>58.375</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>51.555555555555557</v>
+        <v>58</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>52.555555555555557</v>
+        <v>59.125</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>53.777777777777779</v>
+        <v>60.5</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>261.44444444444446</v>
+        <v>294.125</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>68.444444444444443</v>
+        <v>77</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>62.888888888888886</v>
+        <v>70.75</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>63.777777777777779</v>
+        <v>71.75</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>68</v>
+        <v>76.5</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>263.11111111111109</v>
+        <v>296</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5204,11 +5204,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>602</v>
+        <v>644</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.11045871559633028</v>
+        <v>0.11816513761467889</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5216,23 +5216,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>2156</v>
+        <v>2485</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.17564154786150712</v>
+        <v>0.20244399185336048</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>10119</v>
+        <v>9790</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1124.3333333333333</v>
+        <v>1223.75</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.5813953488372094</v>
+        <v>3.8586956521739131</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{728BF3AA-4CC2-4D14-A3CD-EE9180728105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ABCBA1-F1F4-41CC-8AFA-CC8738A84643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3643,18 +3643,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.69230769230769229</v>
+        <v>0.73076923076923073</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" s="94">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3749,34 +3749,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6+12+6+6+12</f>
-        <v>164</v>
+        <f>92+9+11+10+6+12+6+6+12+6</f>
+        <v>170</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.27333333333333332</v>
+        <v>0.28333333333333333</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.33636363636363636</v>
+        <v>0.35090909090909089</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>45.625</v>
+        <v>51</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1280487804878048</v>
+        <v>1.1352941176470588</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3806,38 +3806,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8+8+8+8+8</f>
-        <v>91</v>
+        <f>38+8+5+8+8+8+8+8+7</f>
+        <v>98</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.15166666666666667</v>
+        <v>0.16333333333333333</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.30666666666666664</v>
+        <v>0.32444444444444442</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>39</v>
+        <v>43.428571428571431</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.5164835164835164</v>
+        <v>1.489795918367347</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>2.0219780219780219</v>
+        <v>1.9863945578231292</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3864,38 +3864,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6+8+5+9</f>
-        <v>76</v>
+        <f>32+7+9+6+8+5+9+7</f>
+        <v>83</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.12666666666666668</v>
+        <v>0.13833333333333334</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>168</v>
+        <v>176</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.30545454545454548</v>
+        <v>0.32</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>47.75</v>
+        <v>53.428571428571431</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>2.2105263157894739</v>
+        <v>2.1204819277108435</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.4114832535885169</v>
+        <v>2.3132530120481927</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3922,38 +3922,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6+5+23+3</f>
-        <v>48</v>
+        <f>5+5+1+6+5+23+3+1</f>
+        <v>49</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>0.08</v>
+        <v>8.1666666666666665E-2</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.1125</v>
+        <v>0.115</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>44.375</v>
+        <v>50.571428571428569</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>0.9375</v>
+        <v>0.93877551020408168</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.40625</v>
+        <v>1.4081632653061225</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>70.5</v>
+        <v>80.571428571428569</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
@@ -4037,38 +4037,38 @@
         <v>600</v>
       </c>
       <c r="H9" s="12">
-        <f>2+4</f>
-        <v>6</v>
+        <f>2+4+4</f>
+        <v>10</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" si="0"/>
-        <v>0.01</v>
+        <v>1.6666666666666666E-2</v>
       </c>
       <c r="J9" s="11">
         <v>550</v>
       </c>
       <c r="K9" s="12">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L9" s="71">
         <f t="shared" si="1"/>
-        <v>1.8181818181818182E-3</v>
+        <v>9.0909090909090905E-3</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="5"/>
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>68.625</v>
+        <v>77.857142857142861</v>
       </c>
       <c r="O9" s="72">
         <f t="shared" si="4"/>
-        <v>0.16666666666666666</v>
+        <v>0.5</v>
       </c>
       <c r="P9" s="14">
         <f t="shared" si="4"/>
-        <v>0.18181818181818182</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="Q9" s="34"/>
     </row>
@@ -4095,38 +4095,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3+7+5+6</f>
-        <v>52</v>
+        <f>22+2+7+3+7+5+6+4</f>
+        <v>56</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.26</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>1058</v>
+        <v>1165</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.35266666666666668</v>
+        <v>0.38833333333333331</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>1942</v>
+        <v>1835</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>242.75</v>
+        <v>262.14285714285717</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>20.346153846153847</v>
+        <v>20.803571428571427</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.3564102564102565</v>
+        <v>1.3869047619047616</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4171,7 +4171,7 @@
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>81.25</v>
+        <v>92.857142857142861</v>
       </c>
       <c r="O11" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>68.75</v>
+        <v>78.571428571428569</v>
       </c>
       <c r="O12" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4324,7 +4324,7 @@
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>-12.5</v>
+        <v>-14.285714285714286</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4426,7 +4426,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>-62.5</v>
+        <v>-71.428571428571431</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4533,11 +4533,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>443</v>
+        <v>472</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>8.8599999999999998E-2</v>
+        <v>9.4399999999999998E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4545,23 +4545,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>2206</v>
+        <v>2342</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.30323024054982817</v>
+        <v>0.32192439862542954</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>5069</v>
+        <v>4933</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>633.625</v>
+        <v>704.71428571428567</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>4.979683972911964</v>
+        <v>4.9618644067796609</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>58.125</v>
+        <v>66.428571428571431</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4670,7 +4670,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>58.375</v>
+        <v>66.714285714285708</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4726,7 +4726,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>58</v>
+        <v>66.285714285714292</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4782,7 +4782,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>59.125</v>
+        <v>67.571428571428569</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>60.5</v>
+        <v>69.142857142857139</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4894,7 +4894,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>294.125</v>
+        <v>336.14285714285717</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4951,7 +4951,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5007,7 +5007,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>70.75</v>
+        <v>80.857142857142861</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>71.75</v>
+        <v>82</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>76.5</v>
+        <v>87.428571428571431</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>296</v>
+        <v>338.28571428571428</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5204,11 +5204,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>644</v>
+        <v>673</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.11816513761467889</v>
+        <v>0.12348623853211009</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5216,23 +5216,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>2485</v>
+        <v>2621</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.20244399185336048</v>
+        <v>0.21352342158859469</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>9790</v>
+        <v>9654</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1223.75</v>
+        <v>1379.1428571428571</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.8586956521739131</v>
+        <v>3.8945022288261515</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19ABCBA1-F1F4-41CC-8AFA-CC8738A84643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1F60D7-56D1-4779-B19D-69D17D689C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA1F60D7-56D1-4779-B19D-69D17D689C55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB95B6D-1231-48B1-87A7-1BE99EF6EF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Today Performance" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="79">
   <si>
     <t>Booking</t>
   </si>
@@ -260,6 +260,9 @@
   </si>
   <si>
     <t>Pendings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yasir </t>
   </si>
 </sst>
 </file>
@@ -3654,7 +3657,7 @@
         <v>7</v>
       </c>
       <c r="F2" s="94">
-        <v>46254</v>
+        <v>46256</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3749,34 +3752,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6+12+6+6+12+6</f>
-        <v>170</v>
+        <f>92+9+11+10+6+12+6+6+12+6+10</f>
+        <v>180</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.28333333333333333</v>
+        <v>0.3</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.35090909090909089</v>
+        <v>0.36545454545454548</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>51</v>
+        <v>49.857142857142854</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1352941176470588</v>
+        <v>1.1166666666666667</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3806,38 +3809,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8+8+8+8+8+7</f>
-        <v>98</v>
+        <f>38+8+5+8+8+8+8+8+7+8</f>
+        <v>106</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.16333333333333333</v>
+        <v>0.17666666666666667</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.32444444444444442</v>
+        <v>0.34222222222222221</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>43.428571428571431</v>
+        <v>42.285714285714285</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.489795918367347</v>
+        <v>1.4528301886792452</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.9863945578231292</v>
+        <v>1.9371069182389937</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3864,38 +3867,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6+8+5+9+7</f>
-        <v>83</v>
+        <f>32+7+9+6+8+5+9+7+5</f>
+        <v>88</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.13833333333333334</v>
+        <v>0.14666666666666667</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.32</v>
+        <v>0.3290909090909091</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>374</v>
+        <v>369</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>53.428571428571431</v>
+        <v>52.714285714285715</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>2.1204819277108435</v>
+        <v>2.0568181818181817</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.3132530120481927</v>
+        <v>2.2438016528925622</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3922,38 +3925,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6+5+23+3+1</f>
-        <v>49</v>
+        <f>5+5+1+6+5+23+3+1+5</f>
+        <v>54</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>8.1666666666666665E-2</v>
+        <v>0.09</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.115</v>
+        <v>0.1275</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>354</v>
+        <v>349</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>50.571428571428569</v>
+        <v>49.857142857142854</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>0.93877551020408168</v>
+        <v>0.94444444444444442</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.4081632653061225</v>
+        <v>1.4166666666666667</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3980,11 +3983,12 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <v>4</v>
+        <f>4+5</f>
+        <v>9</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>6.6666666666666671E-3</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
@@ -4006,11 +4010,11 @@
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>2.75</v>
+        <v>1.2222222222222223</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>2.8695652173913042</v>
+        <v>1.2753623188405796</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4037,12 +4041,12 @@
         <v>600</v>
       </c>
       <c r="H9" s="12">
-        <f>2+4+4</f>
-        <v>10</v>
+        <f>2+4+4+9</f>
+        <v>19</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" si="0"/>
-        <v>1.6666666666666666E-2</v>
+        <v>3.1666666666666669E-2</v>
       </c>
       <c r="J9" s="11">
         <v>550</v>
@@ -4064,11 +4068,11 @@
       </c>
       <c r="O9" s="72">
         <f t="shared" si="4"/>
-        <v>0.5</v>
+        <v>0.26315789473684209</v>
       </c>
       <c r="P9" s="14">
         <f t="shared" si="4"/>
-        <v>0.54545454545454541</v>
+        <v>0.2870813397129186</v>
       </c>
       <c r="Q9" s="34"/>
     </row>
@@ -4095,38 +4099,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3+7+5+6+4</f>
-        <v>56</v>
+        <f>22+2+7+3+7+5+6+4+10</f>
+        <v>66</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0.33</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>1165</v>
+        <v>1293</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.38833333333333331</v>
+        <v>0.43099999999999999</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>1835</v>
+        <v>1707</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>262.14285714285717</v>
+        <v>243.85714285714286</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>20.803571428571427</v>
+        <v>19.59090909090909</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.3869047619047616</v>
+        <v>1.3060606060606059</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4252,34 +4256,44 @@
       <c r="E13" s="16" t="s">
         <v>22</v>
       </c>
-      <c r="F13" s="49"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="12"/>
-      <c r="I13" s="70" t="e">
+      <c r="F13" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="11">
+        <v>600</v>
+      </c>
+      <c r="H13" s="12">
+        <v>15</v>
+      </c>
+      <c r="I13" s="70">
         <f t="shared" ref="I13:I15" si="7">H13/G13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="J13" s="11"/>
-      <c r="K13" s="12"/>
-      <c r="L13" s="71" t="e">
+        <v>2.5000000000000001E-2</v>
+      </c>
+      <c r="J13" s="11">
+        <v>450</v>
+      </c>
+      <c r="K13" s="12">
+        <v>14</v>
+      </c>
+      <c r="L13" s="71">
         <f t="shared" ref="L13:L16" si="8">K13/J13</f>
-        <v>#DIV/0!</v>
+        <v>3.111111111111111E-2</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>436</v>
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>0</v>
-      </c>
-      <c r="O13" s="72" t="e">
+        <v>62.285714285714285</v>
+      </c>
+      <c r="O13" s="72">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P13" s="14" t="e">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="P13" s="14">
         <f t="shared" ref="P13:P16" si="11">L13/I13</f>
-        <v>#DIV/0!</v>
+        <v>1.2444444444444442</v>
       </c>
       <c r="Q13" s="34"/>
     </row>
@@ -4529,39 +4543,39 @@
       <c r="F19" s="100"/>
       <c r="G19" s="40">
         <f>SUM(G4:G18)</f>
-        <v>5000</v>
+        <v>5600</v>
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>472</v>
+        <v>539</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>9.4399999999999998E-2</v>
+        <v>9.6250000000000002E-2</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
-        <v>7275</v>
+        <v>7725</v>
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>2342</v>
+        <v>2510</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.32192439862542954</v>
+        <v>0.32491909385113271</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>4933</v>
+        <v>5215</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>704.71428571428567</v>
+        <v>745</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>4.9618644067796609</v>
+        <v>4.6567717996289426</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -5200,39 +5214,39 @@
       <c r="F31" s="57"/>
       <c r="G31" s="20">
         <f>+G30+G25+G19</f>
-        <v>5450</v>
+        <v>6050</v>
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>673</v>
+        <v>740</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.12348623853211009</v>
+        <v>0.12231404958677686</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
-        <v>12275</v>
+        <v>12725</v>
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>2621</v>
+        <v>2789</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.21352342158859469</v>
+        <v>0.21917485265225933</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>9654</v>
+        <v>9936</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1379.1428571428571</v>
+        <v>1419.4285714285713</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.8945022288261515</v>
+        <v>3.7689189189189189</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB95B6D-1231-48B1-87A7-1BE99EF6EF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F0EDB3-41FC-4ECD-93C1-9211CF31B782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3646,18 +3646,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.73076923076923073</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" s="94">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3752,34 +3752,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6+12+6+6+12+6+10</f>
-        <v>180</v>
+        <f>92+9+11+10+6+12+6+6+12+6+10+14</f>
+        <v>194</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.3</v>
+        <v>0.32333333333333331</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>201</v>
+        <v>226</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.36545454545454548</v>
+        <v>0.41090909090909089</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>349</v>
+        <v>324</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>49.857142857142854</v>
+        <v>54</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1166666666666667</v>
+        <v>1.1649484536082475</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3809,38 +3809,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8+8+8+8+8+7+8</f>
-        <v>106</v>
+        <f>38+8+5+8+8+8+8+8+7+8+9</f>
+        <v>115</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.17666666666666667</v>
+        <v>0.19166666666666668</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>154</v>
+        <v>176</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.34222222222222221</v>
+        <v>0.39111111111111113</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>42.285714285714285</v>
+        <v>45.666666666666664</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.4528301886792452</v>
+        <v>1.5304347826086957</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.9371069182389937</v>
+        <v>2.0405797101449274</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3867,38 +3867,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6+8+5+9+7+5</f>
-        <v>88</v>
+        <f>32+7+9+6+8+5+9+7+5+6</f>
+        <v>94</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.14666666666666667</v>
+        <v>0.15666666666666668</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.3290909090909091</v>
+        <v>0.35818181818181816</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>52.714285714285715</v>
+        <v>58.833333333333336</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>2.0568181818181817</v>
+        <v>2.0957446808510638</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.2438016528925622</v>
+        <v>2.2862669245647966</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3925,38 +3925,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6+5+23+3+1+5</f>
-        <v>54</v>
+        <f>5+5+1+6+5+23+3+1+5+8</f>
+        <v>62</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>0.09</v>
+        <v>0.10333333333333333</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.1275</v>
+        <v>0.1825</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>349</v>
+        <v>327</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>49.857142857142854</v>
+        <v>54.5</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>0.94444444444444442</v>
+        <v>1.1774193548387097</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.4166666666666667</v>
+        <v>1.7661290322580645</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>80.571428571428569</v>
+        <v>94</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
@@ -4041,38 +4041,38 @@
         <v>600</v>
       </c>
       <c r="H9" s="12">
-        <f>2+4+4+9</f>
-        <v>19</v>
+        <f>2+4+4+9+8</f>
+        <v>27</v>
       </c>
       <c r="I9" s="70">
         <f t="shared" si="0"/>
-        <v>3.1666666666666669E-2</v>
+        <v>4.4999999999999998E-2</v>
       </c>
       <c r="J9" s="11">
         <v>550</v>
       </c>
       <c r="K9" s="12">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="L9" s="71">
         <f t="shared" si="1"/>
-        <v>9.0909090909090905E-3</v>
+        <v>5.6363636363636366E-2</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="5"/>
-        <v>545</v>
+        <v>519</v>
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>77.857142857142861</v>
+        <v>86.5</v>
       </c>
       <c r="O9" s="72">
         <f t="shared" si="4"/>
-        <v>0.26315789473684209</v>
+        <v>1.1481481481481481</v>
       </c>
       <c r="P9" s="14">
         <f t="shared" si="4"/>
-        <v>0.2870813397129186</v>
+        <v>1.2525252525252526</v>
       </c>
       <c r="Q9" s="34"/>
     </row>
@@ -4099,38 +4099,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3+7+5+6+4+10</f>
-        <v>66</v>
+        <f>22+2+7+3+7+5+6+4+10+5</f>
+        <v>71</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.33</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>1293</v>
+        <v>1333</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.43099999999999999</v>
+        <v>0.44433333333333336</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>1707</v>
+        <v>1667</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>243.85714285714286</v>
+        <v>277.83333333333331</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>19.59090909090909</v>
+        <v>18.774647887323944</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.3060606060606059</v>
+        <v>1.2516431924882629</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4156,34 +4156,38 @@
       <c r="G11" s="11">
         <v>600</v>
       </c>
-      <c r="H11" s="12"/>
+      <c r="H11" s="12">
+        <v>322</v>
+      </c>
       <c r="I11" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.53666666666666663</v>
       </c>
       <c r="J11" s="11">
         <v>650</v>
       </c>
-      <c r="K11" s="12"/>
+      <c r="K11" s="12">
+        <v>370</v>
+      </c>
       <c r="L11" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.56923076923076921</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="5"/>
-        <v>650</v>
+        <v>280</v>
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>92.857142857142861</v>
-      </c>
-      <c r="O11" s="72" t="e">
+        <v>46.666666666666664</v>
+      </c>
+      <c r="O11" s="72">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P11" s="14" t="e">
+        <v>1.1490683229813665</v>
+      </c>
+      <c r="P11" s="14">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>1.0606784519827999</v>
       </c>
       <c r="Q11" s="34"/>
     </row>
@@ -4209,34 +4213,38 @@
       <c r="G12" s="11">
         <v>600</v>
       </c>
-      <c r="H12" s="12"/>
+      <c r="H12" s="12">
+        <v>182</v>
+      </c>
       <c r="I12" s="70">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>0.30333333333333334</v>
       </c>
       <c r="J12" s="11">
         <v>550</v>
       </c>
-      <c r="K12" s="12"/>
+      <c r="K12" s="12">
+        <v>185</v>
+      </c>
       <c r="L12" s="71">
         <f t="shared" si="1"/>
-        <v>0</v>
+        <v>0.33636363636363636</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
-        <v>550</v>
+        <v>365</v>
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>78.571428571428569</v>
-      </c>
-      <c r="O12" s="72" t="e">
+        <v>60.833333333333336</v>
+      </c>
+      <c r="O12" s="72">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="P12" s="14" t="e">
+        <v>1.0164835164835164</v>
+      </c>
+      <c r="P12" s="14">
         <f t="shared" si="4"/>
-        <v>#DIV/0!</v>
+        <v>1.1088911088911089</v>
       </c>
       <c r="Q12" s="34"/>
     </row>
@@ -4285,7 +4293,7 @@
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>62.285714285714285</v>
+        <v>72.666666666666671</v>
       </c>
       <c r="O13" s="72">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
@@ -4338,7 +4346,7 @@
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>-14.285714285714286</v>
+        <v>-16.666666666666668</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4440,7 +4448,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>-71.428571428571431</v>
+        <v>-83.333333333333329</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4547,11 +4555,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>539</v>
+        <v>1093</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>9.6250000000000002E-2</v>
+        <v>0.19517857142857142</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4559,27 +4567,27 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>2510</v>
+        <v>3216</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.32491909385113271</v>
+        <v>0.41631067961165047</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>5215</v>
+        <v>4509</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>745</v>
+        <v>751.5</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>4.6567717996289426</v>
-      </c>
-      <c r="P19" s="43" t="e">
+        <v>2.9423604757548034</v>
+      </c>
+      <c r="P19" s="43">
         <f>AVERAGE(P4:P12)</f>
-        <v>#DIV/0!</v>
+        <v>1.6713417768550882</v>
       </c>
       <c r="Q19" s="44"/>
     </row>
@@ -4628,7 +4636,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>66.428571428571431</v>
+        <v>77.5</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4684,7 +4692,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>66.714285714285708</v>
+        <v>77.833333333333329</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4740,7 +4748,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>66.285714285714292</v>
+        <v>77.333333333333329</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4796,7 +4804,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>67.571428571428569</v>
+        <v>78.833333333333329</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4852,7 +4860,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>69.142857142857139</v>
+        <v>80.666666666666671</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4908,7 +4916,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>336.14285714285717</v>
+        <v>392.16666666666669</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4965,7 +4973,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>88</v>
+        <v>102.66666666666667</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5021,7 +5029,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>80.857142857142861</v>
+        <v>94.333333333333329</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5077,7 +5085,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>82</v>
+        <v>95.666666666666671</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5133,7 +5141,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>87.428571428571431</v>
+        <v>102</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5189,7 +5197,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>338.28571428571428</v>
+        <v>394.66666666666669</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5218,11 +5226,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>740</v>
+        <v>1294</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.12231404958677686</v>
+        <v>0.21388429752066115</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5230,27 +5238,27 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>2789</v>
+        <v>3495</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.21917485265225933</v>
+        <v>0.27465618860510804</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>9936</v>
+        <v>9230</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1419.4285714285713</v>
+        <v>1538.3333333333333</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>3.7689189189189189</v>
-      </c>
-      <c r="P31" s="23" t="e">
+        <v>2.7009273570324575</v>
+      </c>
+      <c r="P31" s="23">
         <f>AVERAGE(P30,P19,P25)</f>
-        <v>#DIV/0!</v>
+        <v>1.2237805922850293</v>
       </c>
       <c r="Q31" s="34"/>
     </row>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56F0EDB3-41FC-4ECD-93C1-9211CF31B782}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023BF768-6C9B-44AD-8945-0A1ABCE78863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="78">
   <si>
     <t>Booking</t>
   </si>
@@ -248,9 +248,6 @@
   </si>
   <si>
     <t xml:space="preserve">Umair </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jabran Iqbal </t>
   </si>
   <si>
     <t>Furqan</t>
@@ -1980,7 +1977,7 @@
         <v>22</v>
       </c>
       <c r="F8" s="17" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G8" s="30">
         <v>50</v>
@@ -2053,7 +2050,7 @@
         <v>22</v>
       </c>
       <c r="F9" s="95" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G9" s="30">
         <v>0</v>
@@ -2189,7 +2186,7 @@
         <v>1.0333333333333334</v>
       </c>
       <c r="W10" s="34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AB10">
         <v>33</v>
@@ -3646,18 +3643,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.76923076923076927</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" s="94">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3752,34 +3749,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6+12+6+6+12+6+10+14</f>
-        <v>194</v>
+        <f>92+9+11+10+6+12+6+6+12+6+10+14+9</f>
+        <v>203</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.32333333333333331</v>
+        <v>0.33833333333333332</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.41090909090909089</v>
+        <v>0.42727272727272725</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>54</v>
+        <v>78.75</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1649484536082475</v>
+        <v>1.1576354679802956</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3809,38 +3806,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8+8+8+8+8+7+8+9</f>
-        <v>115</v>
+        <f>38+8+5+8+8+8+8+8+7+8+9+15</f>
+        <v>130</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.19166666666666668</v>
+        <v>0.21666666666666667</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.39111111111111113</v>
+        <v>0.42</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>274</v>
+        <v>261</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>45.666666666666664</v>
+        <v>65.25</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.5304347826086957</v>
+        <v>1.4538461538461538</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>2.0405797101449274</v>
+        <v>1.9384615384615382</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3867,38 +3864,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6+8+5+9+7+5+6</f>
-        <v>94</v>
+        <f>32+7+9+6+8+5+9+7+5+6+8</f>
+        <v>102</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.15666666666666668</v>
+        <v>0.17</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.35818181818181816</v>
+        <v>0.36909090909090908</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>58.833333333333336</v>
+        <v>86.75</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>2.0957446808510638</v>
+        <v>1.9901960784313726</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.2862669245647966</v>
+        <v>2.1711229946524062</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3925,38 +3922,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6+5+23+3+1+5+8</f>
-        <v>62</v>
+        <f>5+5+1+6+5+23+3+1+5+8+7</f>
+        <v>69</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>0.10333333333333333</v>
+        <v>0.115</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.1825</v>
+        <v>0.1925</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>54.5</v>
+        <v>80.75</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.1774193548387097</v>
+        <v>1.1159420289855073</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.7661290322580645</v>
+        <v>1.6739130434782608</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3983,38 +3980,37 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>4+5</f>
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>1.4999999999999999E-2</v>
+        <v>6.6666666666666666E-2</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>11</v>
+        <v>44</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>1.9130434782608695E-2</v>
+        <v>7.6521739130434779E-2</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>564</v>
+        <v>531</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>94</v>
+        <v>132.75</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.2222222222222223</v>
+        <v>1.1000000000000001</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.2753623188405796</v>
+        <v>1.1478260869565218</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4035,44 +4031,39 @@
         <v>22</v>
       </c>
       <c r="F9" s="17" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="G9" s="30">
         <v>600</v>
       </c>
-      <c r="H9" s="12">
-        <f>2+4+4+9+8</f>
-        <v>27</v>
-      </c>
+      <c r="H9" s="12"/>
       <c r="I9" s="70">
         <f t="shared" si="0"/>
-        <v>4.4999999999999998E-2</v>
+        <v>0</v>
       </c>
       <c r="J9" s="11">
         <v>550</v>
       </c>
-      <c r="K9" s="12">
-        <v>31</v>
-      </c>
+      <c r="K9" s="12"/>
       <c r="L9" s="71">
         <f t="shared" si="1"/>
-        <v>5.6363636363636366E-2</v>
+        <v>0</v>
       </c>
       <c r="M9" s="12">
         <f t="shared" si="5"/>
-        <v>519</v>
+        <v>550</v>
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>86.5</v>
-      </c>
-      <c r="O9" s="72">
+        <v>137.5</v>
+      </c>
+      <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
-        <v>1.1481481481481481</v>
-      </c>
-      <c r="P9" s="14">
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P9" s="14" t="e">
         <f t="shared" si="4"/>
-        <v>1.2525252525252526</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q9" s="34"/>
     </row>
@@ -4099,38 +4090,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3+7+5+6+4+10+5</f>
-        <v>71</v>
+        <f>22+2+7+3+7+5+6+4+10+5+5</f>
+        <v>76</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.35499999999999998</v>
+        <v>0.38</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>1333</v>
+        <v>1374</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.44433333333333336</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>1667</v>
+        <v>1626</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>277.83333333333331</v>
+        <v>406.5</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>18.774647887323944</v>
+        <v>18.078947368421051</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.2516431924882629</v>
+        <v>1.2052631578947368</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4157,37 +4148,39 @@
         <v>600</v>
       </c>
       <c r="H11" s="12">
-        <v>322</v>
+        <f>322+12</f>
+        <v>334</v>
       </c>
       <c r="I11" s="70">
         <f t="shared" si="0"/>
-        <v>0.53666666666666663</v>
+        <v>0.55666666666666664</v>
       </c>
       <c r="J11" s="11">
         <v>650</v>
       </c>
       <c r="K11" s="12">
-        <v>370</v>
+        <f>370+19</f>
+        <v>389</v>
       </c>
       <c r="L11" s="71">
         <f t="shared" si="1"/>
-        <v>0.56923076923076921</v>
+        <v>0.59846153846153849</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="5"/>
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>46.666666666666664</v>
+        <v>65.25</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
-        <v>1.1490683229813665</v>
+        <v>1.1646706586826348</v>
       </c>
       <c r="P11" s="14">
         <f t="shared" si="4"/>
-        <v>1.0606784519827999</v>
+        <v>1.0750806080147399</v>
       </c>
       <c r="Q11" s="34"/>
     </row>
@@ -4214,37 +4207,39 @@
         <v>600</v>
       </c>
       <c r="H12" s="12">
-        <v>182</v>
+        <f>182+7</f>
+        <v>189</v>
       </c>
       <c r="I12" s="70">
         <f t="shared" si="0"/>
-        <v>0.30333333333333334</v>
+        <v>0.315</v>
       </c>
       <c r="J12" s="11">
         <v>550</v>
       </c>
       <c r="K12" s="12">
-        <v>185</v>
+        <f>185+12</f>
+        <v>197</v>
       </c>
       <c r="L12" s="71">
         <f t="shared" si="1"/>
-        <v>0.33636363636363636</v>
+        <v>0.35818181818181816</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
-        <v>365</v>
+        <v>353</v>
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>60.833333333333336</v>
+        <v>88.25</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
-        <v>1.0164835164835164</v>
+        <v>1.0423280423280423</v>
       </c>
       <c r="P12" s="14">
         <f t="shared" si="4"/>
-        <v>1.1088911088911089</v>
+        <v>1.1370851370851369</v>
       </c>
       <c r="Q12" s="34"/>
     </row>
@@ -4265,7 +4260,7 @@
         <v>22</v>
       </c>
       <c r="F13" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G13" s="11">
         <v>600</v>
@@ -4293,7 +4288,7 @@
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>72.666666666666671</v>
+        <v>109</v>
       </c>
       <c r="O13" s="72">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
@@ -4346,7 +4341,7 @@
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>-16.666666666666668</v>
+        <v>-25</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4448,7 +4443,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>-83.333333333333329</v>
+        <v>-125</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4555,11 +4550,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>1093</v>
+        <v>1160</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.19517857142857142</v>
+        <v>0.20714285714285716</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4567,27 +4562,27 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>3216</v>
+        <v>3322</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.41631067961165047</v>
+        <v>0.4300323624595469</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>4509</v>
+        <v>4403</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>751.5</v>
+        <v>1100.75</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.9423604757548034</v>
-      </c>
-      <c r="P19" s="43">
+        <v>2.863793103448276</v>
+      </c>
+      <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
-        <v>1.6713417768550882</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q19" s="44"/>
     </row>
@@ -4636,7 +4631,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>77.5</v>
+        <v>116.25</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4692,7 +4687,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>77.833333333333329</v>
+        <v>116.75</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4748,7 +4743,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>77.333333333333329</v>
+        <v>116</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4804,7 +4799,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>78.833333333333329</v>
+        <v>118.25</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4860,7 +4855,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>80.666666666666671</v>
+        <v>121</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4916,7 +4911,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>392.16666666666669</v>
+        <v>588.25</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4973,7 +4968,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>102.66666666666667</v>
+        <v>154</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5029,7 +5024,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>94.333333333333329</v>
+        <v>141.5</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5085,7 +5080,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>95.666666666666671</v>
+        <v>143.5</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5141,7 +5136,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>102</v>
+        <v>153</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5197,7 +5192,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>394.66666666666669</v>
+        <v>592</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5226,11 +5221,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>1294</v>
+        <v>1361</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.21388429752066115</v>
+        <v>0.2249586776859504</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5238,27 +5233,27 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>3495</v>
+        <v>3601</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.27465618860510804</v>
+        <v>0.28298624754420432</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>9230</v>
+        <v>9124</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>1538.3333333333333</v>
+        <v>2281</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.7009273570324575</v>
-      </c>
-      <c r="P31" s="23">
+        <v>2.6458486407053639</v>
+      </c>
+      <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>
-        <v>1.2237805922850293</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="Q31" s="34"/>
     </row>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023BF768-6C9B-44AD-8945-0A1ABCE78863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87022A4B-14DD-4682-9BC7-775868870F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3643,18 +3643,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.84615384615384615</v>
+        <v>0.92307692307692313</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F2" s="94">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3749,34 +3749,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6+12+6+6+12+6+10+14+9</f>
-        <v>203</v>
+        <f>92+9+11+10+6+12+6+6+12+6+10+14+9+10</f>
+        <v>213</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.33833333333333332</v>
+        <v>0.35499999999999998</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.42727272727272725</v>
+        <v>0.44</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>78.75</v>
+        <v>154</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1576354679802956</v>
+        <v>1.136150234741784</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3806,38 +3806,38 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8+8+8+8+8+7+8+9+15</f>
-        <v>130</v>
+        <f>38+8+5+8+8+8+8+8+7+8+9+15+3</f>
+        <v>133</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.21666666666666667</v>
+        <v>0.22166666666666668</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.42</v>
+        <v>0.43333333333333335</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>65.25</v>
+        <v>127.5</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.4538461538461538</v>
+        <v>1.4661654135338347</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.9384615384615382</v>
+        <v>1.9548872180451127</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3864,38 +3864,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6+8+5+9+7+5+6+8</f>
-        <v>102</v>
+        <f>32+7+9+6+8+5+9+7+5+6+8+6</f>
+        <v>108</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.36909090909090908</v>
+        <v>0.38363636363636361</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>86.75</v>
+        <v>169.5</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.9901960784313726</v>
+        <v>1.9537037037037037</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.1711229946524062</v>
+        <v>2.131313131313131</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3922,38 +3922,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6+5+23+3+1+5+8+7</f>
-        <v>69</v>
+        <f>5+5+1+6+5+23+3+1+5+8+7+5</f>
+        <v>74</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>0.115</v>
+        <v>0.12333333333333334</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.1925</v>
+        <v>0.20499999999999999</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>80.75</v>
+        <v>159</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.1159420289855073</v>
+        <v>1.1081081081081081</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.6739130434782608</v>
+        <v>1.6621621621621621</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3980,37 +3980,39 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <v>40</v>
+        <f>40+5</f>
+        <v>45</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>6.6666666666666666E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>44</v>
+        <f>44+7</f>
+        <v>51</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>7.6521739130434779E-2</v>
+        <v>8.8695652173913037E-2</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>531</v>
+        <v>524</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>132.75</v>
+        <v>262</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.1000000000000001</v>
+        <v>1.1333333333333333</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.1478260869565218</v>
+        <v>1.182608695652174</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4055,7 +4057,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>137.5</v>
+        <v>275</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4090,38 +4092,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3+7+5+6+4+10+5+5</f>
-        <v>76</v>
+        <f>22+2+7+3+7+5+6+4+10+5+5+7</f>
+        <v>83</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.38</v>
+        <v>0.41499999999999998</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>1374</v>
+        <v>1589</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.45800000000000002</v>
+        <v>0.52966666666666662</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>1626</v>
+        <v>1411</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>406.5</v>
+        <v>705.5</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>18.078947368421051</v>
+        <v>19.14457831325301</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.2052631578947368</v>
+        <v>1.2763052208835342</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4148,39 +4150,39 @@
         <v>600</v>
       </c>
       <c r="H11" s="12">
-        <f>322+12</f>
-        <v>334</v>
+        <f>322+12+10</f>
+        <v>344</v>
       </c>
       <c r="I11" s="70">
         <f t="shared" si="0"/>
-        <v>0.55666666666666664</v>
+        <v>0.57333333333333336</v>
       </c>
       <c r="J11" s="11">
         <v>650</v>
       </c>
       <c r="K11" s="12">
-        <f>370+19</f>
-        <v>389</v>
+        <f>370+19+12</f>
+        <v>401</v>
       </c>
       <c r="L11" s="71">
         <f t="shared" si="1"/>
-        <v>0.59846153846153849</v>
+        <v>0.61692307692307691</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="5"/>
-        <v>261</v>
+        <v>249</v>
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>65.25</v>
+        <v>124.5</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
-        <v>1.1646706586826348</v>
+        <v>1.1656976744186047</v>
       </c>
       <c r="P11" s="14">
         <f t="shared" si="4"/>
-        <v>1.0750806080147399</v>
+        <v>1.0760286225402504</v>
       </c>
       <c r="Q11" s="34"/>
     </row>
@@ -4207,39 +4209,39 @@
         <v>600</v>
       </c>
       <c r="H12" s="12">
-        <f>182+7</f>
-        <v>189</v>
+        <f>182+7+10+10</f>
+        <v>209</v>
       </c>
       <c r="I12" s="70">
         <f t="shared" si="0"/>
-        <v>0.315</v>
+        <v>0.34833333333333333</v>
       </c>
       <c r="J12" s="11">
         <v>550</v>
       </c>
       <c r="K12" s="12">
-        <f>185+12</f>
-        <v>197</v>
+        <f>185+12+13</f>
+        <v>210</v>
       </c>
       <c r="L12" s="71">
         <f t="shared" si="1"/>
-        <v>0.35818181818181816</v>
+        <v>0.38181818181818183</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>88.25</v>
+        <v>170</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
-        <v>1.0423280423280423</v>
+        <v>1.0047846889952152</v>
       </c>
       <c r="P12" s="14">
         <f t="shared" si="4"/>
-        <v>1.1370851370851369</v>
+        <v>1.096128751631144</v>
       </c>
       <c r="Q12" s="34"/>
     </row>
@@ -4266,37 +4268,39 @@
         <v>600</v>
       </c>
       <c r="H13" s="12">
-        <v>15</v>
+        <f>15+8</f>
+        <v>23</v>
       </c>
       <c r="I13" s="70">
         <f t="shared" ref="I13:I15" si="7">H13/G13</f>
-        <v>2.5000000000000001E-2</v>
+        <v>3.833333333333333E-2</v>
       </c>
       <c r="J13" s="11">
         <v>450</v>
       </c>
       <c r="K13" s="12">
-        <v>14</v>
+        <f>14+9</f>
+        <v>23</v>
       </c>
       <c r="L13" s="71">
         <f t="shared" ref="L13:L16" si="8">K13/J13</f>
-        <v>3.111111111111111E-2</v>
+        <v>5.1111111111111114E-2</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="5"/>
-        <v>436</v>
+        <v>427</v>
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>109</v>
+        <v>213.5</v>
       </c>
       <c r="O13" s="72">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
-        <v>0.93333333333333335</v>
+        <v>1</v>
       </c>
       <c r="P13" s="14">
         <f t="shared" ref="P13:P16" si="11">L13/I13</f>
-        <v>1.2444444444444442</v>
+        <v>1.3333333333333335</v>
       </c>
       <c r="Q13" s="34"/>
     </row>
@@ -4341,7 +4345,7 @@
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>-25</v>
+        <v>-50</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4443,7 +4447,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>-125</v>
+        <v>-250</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4550,11 +4554,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>1160</v>
+        <v>1234</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.20714285714285716</v>
+        <v>0.22035714285714286</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4562,23 +4566,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>3322</v>
+        <v>3604</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.4300323624595469</v>
+        <v>0.46653721682847898</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>4403</v>
+        <v>4121</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>1100.75</v>
+        <v>2060.5</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.863793103448276</v>
+        <v>2.9205834683954621</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4631,7 +4635,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>116.25</v>
+        <v>232.5</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4687,7 +4691,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>116.75</v>
+        <v>233.5</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4743,7 +4747,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>116</v>
+        <v>232</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4799,7 +4803,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>118.25</v>
+        <v>236.5</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4855,7 +4859,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>121</v>
+        <v>242</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4911,7 +4915,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>588.25</v>
+        <v>1176.5</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4968,7 +4972,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>154</v>
+        <v>308</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5024,7 +5028,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>141.5</v>
+        <v>283</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5080,7 +5084,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>143.5</v>
+        <v>287</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5136,7 +5140,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>153</v>
+        <v>306</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5192,7 +5196,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>592</v>
+        <v>1184</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5221,11 +5225,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>1361</v>
+        <v>1435</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.2249586776859504</v>
+        <v>0.2371900826446281</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5233,23 +5237,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>3601</v>
+        <v>3883</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.28298624754420432</v>
+        <v>0.30514734774066798</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>9124</v>
+        <v>8842</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>2281</v>
+        <v>4421</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.6458486407053639</v>
+        <v>2.7059233449477351</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87022A4B-14DD-4682-9BC7-775868870F3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3069FD1-F040-4401-8EB0-F26439B4637F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3643,18 +3643,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.92307692307692313</v>
+        <v>0.96153846153846156</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2" s="94">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3749,34 +3749,34 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6+12+6+6+12+6+10+14+9+10</f>
-        <v>213</v>
+        <f>92+9+11+10+6+12+6+6+12+6+10+14+9+10+19</f>
+        <v>232</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.35499999999999998</v>
+        <v>0.38666666666666666</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.44</v>
+        <v>0.46727272727272728</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="N4" s="10">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>154</v>
+        <v>293</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.136150234741784</v>
+        <v>1.1077586206896552</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="N5" s="14">
         <f t="shared" si="3"/>
-        <v>127.5</v>
+        <v>255</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
@@ -3864,38 +3864,38 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6+8+5+9+7+5+6+8+6</f>
-        <v>108</v>
+        <f>32+7+9+6+8+5+9+7+5+6+8+6+6</f>
+        <v>114</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.38363636363636361</v>
+        <v>0.40727272727272729</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="N6" s="14">
         <f t="shared" si="3"/>
-        <v>169.5</v>
+        <v>326</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>1.9537037037037037</v>
+        <v>1.9649122807017543</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.131313131313131</v>
+        <v>2.1435406698564594</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3922,38 +3922,38 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6+5+23+3+1+5+8+7+5</f>
-        <v>74</v>
+        <f>5+5+1+6+5+23+3+1+5+8+7+5+1</f>
+        <v>75</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>0.12333333333333334</v>
+        <v>0.125</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.20499999999999999</v>
+        <v>0.20749999999999999</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="N7" s="14">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>159</v>
+        <v>317</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.1081081081081081</v>
+        <v>1.1066666666666667</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.6621621621621621</v>
+        <v>1.66</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3980,39 +3980,39 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>40+5</f>
-        <v>45</v>
+        <f>40+5+5</f>
+        <v>50</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>7.4999999999999997E-2</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <f>44+7</f>
-        <v>51</v>
+        <f>44+7+2.5</f>
+        <v>53.5</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>8.8695652173913037E-2</v>
+        <v>9.3043478260869561E-2</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>524</v>
+        <v>521.5</v>
       </c>
       <c r="N8" s="14">
         <f t="shared" si="6"/>
-        <v>262</v>
+        <v>521.5</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.1333333333333333</v>
+        <v>1.07</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.182608695652174</v>
+        <v>1.1165217391304347</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4057,7 +4057,7 @@
       </c>
       <c r="N9" s="14">
         <f t="shared" si="6"/>
-        <v>275</v>
+        <v>550</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4092,38 +4092,38 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3+7+5+6+4+10+5+5+7</f>
-        <v>83</v>
+        <f>22+2+7+3+7+5+6+4+10+5+5+7+2</f>
+        <v>85</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.41499999999999998</v>
+        <v>0.42499999999999999</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>1589</v>
+        <v>1633</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.52966666666666662</v>
+        <v>0.54433333333333334</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>1411</v>
+        <v>1367</v>
       </c>
       <c r="N10" s="14">
         <f t="shared" si="6"/>
-        <v>705.5</v>
+        <v>1367</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>19.14457831325301</v>
+        <v>19.211764705882352</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.2763052208835342</v>
+        <v>1.2807843137254902</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4150,39 +4150,39 @@
         <v>600</v>
       </c>
       <c r="H11" s="12">
-        <f>322+12+10</f>
-        <v>344</v>
+        <f>322+12+10+10</f>
+        <v>354</v>
       </c>
       <c r="I11" s="70">
         <f t="shared" si="0"/>
-        <v>0.57333333333333336</v>
+        <v>0.59</v>
       </c>
       <c r="J11" s="11">
         <v>650</v>
       </c>
       <c r="K11" s="12">
-        <f>370+19+12</f>
-        <v>401</v>
+        <f>370+19+12+20</f>
+        <v>421</v>
       </c>
       <c r="L11" s="71">
         <f t="shared" si="1"/>
-        <v>0.61692307692307691</v>
+        <v>0.64769230769230768</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="5"/>
-        <v>249</v>
+        <v>229</v>
       </c>
       <c r="N11" s="14">
         <f t="shared" si="6"/>
-        <v>124.5</v>
+        <v>229</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
-        <v>1.1656976744186047</v>
+        <v>1.1892655367231639</v>
       </c>
       <c r="P11" s="14">
         <f t="shared" si="4"/>
-        <v>1.0760286225402504</v>
+        <v>1.0977835723598435</v>
       </c>
       <c r="Q11" s="34"/>
     </row>
@@ -4209,39 +4209,39 @@
         <v>600</v>
       </c>
       <c r="H12" s="12">
-        <f>182+7+10+10</f>
-        <v>209</v>
+        <f>182+7+10+10+13</f>
+        <v>222</v>
       </c>
       <c r="I12" s="70">
         <f t="shared" si="0"/>
-        <v>0.34833333333333333</v>
+        <v>0.37</v>
       </c>
       <c r="J12" s="11">
         <v>550</v>
       </c>
       <c r="K12" s="12">
-        <f>185+12+13</f>
-        <v>210</v>
+        <f>185+12+13+30</f>
+        <v>240</v>
       </c>
       <c r="L12" s="71">
         <f t="shared" si="1"/>
-        <v>0.38181818181818183</v>
+        <v>0.43636363636363634</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
-        <v>340</v>
+        <v>310</v>
       </c>
       <c r="N12" s="14">
         <f t="shared" si="6"/>
-        <v>170</v>
+        <v>310</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
-        <v>1.0047846889952152</v>
+        <v>1.0810810810810811</v>
       </c>
       <c r="P12" s="14">
         <f t="shared" si="4"/>
-        <v>1.096128751631144</v>
+        <v>1.1793611793611793</v>
       </c>
       <c r="Q12" s="34"/>
     </row>
@@ -4268,39 +4268,39 @@
         <v>600</v>
       </c>
       <c r="H13" s="12">
-        <f>15+8</f>
-        <v>23</v>
+        <f>15+8+8</f>
+        <v>31</v>
       </c>
       <c r="I13" s="70">
         <f t="shared" ref="I13:I15" si="7">H13/G13</f>
-        <v>3.833333333333333E-2</v>
+        <v>5.1666666666666666E-2</v>
       </c>
       <c r="J13" s="11">
         <v>450</v>
       </c>
       <c r="K13" s="12">
-        <f>14+9</f>
-        <v>23</v>
+        <f>14+9+6</f>
+        <v>29</v>
       </c>
       <c r="L13" s="71">
         <f t="shared" ref="L13:L16" si="8">K13/J13</f>
-        <v>5.1111111111111114E-2</v>
+        <v>6.4444444444444443E-2</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="5"/>
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="N13" s="14">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>213.5</v>
+        <v>421</v>
       </c>
       <c r="O13" s="72">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
-        <v>1</v>
+        <v>0.93548387096774188</v>
       </c>
       <c r="P13" s="14">
         <f t="shared" ref="P13:P16" si="11">L13/I13</f>
-        <v>1.3333333333333335</v>
+        <v>1.2473118279569892</v>
       </c>
       <c r="Q13" s="34"/>
     </row>
@@ -4345,7 +4345,7 @@
       </c>
       <c r="N14" s="14">
         <f t="shared" si="9"/>
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4447,7 +4447,7 @@
       </c>
       <c r="N16" s="14">
         <f t="shared" si="6"/>
-        <v>-250</v>
+        <v>-500</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4554,11 +4554,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>1234</v>
+        <v>1298</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.22035714285714286</v>
+        <v>0.23178571428571429</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4566,23 +4566,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>3604</v>
+        <v>3735.5</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.46653721682847898</v>
+        <v>0.48355987055016181</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>4121</v>
+        <v>3989.5</v>
       </c>
       <c r="N19" s="83">
         <f t="shared" si="6"/>
-        <v>2060.5</v>
+        <v>3989.5</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>2.9205834683954621</v>
+        <v>2.8778890600924498</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4635,7 +4635,7 @@
       </c>
       <c r="N20" s="10">
         <f t="shared" si="6"/>
-        <v>232.5</v>
+        <v>465</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4691,7 +4691,7 @@
       </c>
       <c r="N21" s="14">
         <f t="shared" si="6"/>
-        <v>233.5</v>
+        <v>467</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4747,7 +4747,7 @@
       </c>
       <c r="N22" s="14">
         <f t="shared" si="6"/>
-        <v>232</v>
+        <v>464</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4803,7 +4803,7 @@
       </c>
       <c r="N23" s="14">
         <f t="shared" si="6"/>
-        <v>236.5</v>
+        <v>473</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="N24" s="77">
         <f t="shared" si="6"/>
-        <v>242</v>
+        <v>484</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4915,7 +4915,7 @@
       </c>
       <c r="N25" s="83">
         <f t="shared" si="6"/>
-        <v>1176.5</v>
+        <v>2353</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4972,7 +4972,7 @@
       </c>
       <c r="N26" s="10">
         <f t="shared" si="6"/>
-        <v>308</v>
+        <v>616</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="N27" s="14">
         <f t="shared" si="6"/>
-        <v>283</v>
+        <v>566</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5084,7 +5084,7 @@
       </c>
       <c r="N28" s="14">
         <f t="shared" si="6"/>
-        <v>287</v>
+        <v>574</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5140,7 +5140,7 @@
       </c>
       <c r="N29" s="77">
         <f t="shared" si="6"/>
-        <v>306</v>
+        <v>612</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="N30" s="83">
         <f t="shared" si="6"/>
-        <v>1184</v>
+        <v>2368</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5225,11 +5225,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>1435</v>
+        <v>1499</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.2371900826446281</v>
+        <v>0.24776859504132231</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5237,23 +5237,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>3883</v>
+        <v>4014.5</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.30514734774066798</v>
+        <v>0.31548133595284872</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>8842</v>
+        <v>8710.5</v>
       </c>
       <c r="N31" s="92">
         <f t="shared" si="6"/>
-        <v>4421</v>
+        <v>8710.5</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.7059233449477351</v>
+        <v>2.6781187458305538</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>

--- a/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
+++ b/Aug_2026/daily Reports/Sales Reporting Elite - Rana Bilal Lahore (Final).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\Aug_2026\daily Reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD2CDFF-D059-4F66-AAD2-C1844100341E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD859F01-FABE-4806-86EA-56099E7F007A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3643,18 +3643,18 @@
         <v>26</v>
       </c>
       <c r="B2" s="24">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" s="63">
         <f>+B2/A2</f>
-        <v>0.96153846153846156</v>
+        <v>1</v>
       </c>
       <c r="D2" s="62">
         <f>+A2-B2</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F2" s="94">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="G2" s="107" t="s">
         <v>38</v>
@@ -3749,34 +3749,33 @@
         <v>600</v>
       </c>
       <c r="H4" s="31">
-        <f>92+9+11+10+6+12+6+6+12+6+10+14+9+10+19+19+17</f>
-        <v>268</v>
+        <v>296</v>
       </c>
       <c r="I4" s="68">
         <f t="shared" ref="I4:I31" si="0">H4/G4</f>
-        <v>0.44666666666666666</v>
+        <v>0.49333333333333335</v>
       </c>
       <c r="J4" s="30">
         <v>550</v>
       </c>
       <c r="K4" s="8">
-        <v>318</v>
+        <v>349</v>
       </c>
       <c r="L4" s="87">
         <f t="shared" ref="L4:L29" si="1">K4/J4</f>
-        <v>0.57818181818181813</v>
+        <v>0.63454545454545452</v>
       </c>
       <c r="M4" s="8">
         <f t="shared" ref="M4:M6" si="2">J4-K4</f>
-        <v>232</v>
-      </c>
-      <c r="N4" s="10">
+        <v>201</v>
+      </c>
+      <c r="N4" s="10" t="e">
         <f t="shared" ref="N4:N6" si="3">M4/$D$2</f>
-        <v>232</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O4" s="69">
         <f t="shared" ref="O4:P12" si="4">K4/H4</f>
-        <v>1.1865671641791045</v>
+        <v>1.1790540540540539</v>
       </c>
       <c r="P4" s="33">
         <v>3</v>
@@ -3806,38 +3805,37 @@
         <v>600</v>
       </c>
       <c r="H5" s="12">
-        <f>38+8+5+8+8+8+8+8+7+8+9+15+3+18+17</f>
-        <v>168</v>
+        <v>201</v>
       </c>
       <c r="I5" s="70">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0.33500000000000002</v>
       </c>
       <c r="J5" s="11">
         <v>450</v>
       </c>
       <c r="K5" s="12">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="L5" s="71">
         <f t="shared" si="1"/>
-        <v>0.49777777777777776</v>
+        <v>0.50444444444444447</v>
       </c>
       <c r="M5" s="12">
         <f t="shared" si="2"/>
-        <v>226</v>
-      </c>
-      <c r="N5" s="14">
+        <v>223</v>
+      </c>
+      <c r="N5" s="14" t="e">
         <f t="shared" si="3"/>
-        <v>226</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O5" s="72">
         <f t="shared" si="4"/>
-        <v>1.3333333333333333</v>
+        <v>1.1293532338308458</v>
       </c>
       <c r="P5" s="14">
         <f t="shared" si="4"/>
-        <v>1.7777777777777775</v>
+        <v>1.5058043117744611</v>
       </c>
       <c r="Q5" s="34"/>
     </row>
@@ -3864,38 +3862,37 @@
         <v>600</v>
       </c>
       <c r="H6" s="12">
-        <f>32+7+9+6+8+5+9+7+5+6+8+6+6+5+11</f>
-        <v>130</v>
+        <v>161</v>
       </c>
       <c r="I6" s="70">
         <f t="shared" si="0"/>
-        <v>0.21666666666666667</v>
+        <v>0.26833333333333331</v>
       </c>
       <c r="J6" s="11">
         <v>550</v>
       </c>
       <c r="K6" s="12">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="L6" s="71">
         <f t="shared" si="1"/>
-        <v>0.50545454545454549</v>
+        <v>0.53454545454545455</v>
       </c>
       <c r="M6" s="12">
         <f t="shared" si="2"/>
-        <v>272</v>
-      </c>
-      <c r="N6" s="14">
+        <v>256</v>
+      </c>
+      <c r="N6" s="14" t="e">
         <f t="shared" si="3"/>
-        <v>272</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O6" s="72">
         <f t="shared" si="4"/>
-        <v>2.1384615384615384</v>
+        <v>1.826086956521739</v>
       </c>
       <c r="P6" s="14">
         <f t="shared" si="4"/>
-        <v>2.3328671328671331</v>
+        <v>1.9920948616600791</v>
       </c>
       <c r="Q6" s="34"/>
     </row>
@@ -3922,38 +3919,37 @@
         <v>600</v>
       </c>
       <c r="H7" s="12">
-        <f>5+5+1+6+5+23+3+1+5+8+7+5+1+5+2</f>
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="I7" s="70">
         <f t="shared" si="0"/>
-        <v>0.13666666666666666</v>
+        <v>0.14333333333333334</v>
       </c>
       <c r="J7" s="11">
         <v>400</v>
       </c>
       <c r="K7" s="12">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="L7" s="71">
         <f t="shared" si="1"/>
-        <v>0.23749999999999999</v>
+        <v>0.26</v>
       </c>
       <c r="M7" s="12">
         <f t="shared" ref="M7:M31" si="5">J7-K7</f>
-        <v>305</v>
-      </c>
-      <c r="N7" s="14">
+        <v>296</v>
+      </c>
+      <c r="N7" s="14" t="e">
         <f t="shared" ref="N7:N31" si="6">M7/$D$2</f>
-        <v>305</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O7" s="72">
         <f t="shared" si="4"/>
-        <v>1.1585365853658536</v>
+        <v>1.2093023255813953</v>
       </c>
       <c r="P7" s="14">
         <f t="shared" si="4"/>
-        <v>1.7378048780487805</v>
+        <v>1.8139534883720929</v>
       </c>
       <c r="Q7" s="34"/>
     </row>
@@ -3980,38 +3976,38 @@
         <v>600</v>
       </c>
       <c r="H8" s="12">
-        <f>40+5+5+1+5</f>
-        <v>56</v>
+        <f>40+5+5+1+5+10</f>
+        <v>66</v>
       </c>
       <c r="I8" s="70">
         <f t="shared" si="0"/>
-        <v>9.3333333333333338E-2</v>
+        <v>0.11</v>
       </c>
       <c r="J8" s="11">
         <v>575</v>
       </c>
       <c r="K8" s="12">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="L8" s="71">
         <f t="shared" si="1"/>
-        <v>0.17739130434782607</v>
+        <v>0.11304347826086956</v>
       </c>
       <c r="M8" s="12">
         <f t="shared" si="5"/>
-        <v>473</v>
-      </c>
-      <c r="N8" s="14">
+        <v>510</v>
+      </c>
+      <c r="N8" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>473</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O8" s="72">
         <f t="shared" si="4"/>
-        <v>1.8214285714285714</v>
+        <v>0.98484848484848486</v>
       </c>
       <c r="P8" s="14">
         <f t="shared" si="4"/>
-        <v>1.9006211180124222</v>
+        <v>1.0276679841897234</v>
       </c>
       <c r="Q8" s="34"/>
     </row>
@@ -4054,9 +4050,9 @@
         <f t="shared" si="5"/>
         <v>550</v>
       </c>
-      <c r="N9" s="14">
+      <c r="N9" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>550</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O9" s="72" t="e">
         <f t="shared" si="4"/>
@@ -4091,38 +4087,37 @@
         <v>200</v>
       </c>
       <c r="H10" s="12">
-        <f>22+2+7+3+7+5+6+4+10+5+5+7+2+2+1</f>
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="I10" s="70">
         <f t="shared" si="0"/>
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="J10" s="11">
         <v>3000</v>
       </c>
       <c r="K10" s="12">
-        <v>1671</v>
+        <v>1687</v>
       </c>
       <c r="L10" s="71">
         <f t="shared" si="1"/>
-        <v>0.55700000000000005</v>
+        <v>0.56233333333333335</v>
       </c>
       <c r="M10" s="12">
         <f t="shared" si="5"/>
-        <v>1329</v>
-      </c>
-      <c r="N10" s="14">
+        <v>1313</v>
+      </c>
+      <c r="N10" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>1329</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O10" s="72">
         <f t="shared" si="4"/>
-        <v>18.988636363636363</v>
+        <v>20.573170731707318</v>
       </c>
       <c r="P10" s="14">
         <f t="shared" si="4"/>
-        <v>1.2659090909090911</v>
+        <v>1.3715447154471545</v>
       </c>
       <c r="Q10" s="34"/>
     </row>
@@ -4159,29 +4154,26 @@
       <c r="J11" s="11">
         <v>650</v>
       </c>
-      <c r="K11" s="12">
-        <f>370+19+12+20+20+16</f>
-        <v>457</v>
-      </c>
+      <c r="K11" s="12"/>
       <c r="L11" s="71">
         <f t="shared" si="1"/>
-        <v>0.70307692307692304</v>
+        <v>0</v>
       </c>
       <c r="M11" s="12">
         <f t="shared" si="5"/>
-        <v>193</v>
-      </c>
-      <c r="N11" s="14">
+        <v>650</v>
+      </c>
+      <c r="N11" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>193</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O11" s="72">
         <f t="shared" si="4"/>
-        <v>1.1901041666666667</v>
+        <v>0</v>
       </c>
       <c r="P11" s="14">
         <f t="shared" si="4"/>
-        <v>1.0985576923076923</v>
+        <v>0</v>
       </c>
       <c r="Q11" s="34"/>
     </row>
@@ -4218,29 +4210,26 @@
       <c r="J12" s="11">
         <v>550</v>
       </c>
-      <c r="K12" s="12">
-        <f>185+12+13+30+30+7</f>
-        <v>277</v>
-      </c>
+      <c r="K12" s="12"/>
       <c r="L12" s="71">
         <f t="shared" si="1"/>
-        <v>0.50363636363636366</v>
+        <v>0</v>
       </c>
       <c r="M12" s="12">
         <f t="shared" si="5"/>
-        <v>273</v>
-      </c>
-      <c r="N12" s="14">
+        <v>550</v>
+      </c>
+      <c r="N12" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>273</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O12" s="72">
         <f t="shared" si="4"/>
-        <v>1.1446280991735538</v>
+        <v>0</v>
       </c>
       <c r="P12" s="14">
         <f t="shared" si="4"/>
-        <v>1.2486851990984222</v>
+        <v>0</v>
       </c>
       <c r="Q12" s="34"/>
     </row>
@@ -4277,29 +4266,26 @@
       <c r="J13" s="11">
         <v>450</v>
       </c>
-      <c r="K13" s="12">
-        <f>14+9+6+6</f>
-        <v>35</v>
-      </c>
+      <c r="K13" s="12"/>
       <c r="L13" s="71">
         <f t="shared" ref="L13:L16" si="8">K13/J13</f>
-        <v>7.7777777777777779E-2</v>
+        <v>0</v>
       </c>
       <c r="M13" s="12">
         <f t="shared" si="5"/>
-        <v>415</v>
-      </c>
-      <c r="N13" s="14">
+        <v>450</v>
+      </c>
+      <c r="N13" s="14" t="e">
         <f t="shared" ref="N13:N15" si="9">M13/$D$2</f>
-        <v>415</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O13" s="72">
         <f t="shared" ref="O13:O16" si="10">K13/H13</f>
-        <v>0.89743589743589747</v>
+        <v>0</v>
       </c>
       <c r="P13" s="14">
         <f t="shared" ref="P13:P16" si="11">L13/I13</f>
-        <v>1.1965811965811965</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="34"/>
     </row>
@@ -4342,9 +4328,9 @@
         <f t="shared" si="5"/>
         <v>-100</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="14" t="e">
         <f t="shared" si="9"/>
-        <v>-100</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O14" s="72">
         <f t="shared" si="10"/>
@@ -4391,9 +4377,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="14" t="e">
         <f t="shared" si="9"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O15" s="72" t="e">
         <f t="shared" si="10"/>
@@ -4444,9 +4430,9 @@
         <f t="shared" si="5"/>
         <v>-1000</v>
       </c>
-      <c r="N16" s="14">
+      <c r="N16" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>-1000</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O16" s="72">
         <f t="shared" si="10"/>
@@ -4487,9 +4473,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N17" s="14">
+      <c r="N17" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O17" s="72"/>
       <c r="P17" s="14"/>
@@ -4524,9 +4510,9 @@
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="N18" s="77">
+      <c r="N18" s="77" t="e">
         <f t="shared" si="6"/>
-        <v>0</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O18" s="78"/>
       <c r="P18" s="39"/>
@@ -4553,11 +4539,11 @@
       </c>
       <c r="H19" s="40">
         <f>SUM(H4:H18)</f>
-        <v>1460</v>
+        <v>1560</v>
       </c>
       <c r="I19" s="79">
         <f t="shared" si="0"/>
-        <v>0.26071428571428573</v>
+        <v>0.27857142857142858</v>
       </c>
       <c r="J19" s="80">
         <f>SUM(J4:J18)</f>
@@ -4565,23 +4551,23 @@
       </c>
       <c r="K19" s="80">
         <f>SUM(K4:K18)</f>
-        <v>4557</v>
+        <v>3826</v>
       </c>
       <c r="L19" s="82">
         <f>K19/J19</f>
-        <v>0.58990291262135919</v>
+        <v>0.49527508090614886</v>
       </c>
       <c r="M19" s="81">
         <f t="shared" si="5"/>
-        <v>3168</v>
-      </c>
-      <c r="N19" s="83">
+        <v>3899</v>
+      </c>
+      <c r="N19" s="83" t="e">
         <f t="shared" si="6"/>
-        <v>3168</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O19" s="84">
         <f>K19/H19</f>
-        <v>3.121232876712329</v>
+        <v>2.4525641025641027</v>
       </c>
       <c r="P19" s="43" t="e">
         <f>AVERAGE(P4:P12)</f>
@@ -4632,9 +4618,9 @@
         <f t="shared" si="5"/>
         <v>465</v>
       </c>
-      <c r="N20" s="10">
+      <c r="N20" s="10" t="e">
         <f t="shared" si="6"/>
-        <v>465</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O20" s="86">
         <f t="shared" ref="O20:O24" si="13">K20/H20</f>
@@ -4688,9 +4674,9 @@
         <f t="shared" si="5"/>
         <v>467</v>
       </c>
-      <c r="N21" s="14">
+      <c r="N21" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>467</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O21" s="72">
         <f t="shared" si="13"/>
@@ -4744,9 +4730,9 @@
         <f t="shared" si="5"/>
         <v>464</v>
       </c>
-      <c r="N22" s="14">
+      <c r="N22" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>464</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O22" s="72">
         <f t="shared" si="13"/>
@@ -4800,9 +4786,9 @@
         <f t="shared" si="5"/>
         <v>473</v>
       </c>
-      <c r="N23" s="14">
+      <c r="N23" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>473</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O23" s="72">
         <f t="shared" si="13"/>
@@ -4856,9 +4842,9 @@
         <f t="shared" si="5"/>
         <v>484</v>
       </c>
-      <c r="N24" s="77">
+      <c r="N24" s="77" t="e">
         <f t="shared" si="6"/>
-        <v>484</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O24" s="78">
         <f t="shared" si="13"/>
@@ -4912,9 +4898,9 @@
         <f t="shared" si="5"/>
         <v>2353</v>
       </c>
-      <c r="N25" s="83">
+      <c r="N25" s="83" t="e">
         <f t="shared" si="6"/>
-        <v>2353</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O25" s="84">
         <f>K25/H25</f>
@@ -4969,9 +4955,9 @@
         <f t="shared" si="5"/>
         <v>616</v>
       </c>
-      <c r="N26" s="10">
+      <c r="N26" s="10" t="e">
         <f t="shared" si="6"/>
-        <v>616</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O26" s="86">
         <f t="shared" ref="O26:O29" si="15">K26/H26</f>
@@ -5025,9 +5011,9 @@
         <f t="shared" si="5"/>
         <v>566</v>
       </c>
-      <c r="N27" s="14">
+      <c r="N27" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>566</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O27" s="72">
         <f t="shared" si="15"/>
@@ -5081,9 +5067,9 @@
         <f t="shared" si="5"/>
         <v>574</v>
       </c>
-      <c r="N28" s="14">
+      <c r="N28" s="14" t="e">
         <f t="shared" si="6"/>
-        <v>574</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O28" s="72">
         <f t="shared" si="15"/>
@@ -5137,9 +5123,9 @@
         <f t="shared" si="5"/>
         <v>612</v>
       </c>
-      <c r="N29" s="77">
+      <c r="N29" s="77" t="e">
         <f t="shared" si="6"/>
-        <v>612</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O29" s="78">
         <f t="shared" si="15"/>
@@ -5193,9 +5179,9 @@
         <f t="shared" si="5"/>
         <v>2368</v>
       </c>
-      <c r="N30" s="83">
+      <c r="N30" s="83" t="e">
         <f t="shared" si="6"/>
-        <v>2368</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O30" s="84">
         <f>K30/H30</f>
@@ -5224,11 +5210,11 @@
       </c>
       <c r="H31" s="21">
         <f t="shared" ref="H31:K31" si="17">+H30+H25+H19</f>
-        <v>1661</v>
+        <v>1761</v>
       </c>
       <c r="I31" s="88">
         <f t="shared" si="0"/>
-        <v>0.27454545454545454</v>
+        <v>0.29107438016528925</v>
       </c>
       <c r="J31" s="89">
         <f t="shared" si="17"/>
@@ -5236,23 +5222,23 @@
       </c>
       <c r="K31" s="90">
         <f t="shared" si="17"/>
-        <v>4836</v>
+        <v>4105</v>
       </c>
       <c r="L31" s="91">
         <f>K31/J31</f>
-        <v>0.3800392927308448</v>
+        <v>0.32259332023575638</v>
       </c>
       <c r="M31" s="90">
         <f t="shared" si="5"/>
-        <v>7889</v>
-      </c>
-      <c r="N31" s="92">
+        <v>8620</v>
+      </c>
+      <c r="N31" s="92" t="e">
         <f t="shared" si="6"/>
-        <v>7889</v>
+        <v>#DIV/0!</v>
       </c>
       <c r="O31" s="93">
         <f>K31/H31</f>
-        <v>2.9114990969295604</v>
+        <v>2.331061896649631</v>
       </c>
       <c r="P31" s="23" t="e">
         <f>AVERAGE(P30,P19,P25)</f>
